--- a/writerConference/rssi_output.xlsx
+++ b/writerConference/rssi_output.xlsx
@@ -2841,2410 +2841,2410 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>-31.73988914489746</v>
+        <v>-34.11637115478516</v>
       </c>
       <c r="B1" t="n">
-        <v>-32.42946243286133</v>
+        <v>-36.6533088684082</v>
       </c>
       <c r="C1" t="n">
-        <v>-35.58815383911133</v>
+        <v>-45.87997817993164</v>
       </c>
       <c r="D1" t="n">
-        <v>-36.15460968017578</v>
+        <v>-40.43303680419922</v>
       </c>
       <c r="E1" t="n">
-        <v>-40.74419403076172</v>
+        <v>-48.62301635742188</v>
       </c>
       <c r="F1" t="n">
-        <v>-39.8609733581543</v>
+        <v>-46.73054122924805</v>
       </c>
       <c r="G1" t="n">
-        <v>-42.57514190673828</v>
+        <v>-58.0098762512207</v>
       </c>
       <c r="H1" t="n">
-        <v>-46.60338592529297</v>
+        <v>-54.2076301574707</v>
       </c>
       <c r="I1" t="n">
-        <v>-48.25447463989258</v>
+        <v>-49.12475204467773</v>
       </c>
       <c r="J1" t="n">
-        <v>-44.60097503662109</v>
+        <v>-62.18411254882812</v>
       </c>
       <c r="K1" t="n">
-        <v>-44.7952995300293</v>
+        <v>-61.45221710205078</v>
       </c>
       <c r="L1" t="n">
-        <v>-45.5946044921875</v>
+        <v>-59.2077522277832</v>
       </c>
       <c r="M1" t="n">
-        <v>-50.12831878662109</v>
+        <v>-63.49897003173828</v>
       </c>
       <c r="N1" t="n">
-        <v>-50.54061126708984</v>
+        <v>-61.66976165771484</v>
       </c>
       <c r="O1" t="n">
-        <v>-50.35604858398438</v>
+        <v>-57.34403610229492</v>
       </c>
       <c r="P1" t="n">
-        <v>-51.69874954223633</v>
+        <v>-64.26811218261719</v>
       </c>
       <c r="Q1" t="n">
-        <v>-50.63460159301758</v>
+        <v>-55.73726272583008</v>
       </c>
       <c r="R1" t="n">
-        <v>-52.20363616943359</v>
+        <v>-67.26081848144531</v>
       </c>
       <c r="S1" t="n">
-        <v>-54.53389739990234</v>
+        <v>-64.12453460693359</v>
       </c>
       <c r="T1" t="n">
-        <v>-52.3571662902832</v>
+        <v>-66.47541809082031</v>
       </c>
       <c r="U1" t="n">
-        <v>-51.42533111572266</v>
+        <v>-67.09975433349609</v>
       </c>
       <c r="V1" t="n">
-        <v>-52.77375411987305</v>
+        <v>-64.16859436035156</v>
       </c>
       <c r="W1" t="n">
-        <v>-52.99045562744141</v>
+        <v>-76.94157409667969</v>
       </c>
       <c r="X1" t="n">
-        <v>-56.56414031982422</v>
+        <v>-73.32273864746094</v>
       </c>
       <c r="Y1" t="n">
-        <v>-57.21269989013672</v>
+        <v>-72.23104095458984</v>
       </c>
       <c r="Z1" t="n">
-        <v>-57.63677978515625</v>
+        <v>-67.95345306396484</v>
       </c>
       <c r="AA1" t="n">
-        <v>-57.56461715698242</v>
+        <v>-74.85580444335938</v>
       </c>
       <c r="AB1" t="n">
-        <v>-60.49135589599609</v>
+        <v>-67.77872467041016</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-36.81267929077148</v>
+        <v>-38.22148895263672</v>
       </c>
       <c r="B2" t="n">
-        <v>-34.91189575195312</v>
+        <v>-37.307373046875</v>
       </c>
       <c r="C2" t="n">
-        <v>-38.66301727294922</v>
+        <v>-41.8782958984375</v>
       </c>
       <c r="D2" t="n">
-        <v>-40.37996292114258</v>
+        <v>-41.02332305908203</v>
       </c>
       <c r="E2" t="n">
-        <v>-42.16316986083984</v>
+        <v>-44.5108757019043</v>
       </c>
       <c r="F2" t="n">
-        <v>-41.91585922241211</v>
+        <v>-52.36992645263672</v>
       </c>
       <c r="G2" t="n">
-        <v>-40.94680023193359</v>
+        <v>-52.86273193359375</v>
       </c>
       <c r="H2" t="n">
-        <v>-46.98404693603516</v>
+        <v>-44.13032531738281</v>
       </c>
       <c r="I2" t="n">
-        <v>-45.71127700805664</v>
+        <v>-58.80984497070312</v>
       </c>
       <c r="J2" t="n">
-        <v>-44.61403656005859</v>
+        <v>-61.93291091918945</v>
       </c>
       <c r="K2" t="n">
-        <v>-48.67433929443359</v>
+        <v>-59.68865203857422</v>
       </c>
       <c r="L2" t="n">
-        <v>-51.93740844726562</v>
+        <v>-62.47419357299805</v>
       </c>
       <c r="M2" t="n">
-        <v>-49.50347137451172</v>
+        <v>-58.7570915222168</v>
       </c>
       <c r="N2" t="n">
-        <v>-48.62194442749023</v>
+        <v>-57.72348022460938</v>
       </c>
       <c r="O2" t="n">
-        <v>-51.27848052978516</v>
+        <v>-59.51596069335938</v>
       </c>
       <c r="P2" t="n">
-        <v>-49.85099411010742</v>
+        <v>-65.06832122802734</v>
       </c>
       <c r="Q2" t="n">
-        <v>-50.41632843017578</v>
+        <v>-60.81069183349609</v>
       </c>
       <c r="R2" t="n">
-        <v>-51.35309600830078</v>
+        <v>-66.96089172363281</v>
       </c>
       <c r="S2" t="n">
-        <v>-52.60859298706055</v>
+        <v>-74.45512390136719</v>
       </c>
       <c r="T2" t="n">
-        <v>-49.4244270324707</v>
+        <v>-71.00965881347656</v>
       </c>
       <c r="U2" t="n">
-        <v>-51.58549880981445</v>
+        <v>-74.88463592529297</v>
       </c>
       <c r="V2" t="n">
-        <v>-53.13056182861328</v>
+        <v>-70.10282135009766</v>
       </c>
       <c r="W2" t="n">
-        <v>-52.93049240112305</v>
+        <v>-75.24186706542969</v>
       </c>
       <c r="X2" t="n">
-        <v>-52.4065055847168</v>
+        <v>-70.05940246582031</v>
       </c>
       <c r="Y2" t="n">
-        <v>-54.28730392456055</v>
+        <v>-78.15744781494141</v>
       </c>
       <c r="Z2" t="n">
-        <v>-53.90579986572266</v>
+        <v>-73.27009582519531</v>
       </c>
       <c r="AA2" t="n">
-        <v>-53.74308395385742</v>
+        <v>-74.01828002929688</v>
       </c>
       <c r="AB2" t="n">
-        <v>-56.30080032348633</v>
+        <v>-78.10478210449219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-38.54506683349609</v>
+        <v>-39.65427398681641</v>
       </c>
       <c r="B3" t="n">
-        <v>-37.9269905090332</v>
+        <v>-36.90192413330078</v>
       </c>
       <c r="C3" t="n">
-        <v>-38.3278923034668</v>
+        <v>-38.78023147583008</v>
       </c>
       <c r="D3" t="n">
-        <v>-42.82613754272461</v>
+        <v>-41.30951309204102</v>
       </c>
       <c r="E3" t="n">
-        <v>-44.05791091918945</v>
+        <v>-47.90862274169922</v>
       </c>
       <c r="F3" t="n">
-        <v>-42.48711013793945</v>
+        <v>-49.11072540283203</v>
       </c>
       <c r="G3" t="n">
-        <v>-47.54775619506836</v>
+        <v>-50.19905090332031</v>
       </c>
       <c r="H3" t="n">
-        <v>-42.41589736938477</v>
+        <v>-48.13653182983398</v>
       </c>
       <c r="I3" t="n">
-        <v>-46.82323455810547</v>
+        <v>-61.45248413085938</v>
       </c>
       <c r="J3" t="n">
-        <v>-43.73761749267578</v>
+        <v>-52.00173950195312</v>
       </c>
       <c r="K3" t="n">
-        <v>-46.90348434448242</v>
+        <v>-56.79397583007812</v>
       </c>
       <c r="L3" t="n">
-        <v>-48.34639739990234</v>
+        <v>-58.40578079223633</v>
       </c>
       <c r="M3" t="n">
-        <v>-50.9393196105957</v>
+        <v>-67.90570068359375</v>
       </c>
       <c r="N3" t="n">
-        <v>-48.37625885009766</v>
+        <v>-65.03328704833984</v>
       </c>
       <c r="O3" t="n">
-        <v>-49.11184310913086</v>
+        <v>-58.81159210205078</v>
       </c>
       <c r="P3" t="n">
-        <v>-50.50649261474609</v>
+        <v>-58.88004684448242</v>
       </c>
       <c r="Q3" t="n">
-        <v>-52.43607330322266</v>
+        <v>-67.30168151855469</v>
       </c>
       <c r="R3" t="n">
-        <v>-51.2906608581543</v>
+        <v>-63.71181488037109</v>
       </c>
       <c r="S3" t="n">
-        <v>-55.76071166992188</v>
+        <v>-67.26791381835938</v>
       </c>
       <c r="T3" t="n">
-        <v>-50.20852661132812</v>
+        <v>-72.96994018554688</v>
       </c>
       <c r="U3" t="n">
-        <v>-55.50812530517578</v>
+        <v>-75.73875427246094</v>
       </c>
       <c r="V3" t="n">
-        <v>-51.6044807434082</v>
+        <v>-67.12599182128906</v>
       </c>
       <c r="W3" t="n">
-        <v>-53.99892044067383</v>
+        <v>-67.43167877197266</v>
       </c>
       <c r="X3" t="n">
-        <v>-53.87089920043945</v>
+        <v>-69.94474792480469</v>
       </c>
       <c r="Y3" t="n">
-        <v>-56.74726104736328</v>
+        <v>-72.42018127441406</v>
       </c>
       <c r="Z3" t="n">
-        <v>-54.44118118286133</v>
+        <v>-73.42662048339844</v>
       </c>
       <c r="AA3" t="n">
-        <v>-57.31298828125</v>
+        <v>-76.06328582763672</v>
       </c>
       <c r="AB3" t="n">
-        <v>-55.3466682434082</v>
+        <v>-73.77793884277344</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-38.04422760009766</v>
+        <v>-42.30608367919922</v>
       </c>
       <c r="B4" t="n">
-        <v>-37.18502044677734</v>
+        <v>-40.14012908935547</v>
       </c>
       <c r="C4" t="n">
-        <v>-38.63078689575195</v>
+        <v>-43.38594055175781</v>
       </c>
       <c r="D4" t="n">
-        <v>-41.09058380126953</v>
+        <v>-43.13276290893555</v>
       </c>
       <c r="E4" t="n">
-        <v>-41.83008575439453</v>
+        <v>-48.0493278503418</v>
       </c>
       <c r="F4" t="n">
-        <v>-43.35531234741211</v>
+        <v>-56.07853317260742</v>
       </c>
       <c r="G4" t="n">
-        <v>-45.87278747558594</v>
+        <v>-57.60425567626953</v>
       </c>
       <c r="H4" t="n">
-        <v>-45.20355606079102</v>
+        <v>-53.7482795715332</v>
       </c>
       <c r="I4" t="n">
-        <v>-47.27805328369141</v>
+        <v>-59.43844604492188</v>
       </c>
       <c r="J4" t="n">
-        <v>-48.25748825073242</v>
+        <v>-56.68595504760742</v>
       </c>
       <c r="K4" t="n">
-        <v>-51.39498138427734</v>
+        <v>-56.51900100708008</v>
       </c>
       <c r="L4" t="n">
-        <v>-48.55614471435547</v>
+        <v>-61.55584716796875</v>
       </c>
       <c r="M4" t="n">
-        <v>-48.38710403442383</v>
+        <v>-60.51676177978516</v>
       </c>
       <c r="N4" t="n">
-        <v>-47.0711669921875</v>
+        <v>-65.96244812011719</v>
       </c>
       <c r="O4" t="n">
-        <v>-50.01717376708984</v>
+        <v>-64.90236663818359</v>
       </c>
       <c r="P4" t="n">
-        <v>-51.92952728271484</v>
+        <v>-66.82142639160156</v>
       </c>
       <c r="Q4" t="n">
-        <v>-53.86928176879883</v>
+        <v>-66.11281585693359</v>
       </c>
       <c r="R4" t="n">
-        <v>-55.63983154296875</v>
+        <v>-66.24061584472656</v>
       </c>
       <c r="S4" t="n">
-        <v>-53.69623565673828</v>
+        <v>-72.46485900878906</v>
       </c>
       <c r="T4" t="n">
-        <v>-52.71157073974609</v>
+        <v>-71.88596343994141</v>
       </c>
       <c r="U4" t="n">
-        <v>-50.58631134033203</v>
+        <v>-76.25927734375</v>
       </c>
       <c r="V4" t="n">
-        <v>-54.9727897644043</v>
+        <v>-73.21586608886719</v>
       </c>
       <c r="W4" t="n">
-        <v>-54.3115348815918</v>
+        <v>-66.10075378417969</v>
       </c>
       <c r="X4" t="n">
-        <v>-56.59212112426758</v>
+        <v>-76.47300720214844</v>
       </c>
       <c r="Y4" t="n">
-        <v>-54.1353874206543</v>
+        <v>-69.06064605712891</v>
       </c>
       <c r="Z4" t="n">
-        <v>-51.92157745361328</v>
+        <v>-75.22959136962891</v>
       </c>
       <c r="AA4" t="n">
-        <v>-55.03647613525391</v>
+        <v>-74.0244140625</v>
       </c>
       <c r="AB4" t="n">
-        <v>-51.60871124267578</v>
+        <v>-70.76675415039062</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-41.05666351318359</v>
+        <v>-45.06870269775391</v>
       </c>
       <c r="B5" t="n">
-        <v>-39.52852630615234</v>
+        <v>-46.41352081298828</v>
       </c>
       <c r="C5" t="n">
-        <v>-45.05177307128906</v>
+        <v>-48.22005462646484</v>
       </c>
       <c r="D5" t="n">
-        <v>-43.23124313354492</v>
+        <v>-49.5151481628418</v>
       </c>
       <c r="E5" t="n">
-        <v>-45.6072998046875</v>
+        <v>-53.07341384887695</v>
       </c>
       <c r="F5" t="n">
-        <v>-43.97835922241211</v>
+        <v>-49.06997680664062</v>
       </c>
       <c r="G5" t="n">
-        <v>-44.34788131713867</v>
+        <v>-45.52576446533203</v>
       </c>
       <c r="H5" t="n">
-        <v>-42.22414016723633</v>
+        <v>-60.41010665893555</v>
       </c>
       <c r="I5" t="n">
-        <v>-46.35562133789062</v>
+        <v>-59.65986251831055</v>
       </c>
       <c r="J5" t="n">
-        <v>-45.75962448120117</v>
+        <v>-58.02349090576172</v>
       </c>
       <c r="K5" t="n">
-        <v>-47.91632843017578</v>
+        <v>-62.98993682861328</v>
       </c>
       <c r="L5" t="n">
-        <v>-48.83633804321289</v>
+        <v>-64.71311187744141</v>
       </c>
       <c r="M5" t="n">
-        <v>-48.36687850952148</v>
+        <v>-58.01709747314453</v>
       </c>
       <c r="N5" t="n">
-        <v>-50.75573348999023</v>
+        <v>-65.38529205322266</v>
       </c>
       <c r="O5" t="n">
-        <v>-50.21101379394531</v>
+        <v>-60.28300857543945</v>
       </c>
       <c r="P5" t="n">
-        <v>-49.68480682373047</v>
+        <v>-65.58174133300781</v>
       </c>
       <c r="Q5" t="n">
-        <v>-50.76472473144531</v>
+        <v>-64.42340087890625</v>
       </c>
       <c r="R5" t="n">
-        <v>-53.2379264831543</v>
+        <v>-64.12812042236328</v>
       </c>
       <c r="S5" t="n">
-        <v>-54.4400520324707</v>
+        <v>-70.83783721923828</v>
       </c>
       <c r="T5" t="n">
-        <v>-52.08837127685547</v>
+        <v>-67.59728240966797</v>
       </c>
       <c r="U5" t="n">
-        <v>-52.79519653320312</v>
+        <v>-69.63531494140625</v>
       </c>
       <c r="V5" t="n">
-        <v>-54.89124298095703</v>
+        <v>-74.05799865722656</v>
       </c>
       <c r="W5" t="n">
-        <v>-52.30797576904297</v>
+        <v>-75.2901611328125</v>
       </c>
       <c r="X5" t="n">
-        <v>-53.9687385559082</v>
+        <v>-66.83589935302734</v>
       </c>
       <c r="Y5" t="n">
-        <v>-54.96966552734375</v>
+        <v>-80.40653991699219</v>
       </c>
       <c r="Z5" t="n">
-        <v>-59.09485626220703</v>
+        <v>-75.79234313964844</v>
       </c>
       <c r="AA5" t="n">
-        <v>-55.8912353515625</v>
+        <v>-73.58518981933594</v>
       </c>
       <c r="AB5" t="n">
-        <v>-52.83844757080078</v>
+        <v>-78.6878662109375</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-40.99485015869141</v>
+        <v>-45.83216094970703</v>
       </c>
       <c r="B6" t="n">
-        <v>-44.61943054199219</v>
+        <v>-45.21195220947266</v>
       </c>
       <c r="C6" t="n">
-        <v>-40.77645111083984</v>
+        <v>-48.22712326049805</v>
       </c>
       <c r="D6" t="n">
-        <v>-44.27646636962891</v>
+        <v>-49.01468658447266</v>
       </c>
       <c r="E6" t="n">
-        <v>-43.09598922729492</v>
+        <v>-52.32479095458984</v>
       </c>
       <c r="F6" t="n">
-        <v>-43.15429306030273</v>
+        <v>-47.5359001159668</v>
       </c>
       <c r="G6" t="n">
-        <v>-45.61401748657227</v>
+        <v>-58.75785446166992</v>
       </c>
       <c r="H6" t="n">
-        <v>-46.14541244506836</v>
+        <v>-52.70646286010742</v>
       </c>
       <c r="I6" t="n">
-        <v>-44.73264312744141</v>
+        <v>-60.93107986450195</v>
       </c>
       <c r="J6" t="n">
-        <v>-50.25421905517578</v>
+        <v>-62.14016723632812</v>
       </c>
       <c r="K6" t="n">
-        <v>-45.63645172119141</v>
+        <v>-58.11358642578125</v>
       </c>
       <c r="L6" t="n">
-        <v>-48.66823959350586</v>
+        <v>-58.88413238525391</v>
       </c>
       <c r="M6" t="n">
-        <v>-52.6375732421875</v>
+        <v>-60.73702239990234</v>
       </c>
       <c r="N6" t="n">
-        <v>-52.8624267578125</v>
+        <v>-66.95805358886719</v>
       </c>
       <c r="O6" t="n">
-        <v>-50.93155288696289</v>
+        <v>-62.501953125</v>
       </c>
       <c r="P6" t="n">
-        <v>-49.86342620849609</v>
+        <v>-62.71464920043945</v>
       </c>
       <c r="Q6" t="n">
-        <v>-52.34780883789062</v>
+        <v>-69.23302459716797</v>
       </c>
       <c r="R6" t="n">
-        <v>-53.71743011474609</v>
+        <v>-69.46364593505859</v>
       </c>
       <c r="S6" t="n">
-        <v>-55.62947845458984</v>
+        <v>-68.75613403320312</v>
       </c>
       <c r="T6" t="n">
-        <v>-58.31301879882812</v>
+        <v>-70.92040252685547</v>
       </c>
       <c r="U6" t="n">
-        <v>-53.8682746887207</v>
+        <v>-71.65497589111328</v>
       </c>
       <c r="V6" t="n">
-        <v>-55.5026741027832</v>
+        <v>-64.84494781494141</v>
       </c>
       <c r="W6" t="n">
-        <v>-54.87021636962891</v>
+        <v>-74.29389953613281</v>
       </c>
       <c r="X6" t="n">
-        <v>-54.19746017456055</v>
+        <v>-77.20683288574219</v>
       </c>
       <c r="Y6" t="n">
-        <v>-51.78805541992188</v>
+        <v>-73.67057800292969</v>
       </c>
       <c r="Z6" t="n">
-        <v>-53.21662521362305</v>
+        <v>-65.24075317382812</v>
       </c>
       <c r="AA6" t="n">
-        <v>-54.3794059753418</v>
+        <v>-73.52275085449219</v>
       </c>
       <c r="AB6" t="n">
-        <v>-58.3748664855957</v>
+        <v>-75.03868103027344</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-42.25920104980469</v>
+        <v>-52.55064010620117</v>
       </c>
       <c r="B7" t="n">
-        <v>-38.40400314331055</v>
+        <v>-44.36159515380859</v>
       </c>
       <c r="C7" t="n">
-        <v>-40.46535873413086</v>
+        <v>-46.95054626464844</v>
       </c>
       <c r="D7" t="n">
-        <v>-46.57241821289062</v>
+        <v>-52.7752799987793</v>
       </c>
       <c r="E7" t="n">
-        <v>-42.15779876708984</v>
+        <v>-59.0351676940918</v>
       </c>
       <c r="F7" t="n">
-        <v>-44.89062881469727</v>
+        <v>-56.33314895629883</v>
       </c>
       <c r="G7" t="n">
-        <v>-47.35093307495117</v>
+        <v>-62.00311279296875</v>
       </c>
       <c r="H7" t="n">
-        <v>-46.50449752807617</v>
+        <v>-54.91413116455078</v>
       </c>
       <c r="I7" t="n">
-        <v>-45.70908737182617</v>
+        <v>-55.67525482177734</v>
       </c>
       <c r="J7" t="n">
-        <v>-47.87649154663086</v>
+        <v>-60.29683303833008</v>
       </c>
       <c r="K7" t="n">
-        <v>-48.74477767944336</v>
+        <v>-63.53171920776367</v>
       </c>
       <c r="L7" t="n">
-        <v>-45.71120452880859</v>
+        <v>-59.90761566162109</v>
       </c>
       <c r="M7" t="n">
-        <v>-54.4282341003418</v>
+        <v>-70.68942260742188</v>
       </c>
       <c r="N7" t="n">
-        <v>-46.24619674682617</v>
+        <v>-63.30930709838867</v>
       </c>
       <c r="O7" t="n">
-        <v>-50.92034149169922</v>
+        <v>-65.38378143310547</v>
       </c>
       <c r="P7" t="n">
-        <v>-48.57260513305664</v>
+        <v>-64.64239501953125</v>
       </c>
       <c r="Q7" t="n">
-        <v>-49.75765228271484</v>
+        <v>-68.47403717041016</v>
       </c>
       <c r="R7" t="n">
-        <v>-51.11204528808594</v>
+        <v>-67.336181640625</v>
       </c>
       <c r="S7" t="n">
-        <v>-52.55612182617188</v>
+        <v>-69.46773529052734</v>
       </c>
       <c r="T7" t="n">
-        <v>-52.98968505859375</v>
+        <v>-70.10330200195312</v>
       </c>
       <c r="U7" t="n">
-        <v>-54.19139862060547</v>
+        <v>-75.05308532714844</v>
       </c>
       <c r="V7" t="n">
-        <v>-52.23403167724609</v>
+        <v>-69.23465728759766</v>
       </c>
       <c r="W7" t="n">
-        <v>-54.4010124206543</v>
+        <v>-76.34042358398438</v>
       </c>
       <c r="X7" t="n">
-        <v>-49.26727294921875</v>
+        <v>-79.91173553466797</v>
       </c>
       <c r="Y7" t="n">
-        <v>-53.65781784057617</v>
+        <v>-77.07918548583984</v>
       </c>
       <c r="Z7" t="n">
-        <v>-58.41410064697266</v>
+        <v>-77.50023651123047</v>
       </c>
       <c r="AA7" t="n">
-        <v>-55.72740936279297</v>
+        <v>-72.87997436523438</v>
       </c>
       <c r="AB7" t="n">
-        <v>-55.60271453857422</v>
+        <v>-73.40400695800781</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-44.45858764648438</v>
+        <v>-58.90299606323242</v>
       </c>
       <c r="B8" t="n">
-        <v>-44.25540924072266</v>
+        <v>-54.50397491455078</v>
       </c>
       <c r="C8" t="n">
-        <v>-43.74545288085938</v>
+        <v>-51.81438064575195</v>
       </c>
       <c r="D8" t="n">
-        <v>-45.87172698974609</v>
+        <v>-56.38456344604492</v>
       </c>
       <c r="E8" t="n">
-        <v>-43.96171188354492</v>
+        <v>-54.65220260620117</v>
       </c>
       <c r="F8" t="n">
-        <v>-45.97286605834961</v>
+        <v>-52.44931793212891</v>
       </c>
       <c r="G8" t="n">
-        <v>-47.42250442504883</v>
+        <v>-62.03805541992188</v>
       </c>
       <c r="H8" t="n">
-        <v>-45.85314178466797</v>
+        <v>-54.58379364013672</v>
       </c>
       <c r="I8" t="n">
-        <v>-48.96924209594727</v>
+        <v>-60.07946014404297</v>
       </c>
       <c r="J8" t="n">
-        <v>-46.9132080078125</v>
+        <v>-54.66326904296875</v>
       </c>
       <c r="K8" t="n">
-        <v>-51.83929443359375</v>
+        <v>-63.52217864990234</v>
       </c>
       <c r="L8" t="n">
-        <v>-48.4498291015625</v>
+        <v>-62.42234420776367</v>
       </c>
       <c r="M8" t="n">
-        <v>-50.18611907958984</v>
+        <v>-60.19309234619141</v>
       </c>
       <c r="N8" t="n">
-        <v>-48.47720718383789</v>
+        <v>-64.77719879150391</v>
       </c>
       <c r="O8" t="n">
-        <v>-53.0195198059082</v>
+        <v>-66.37787628173828</v>
       </c>
       <c r="P8" t="n">
-        <v>-53.72293853759766</v>
+        <v>-66.99349975585938</v>
       </c>
       <c r="Q8" t="n">
-        <v>-52.75686645507812</v>
+        <v>-65.32234954833984</v>
       </c>
       <c r="R8" t="n">
-        <v>-52.73811721801758</v>
+        <v>-71.58641052246094</v>
       </c>
       <c r="S8" t="n">
-        <v>-51.50477981567383</v>
+        <v>-67.9176025390625</v>
       </c>
       <c r="T8" t="n">
-        <v>-54.09079742431641</v>
+        <v>-74.50788879394531</v>
       </c>
       <c r="U8" t="n">
-        <v>-52.62389373779297</v>
+        <v>-73.09005737304688</v>
       </c>
       <c r="V8" t="n">
-        <v>-53.69901657104492</v>
+        <v>-79.71280670166016</v>
       </c>
       <c r="W8" t="n">
-        <v>-54.2218017578125</v>
+        <v>-76.6611328125</v>
       </c>
       <c r="X8" t="n">
-        <v>-56.57583618164062</v>
+        <v>-80.03514099121094</v>
       </c>
       <c r="Y8" t="n">
-        <v>-53.90227127075195</v>
+        <v>-75.90629577636719</v>
       </c>
       <c r="Z8" t="n">
-        <v>-51.38205718994141</v>
+        <v>-82.63311767578125</v>
       </c>
       <c r="AA8" t="n">
-        <v>-54.3906135559082</v>
+        <v>-73.03665924072266</v>
       </c>
       <c r="AB8" t="n">
-        <v>-51.83428192138672</v>
+        <v>-78.9610595703125</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-44.66403198242188</v>
+        <v>-54.93033981323242</v>
       </c>
       <c r="B9" t="n">
-        <v>-45.29808807373047</v>
+        <v>-63.51296234130859</v>
       </c>
       <c r="C9" t="n">
-        <v>-45.10898971557617</v>
+        <v>-45.91229248046875</v>
       </c>
       <c r="D9" t="n">
-        <v>-47.71498107910156</v>
+        <v>-50.96499252319336</v>
       </c>
       <c r="E9" t="n">
-        <v>-45.70597839355469</v>
+        <v>-54.72962188720703</v>
       </c>
       <c r="F9" t="n">
-        <v>-47.09680938720703</v>
+        <v>-61.21733856201172</v>
       </c>
       <c r="G9" t="n">
-        <v>-47.5026969909668</v>
+        <v>-54.1136589050293</v>
       </c>
       <c r="H9" t="n">
-        <v>-48.38098907470703</v>
+        <v>-57.64798736572266</v>
       </c>
       <c r="I9" t="n">
-        <v>-46.61978149414062</v>
+        <v>-66.20262145996094</v>
       </c>
       <c r="J9" t="n">
-        <v>-51.20893478393555</v>
+        <v>-61.69264602661133</v>
       </c>
       <c r="K9" t="n">
-        <v>-49.2418327331543</v>
+        <v>-61.90459442138672</v>
       </c>
       <c r="L9" t="n">
-        <v>-47.6416015625</v>
+        <v>-67.56010437011719</v>
       </c>
       <c r="M9" t="n">
-        <v>-52.03745651245117</v>
+        <v>-64.25249481201172</v>
       </c>
       <c r="N9" t="n">
-        <v>-52.97294998168945</v>
+        <v>-67.17228698730469</v>
       </c>
       <c r="O9" t="n">
-        <v>-54.36359405517578</v>
+        <v>-63.75237274169922</v>
       </c>
       <c r="P9" t="n">
-        <v>-52.6606330871582</v>
+        <v>-70.75910186767578</v>
       </c>
       <c r="Q9" t="n">
-        <v>-55.86273193359375</v>
+        <v>-63.83807373046875</v>
       </c>
       <c r="R9" t="n">
-        <v>-53.16482543945312</v>
+        <v>-72.48048400878906</v>
       </c>
       <c r="S9" t="n">
-        <v>-53.9349479675293</v>
+        <v>-73.07559967041016</v>
       </c>
       <c r="T9" t="n">
-        <v>-54.6314697265625</v>
+        <v>-68.86283874511719</v>
       </c>
       <c r="U9" t="n">
-        <v>-51.4801025390625</v>
+        <v>-68.93473815917969</v>
       </c>
       <c r="V9" t="n">
-        <v>-52.78258514404297</v>
+        <v>-75.88720703125</v>
       </c>
       <c r="W9" t="n">
-        <v>-52.32088088989258</v>
+        <v>-74.65080261230469</v>
       </c>
       <c r="X9" t="n">
-        <v>-53.01553344726562</v>
+        <v>-70.75167083740234</v>
       </c>
       <c r="Y9" t="n">
-        <v>-53.86494827270508</v>
+        <v>-77.44165802001953</v>
       </c>
       <c r="Z9" t="n">
-        <v>-53.30454254150391</v>
+        <v>-76.54146575927734</v>
       </c>
       <c r="AA9" t="n">
-        <v>-55.30101776123047</v>
+        <v>-79.22209167480469</v>
       </c>
       <c r="AB9" t="n">
-        <v>-57.9416389465332</v>
+        <v>-78.50932312011719</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-39.12181091308594</v>
+        <v>-53.9743537902832</v>
       </c>
       <c r="B10" t="n">
-        <v>-46.64934921264648</v>
+        <v>-52.66562652587891</v>
       </c>
       <c r="C10" t="n">
-        <v>-45.1938591003418</v>
+        <v>-51.15245056152344</v>
       </c>
       <c r="D10" t="n">
-        <v>-48.27265167236328</v>
+        <v>-61.33113479614258</v>
       </c>
       <c r="E10" t="n">
-        <v>-50.68456268310547</v>
+        <v>-67.76570129394531</v>
       </c>
       <c r="F10" t="n">
-        <v>-45.89110946655273</v>
+        <v>-65.94810485839844</v>
       </c>
       <c r="G10" t="n">
-        <v>-46.09725952148438</v>
+        <v>-60.66793060302734</v>
       </c>
       <c r="H10" t="n">
-        <v>-48.12667465209961</v>
+        <v>-62.16201782226562</v>
       </c>
       <c r="I10" t="n">
-        <v>-47.01843643188477</v>
+        <v>-61.02276611328125</v>
       </c>
       <c r="J10" t="n">
-        <v>-50.17618560791016</v>
+        <v>-68.72425079345703</v>
       </c>
       <c r="K10" t="n">
-        <v>-48.57525634765625</v>
+        <v>-67.71443939208984</v>
       </c>
       <c r="L10" t="n">
-        <v>-53.5469856262207</v>
+        <v>-65.15165710449219</v>
       </c>
       <c r="M10" t="n">
-        <v>-50.12737274169922</v>
+        <v>-66.53916931152344</v>
       </c>
       <c r="N10" t="n">
-        <v>-54.78336334228516</v>
+        <v>-65.94584655761719</v>
       </c>
       <c r="O10" t="n">
-        <v>-53.8497314453125</v>
+        <v>-69.16143035888672</v>
       </c>
       <c r="P10" t="n">
-        <v>-52.02029418945312</v>
+        <v>-69.70945739746094</v>
       </c>
       <c r="Q10" t="n">
-        <v>-50.90266799926758</v>
+        <v>-66.43873596191406</v>
       </c>
       <c r="R10" t="n">
-        <v>-50.06453704833984</v>
+        <v>-69.97699737548828</v>
       </c>
       <c r="S10" t="n">
-        <v>-53.68118286132812</v>
+        <v>-70.95146942138672</v>
       </c>
       <c r="T10" t="n">
-        <v>-54.89473724365234</v>
+        <v>-71.34263610839844</v>
       </c>
       <c r="U10" t="n">
-        <v>-56.57947540283203</v>
+        <v>-73.86199188232422</v>
       </c>
       <c r="V10" t="n">
-        <v>-55.93012619018555</v>
+        <v>-74.97004699707031</v>
       </c>
       <c r="W10" t="n">
-        <v>-54.77272796630859</v>
+        <v>-65.27073669433594</v>
       </c>
       <c r="X10" t="n">
-        <v>-54.05218505859375</v>
+        <v>-74.90641784667969</v>
       </c>
       <c r="Y10" t="n">
-        <v>-54.90413284301758</v>
+        <v>-74.16950988769531</v>
       </c>
       <c r="Z10" t="n">
-        <v>-55.8582878112793</v>
+        <v>-74.47250366210938</v>
       </c>
       <c r="AA10" t="n">
-        <v>-58.16130447387695</v>
+        <v>-76.69729614257812</v>
       </c>
       <c r="AB10" t="n">
-        <v>-53.4565315246582</v>
+        <v>-81.33036041259766</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-47.02125549316406</v>
+        <v>-58.41929244995117</v>
       </c>
       <c r="B11" t="n">
-        <v>-46.58137893676758</v>
+        <v>-51.51115798950195</v>
       </c>
       <c r="C11" t="n">
-        <v>-47.22534942626953</v>
+        <v>-49.23949813842773</v>
       </c>
       <c r="D11" t="n">
-        <v>-46.60981750488281</v>
+        <v>-58.14957427978516</v>
       </c>
       <c r="E11" t="n">
-        <v>-49.63618087768555</v>
+        <v>-63.22345733642578</v>
       </c>
       <c r="F11" t="n">
-        <v>-47.89403533935547</v>
+        <v>-54.51686477661133</v>
       </c>
       <c r="G11" t="n">
-        <v>-49.24105072021484</v>
+        <v>-57.3114128112793</v>
       </c>
       <c r="H11" t="n">
-        <v>-52.19019317626953</v>
+        <v>-63.6290168762207</v>
       </c>
       <c r="I11" t="n">
-        <v>-46.71459197998047</v>
+        <v>-61.3636589050293</v>
       </c>
       <c r="J11" t="n">
-        <v>-50.47639846801758</v>
+        <v>-64.21614837646484</v>
       </c>
       <c r="K11" t="n">
-        <v>-47.24239730834961</v>
+        <v>-61.12168121337891</v>
       </c>
       <c r="L11" t="n">
-        <v>-53.22939300537109</v>
+        <v>-60.05228424072266</v>
       </c>
       <c r="M11" t="n">
-        <v>-50.3544921875</v>
+        <v>-66.45494842529297</v>
       </c>
       <c r="N11" t="n">
-        <v>-48.27704620361328</v>
+        <v>-64.01594543457031</v>
       </c>
       <c r="O11" t="n">
-        <v>-52.2994270324707</v>
+        <v>-63.36746978759766</v>
       </c>
       <c r="P11" t="n">
-        <v>-51.86870574951172</v>
+        <v>-66.71738433837891</v>
       </c>
       <c r="Q11" t="n">
-        <v>-52.95248413085938</v>
+        <v>-69.00900268554688</v>
       </c>
       <c r="R11" t="n">
-        <v>-52.68215179443359</v>
+        <v>-68.34485626220703</v>
       </c>
       <c r="S11" t="n">
-        <v>-54.14744186401367</v>
+        <v>-70.28801727294922</v>
       </c>
       <c r="T11" t="n">
-        <v>-54.42976760864258</v>
+        <v>-69.07244110107422</v>
       </c>
       <c r="U11" t="n">
-        <v>-52.95650482177734</v>
+        <v>-67.63325500488281</v>
       </c>
       <c r="V11" t="n">
-        <v>-55.82483673095703</v>
+        <v>-77.52460479736328</v>
       </c>
       <c r="W11" t="n">
-        <v>-54.35262298583984</v>
+        <v>-72.37155151367188</v>
       </c>
       <c r="X11" t="n">
-        <v>-55.69370269775391</v>
+        <v>-67.98761749267578</v>
       </c>
       <c r="Y11" t="n">
-        <v>-55.3239631652832</v>
+        <v>-76.34034729003906</v>
       </c>
       <c r="Z11" t="n">
-        <v>-56.95648956298828</v>
+        <v>-72.62679290771484</v>
       </c>
       <c r="AA11" t="n">
-        <v>-56.28501510620117</v>
+        <v>-78.50975799560547</v>
       </c>
       <c r="AB11" t="n">
-        <v>-57.09693145751953</v>
+        <v>-77.57418060302734</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-47.32057952880859</v>
+        <v>-60.5819091796875</v>
       </c>
       <c r="B12" t="n">
-        <v>-48.1151123046875</v>
+        <v>-59.75081253051758</v>
       </c>
       <c r="C12" t="n">
-        <v>-45.90510559082031</v>
+        <v>-65.18190765380859</v>
       </c>
       <c r="D12" t="n">
-        <v>-49.08084869384766</v>
+        <v>-60.92673492431641</v>
       </c>
       <c r="E12" t="n">
-        <v>-49.94729995727539</v>
+        <v>-56.57034301757812</v>
       </c>
       <c r="F12" t="n">
-        <v>-50.68285369873047</v>
+        <v>-64.231201171875</v>
       </c>
       <c r="G12" t="n">
-        <v>-50.95113372802734</v>
+        <v>-65.41545867919922</v>
       </c>
       <c r="H12" t="n">
-        <v>-52.38076782226562</v>
+        <v>-65.32072448730469</v>
       </c>
       <c r="I12" t="n">
-        <v>-47.47702026367188</v>
+        <v>-65.29581451416016</v>
       </c>
       <c r="J12" t="n">
-        <v>-48.8932991027832</v>
+        <v>-59.62632369995117</v>
       </c>
       <c r="K12" t="n">
-        <v>-48.71118545532227</v>
+        <v>-63.64745330810547</v>
       </c>
       <c r="L12" t="n">
-        <v>-51.22174072265625</v>
+        <v>-66.81346893310547</v>
       </c>
       <c r="M12" t="n">
-        <v>-49.00471878051758</v>
+        <v>-61.53045654296875</v>
       </c>
       <c r="N12" t="n">
-        <v>-52.05788040161133</v>
+        <v>-68.79829406738281</v>
       </c>
       <c r="O12" t="n">
-        <v>-51.26788330078125</v>
+        <v>-66.03692626953125</v>
       </c>
       <c r="P12" t="n">
-        <v>-51.9616813659668</v>
+        <v>-66.28581237792969</v>
       </c>
       <c r="Q12" t="n">
-        <v>-54.03864669799805</v>
+        <v>-71.20291900634766</v>
       </c>
       <c r="R12" t="n">
-        <v>-53.4595947265625</v>
+        <v>-72.65174865722656</v>
       </c>
       <c r="S12" t="n">
-        <v>-55.94376373291016</v>
+        <v>-65.07954406738281</v>
       </c>
       <c r="T12" t="n">
-        <v>-56.25168991088867</v>
+        <v>-71.67091369628906</v>
       </c>
       <c r="U12" t="n">
-        <v>-53.57329559326172</v>
+        <v>-75.44611358642578</v>
       </c>
       <c r="V12" t="n">
-        <v>-56.7467155456543</v>
+        <v>-71.52532196044922</v>
       </c>
       <c r="W12" t="n">
-        <v>-52.3035774230957</v>
+        <v>-74.06021881103516</v>
       </c>
       <c r="X12" t="n">
-        <v>-53.90332794189453</v>
+        <v>-70.15785980224609</v>
       </c>
       <c r="Y12" t="n">
-        <v>-54.30168533325195</v>
+        <v>-74.05391693115234</v>
       </c>
       <c r="Z12" t="n">
-        <v>-54.806884765625</v>
+        <v>-74.82475280761719</v>
       </c>
       <c r="AA12" t="n">
-        <v>-55.5299072265625</v>
+        <v>-69.72624206542969</v>
       </c>
       <c r="AB12" t="n">
-        <v>-57.26963043212891</v>
+        <v>-85.77940368652344</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-47.22951889038086</v>
+        <v>-66.10333251953125</v>
       </c>
       <c r="B13" t="n">
-        <v>-46.4117546081543</v>
+        <v>-65.132568359375</v>
       </c>
       <c r="C13" t="n">
-        <v>-44.74771499633789</v>
+        <v>-60.55240631103516</v>
       </c>
       <c r="D13" t="n">
-        <v>-48.97022247314453</v>
+        <v>-60.28391265869141</v>
       </c>
       <c r="E13" t="n">
-        <v>-49.82147216796875</v>
+        <v>-63.48889923095703</v>
       </c>
       <c r="F13" t="n">
-        <v>-46.24026107788086</v>
+        <v>-67.64989471435547</v>
       </c>
       <c r="G13" t="n">
-        <v>-48.67017364501953</v>
+        <v>-67.74240875244141</v>
       </c>
       <c r="H13" t="n">
-        <v>-52.14723587036133</v>
+        <v>-64.08216857910156</v>
       </c>
       <c r="I13" t="n">
-        <v>-50.37056350708008</v>
+        <v>-61.44413375854492</v>
       </c>
       <c r="J13" t="n">
-        <v>-52.03292083740234</v>
+        <v>-66.57853698730469</v>
       </c>
       <c r="K13" t="n">
-        <v>-48.5875358581543</v>
+        <v>-59.67586135864258</v>
       </c>
       <c r="L13" t="n">
-        <v>-49.95302581787109</v>
+        <v>-64.68779754638672</v>
       </c>
       <c r="M13" t="n">
-        <v>-50.90197372436523</v>
+        <v>-60.31438064575195</v>
       </c>
       <c r="N13" t="n">
-        <v>-54.14835739135742</v>
+        <v>-63.5710334777832</v>
       </c>
       <c r="O13" t="n">
-        <v>-52.00418090820312</v>
+        <v>-68.38706207275391</v>
       </c>
       <c r="P13" t="n">
-        <v>-47.94605255126953</v>
+        <v>-73.76930236816406</v>
       </c>
       <c r="Q13" t="n">
-        <v>-52.76544952392578</v>
+        <v>-67.16481781005859</v>
       </c>
       <c r="R13" t="n">
-        <v>-49.96628570556641</v>
+        <v>-67.60848236083984</v>
       </c>
       <c r="S13" t="n">
-        <v>-52.44472503662109</v>
+        <v>-68.75886535644531</v>
       </c>
       <c r="T13" t="n">
-        <v>-55.5615119934082</v>
+        <v>-74.66067504882812</v>
       </c>
       <c r="U13" t="n">
-        <v>-56.65592575073242</v>
+        <v>-76.5196533203125</v>
       </c>
       <c r="V13" t="n">
-        <v>-55.6765251159668</v>
+        <v>-69.67460632324219</v>
       </c>
       <c r="W13" t="n">
-        <v>-53.3101921081543</v>
+        <v>-69.29115295410156</v>
       </c>
       <c r="X13" t="n">
-        <v>-53.7601203918457</v>
+        <v>-71.65747833251953</v>
       </c>
       <c r="Y13" t="n">
-        <v>-55.26053619384766</v>
+        <v>-82.18756866455078</v>
       </c>
       <c r="Z13" t="n">
-        <v>-58.28661346435547</v>
+        <v>-75.29896545410156</v>
       </c>
       <c r="AA13" t="n">
-        <v>-57.93131637573242</v>
+        <v>-76.22628784179688</v>
       </c>
       <c r="AB13" t="n">
-        <v>-55.39469146728516</v>
+        <v>-73.98787689208984</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-47.49927520751953</v>
+        <v>-54.52248382568359</v>
       </c>
       <c r="B14" t="n">
-        <v>-45.82749557495117</v>
+        <v>-58.80188751220703</v>
       </c>
       <c r="C14" t="n">
-        <v>-50.25790405273438</v>
+        <v>-64.53090667724609</v>
       </c>
       <c r="D14" t="n">
-        <v>-50.47902297973633</v>
+        <v>-65.10008239746094</v>
       </c>
       <c r="E14" t="n">
-        <v>-49.31134033203125</v>
+        <v>-63.56110763549805</v>
       </c>
       <c r="F14" t="n">
-        <v>-49.67377471923828</v>
+        <v>-67.47025299072266</v>
       </c>
       <c r="G14" t="n">
-        <v>-51.81311798095703</v>
+        <v>-63.78549194335938</v>
       </c>
       <c r="H14" t="n">
-        <v>-51.02509689331055</v>
+        <v>-65.67814636230469</v>
       </c>
       <c r="I14" t="n">
-        <v>-54.84840774536133</v>
+        <v>-69.32896423339844</v>
       </c>
       <c r="J14" t="n">
-        <v>-51.90558624267578</v>
+        <v>-73.18755340576172</v>
       </c>
       <c r="K14" t="n">
-        <v>-49.55432510375977</v>
+        <v>-67.50411224365234</v>
       </c>
       <c r="L14" t="n">
-        <v>-53.67982864379883</v>
+        <v>-58.53595733642578</v>
       </c>
       <c r="M14" t="n">
-        <v>-50.16133880615234</v>
+        <v>-67.48514556884766</v>
       </c>
       <c r="N14" t="n">
-        <v>-49.76430892944336</v>
+        <v>-69.27976989746094</v>
       </c>
       <c r="O14" t="n">
-        <v>-53.96170806884766</v>
+        <v>-70.97752380371094</v>
       </c>
       <c r="P14" t="n">
-        <v>-54.1585807800293</v>
+        <v>-74.61062622070312</v>
       </c>
       <c r="Q14" t="n">
-        <v>-54.64727783203125</v>
+        <v>-75.02696228027344</v>
       </c>
       <c r="R14" t="n">
-        <v>-54.147705078125</v>
+        <v>-65.50127410888672</v>
       </c>
       <c r="S14" t="n">
-        <v>-52.84505462646484</v>
+        <v>-66.63320159912109</v>
       </c>
       <c r="T14" t="n">
-        <v>-51.99172210693359</v>
+        <v>-74.39483642578125</v>
       </c>
       <c r="U14" t="n">
-        <v>-53.20928955078125</v>
+        <v>-76.00064086914062</v>
       </c>
       <c r="V14" t="n">
-        <v>-55.54476165771484</v>
+        <v>-75.00688934326172</v>
       </c>
       <c r="W14" t="n">
-        <v>-50.70330047607422</v>
+        <v>-77.16098022460938</v>
       </c>
       <c r="X14" t="n">
-        <v>-53.22603607177734</v>
+        <v>-76.37614440917969</v>
       </c>
       <c r="Y14" t="n">
-        <v>-56.68585968017578</v>
+        <v>-78.99638366699219</v>
       </c>
       <c r="Z14" t="n">
-        <v>-58.62018585205078</v>
+        <v>-73.80770874023438</v>
       </c>
       <c r="AA14" t="n">
-        <v>-55.93502044677734</v>
+        <v>-73.95625305175781</v>
       </c>
       <c r="AB14" t="n">
-        <v>-55.12460327148438</v>
+        <v>-75.29637145996094</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-50.28752136230469</v>
+        <v>-62.79875564575195</v>
       </c>
       <c r="B15" t="n">
-        <v>-48.19797515869141</v>
+        <v>-62.30280685424805</v>
       </c>
       <c r="C15" t="n">
-        <v>-50.74509811401367</v>
+        <v>-60.66049957275391</v>
       </c>
       <c r="D15" t="n">
-        <v>-49.95989227294922</v>
+        <v>-61.54913330078125</v>
       </c>
       <c r="E15" t="n">
-        <v>-50.29404449462891</v>
+        <v>-63.65618896484375</v>
       </c>
       <c r="F15" t="n">
-        <v>-51.78090286254883</v>
+        <v>-57.12605667114258</v>
       </c>
       <c r="G15" t="n">
-        <v>-52.7792854309082</v>
+        <v>-72.72144317626953</v>
       </c>
       <c r="H15" t="n">
-        <v>-51.85343551635742</v>
+        <v>-61.99558639526367</v>
       </c>
       <c r="I15" t="n">
-        <v>-46.35147094726562</v>
+        <v>-68.49256896972656</v>
       </c>
       <c r="J15" t="n">
-        <v>-53.22740936279297</v>
+        <v>-67.61899566650391</v>
       </c>
       <c r="K15" t="n">
-        <v>-50.39856719970703</v>
+        <v>-65.04885101318359</v>
       </c>
       <c r="L15" t="n">
-        <v>-53.3067512512207</v>
+        <v>-68.93846130371094</v>
       </c>
       <c r="M15" t="n">
-        <v>-50.5528450012207</v>
+        <v>-65.11258697509766</v>
       </c>
       <c r="N15" t="n">
-        <v>-54.63793182373047</v>
+        <v>-66.74104309082031</v>
       </c>
       <c r="O15" t="n">
-        <v>-51.31819534301758</v>
+        <v>-75.58149719238281</v>
       </c>
       <c r="P15" t="n">
-        <v>-64.55559539794922</v>
+        <v>-78.36625671386719</v>
       </c>
       <c r="Q15" t="n">
-        <v>-68.69786071777344</v>
+        <v>-76.46271514892578</v>
       </c>
       <c r="R15" t="n">
-        <v>-64.40249633789062</v>
+        <v>-73.13027191162109</v>
       </c>
       <c r="S15" t="n">
-        <v>-68.73667907714844</v>
+        <v>-69.25746917724609</v>
       </c>
       <c r="T15" t="n">
-        <v>-64.65493011474609</v>
+        <v>-78.64080810546875</v>
       </c>
       <c r="U15" t="n">
-        <v>-66.87474060058594</v>
+        <v>-71.73487854003906</v>
       </c>
       <c r="V15" t="n">
-        <v>-66.82463073730469</v>
+        <v>-72.58130645751953</v>
       </c>
       <c r="W15" t="n">
-        <v>-71.66188049316406</v>
+        <v>-74.39270782470703</v>
       </c>
       <c r="X15" t="n">
-        <v>-70.35524749755859</v>
+        <v>-71.67909240722656</v>
       </c>
       <c r="Y15" t="n">
-        <v>-69.22618103027344</v>
+        <v>-73.18355560302734</v>
       </c>
       <c r="Z15" t="n">
-        <v>-69.90742492675781</v>
+        <v>-76.16712188720703</v>
       </c>
       <c r="AA15" t="n">
-        <v>-69.34880828857422</v>
+        <v>-74.42573547363281</v>
       </c>
       <c r="AB15" t="n">
-        <v>-71.47173309326172</v>
+        <v>-80.55986022949219</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-47.89324188232422</v>
+        <v>-72.00758361816406</v>
       </c>
       <c r="B16" t="n">
-        <v>-48.77280426025391</v>
+        <v>-60.17617797851562</v>
       </c>
       <c r="C16" t="n">
-        <v>-47.33703994750977</v>
+        <v>-70.04421234130859</v>
       </c>
       <c r="D16" t="n">
-        <v>-48.29613494873047</v>
+        <v>-69.25435638427734</v>
       </c>
       <c r="E16" t="n">
-        <v>-49.33088302612305</v>
+        <v>-63.2730827331543</v>
       </c>
       <c r="F16" t="n">
-        <v>-50.8424186706543</v>
+        <v>-63.0435676574707</v>
       </c>
       <c r="G16" t="n">
-        <v>-51.62396240234375</v>
+        <v>-66.91072845458984</v>
       </c>
       <c r="H16" t="n">
-        <v>-55.71799850463867</v>
+        <v>-72.24715423583984</v>
       </c>
       <c r="I16" t="n">
-        <v>-52.55010223388672</v>
+        <v>-66.65049743652344</v>
       </c>
       <c r="J16" t="n">
-        <v>-51.89943695068359</v>
+        <v>-68.80075836181641</v>
       </c>
       <c r="K16" t="n">
-        <v>-51.68509674072266</v>
+        <v>-74.02100372314453</v>
       </c>
       <c r="L16" t="n">
-        <v>-52.66959381103516</v>
+        <v>-68.44707489013672</v>
       </c>
       <c r="M16" t="n">
-        <v>-56.301025390625</v>
+        <v>-69.06774139404297</v>
       </c>
       <c r="N16" t="n">
-        <v>-55.11457061767578</v>
+        <v>-70.98493957519531</v>
       </c>
       <c r="O16" t="n">
-        <v>-53.9765510559082</v>
+        <v>-75.32363891601562</v>
       </c>
       <c r="P16" t="n">
-        <v>-51.9483642578125</v>
+        <v>-83.80572509765625</v>
       </c>
       <c r="Q16" t="n">
-        <v>-67.92775726318359</v>
+        <v>-75.67152404785156</v>
       </c>
       <c r="R16" t="n">
-        <v>-66.52024841308594</v>
+        <v>-74.83447265625</v>
       </c>
       <c r="S16" t="n">
-        <v>-69.79842376708984</v>
+        <v>-74.71366882324219</v>
       </c>
       <c r="T16" t="n">
-        <v>-70.58229064941406</v>
+        <v>-70.07478332519531</v>
       </c>
       <c r="U16" t="n">
-        <v>-66.39036560058594</v>
+        <v>-77.15499877929688</v>
       </c>
       <c r="V16" t="n">
-        <v>-70.05596160888672</v>
+        <v>-72.09336853027344</v>
       </c>
       <c r="W16" t="n">
-        <v>-68.60011291503906</v>
+        <v>-75.51203155517578</v>
       </c>
       <c r="X16" t="n">
-        <v>-69.43851470947266</v>
+        <v>-76.56692504882812</v>
       </c>
       <c r="Y16" t="n">
-        <v>-67.20568084716797</v>
+        <v>-80.41970062255859</v>
       </c>
       <c r="Z16" t="n">
-        <v>-67.77571868896484</v>
+        <v>-81.08265686035156</v>
       </c>
       <c r="AA16" t="n">
-        <v>-71.20092010498047</v>
+        <v>-72.39835357666016</v>
       </c>
       <c r="AB16" t="n">
-        <v>-68.03513336181641</v>
+        <v>-76.18902587890625</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-48.64846038818359</v>
+        <v>-66.08208465576172</v>
       </c>
       <c r="B17" t="n">
-        <v>-46.66537094116211</v>
+        <v>-67.19593811035156</v>
       </c>
       <c r="C17" t="n">
-        <v>-48.49109649658203</v>
+        <v>-66.69944000244141</v>
       </c>
       <c r="D17" t="n">
-        <v>-49.96242904663086</v>
+        <v>-69.75330352783203</v>
       </c>
       <c r="E17" t="n">
-        <v>-51.98567962646484</v>
+        <v>-64.92133331298828</v>
       </c>
       <c r="F17" t="n">
-        <v>-50.91937637329102</v>
+        <v>-72.8037109375</v>
       </c>
       <c r="G17" t="n">
-        <v>-54.87287521362305</v>
+        <v>-69.7442626953125</v>
       </c>
       <c r="H17" t="n">
-        <v>-49.38460540771484</v>
+        <v>-67.11502838134766</v>
       </c>
       <c r="I17" t="n">
-        <v>-50.48985290527344</v>
+        <v>-71.09755706787109</v>
       </c>
       <c r="J17" t="n">
-        <v>-51.86396408081055</v>
+        <v>-74.00000762939453</v>
       </c>
       <c r="K17" t="n">
-        <v>-52.21939086914062</v>
+        <v>-69.71230316162109</v>
       </c>
       <c r="L17" t="n">
-        <v>-51.35604095458984</v>
+        <v>-73.02872467041016</v>
       </c>
       <c r="M17" t="n">
-        <v>-53.53836822509766</v>
+        <v>-72.77823638916016</v>
       </c>
       <c r="N17" t="n">
-        <v>-50.91620635986328</v>
+        <v>-72.52186584472656</v>
       </c>
       <c r="O17" t="n">
-        <v>-54.85881423950195</v>
+        <v>-69.93449401855469</v>
       </c>
       <c r="P17" t="n">
-        <v>-53.30976104736328</v>
+        <v>-74.63346862792969</v>
       </c>
       <c r="Q17" t="n">
-        <v>-57.02696990966797</v>
+        <v>-70.41405487060547</v>
       </c>
       <c r="R17" t="n">
-        <v>-65.77300262451172</v>
+        <v>-74.89646911621094</v>
       </c>
       <c r="S17" t="n">
-        <v>-65.89887237548828</v>
+        <v>-78.45729064941406</v>
       </c>
       <c r="T17" t="n">
-        <v>-70.76648712158203</v>
+        <v>-73.927734375</v>
       </c>
       <c r="U17" t="n">
-        <v>-67.61903381347656</v>
+        <v>-75.72846984863281</v>
       </c>
       <c r="V17" t="n">
-        <v>-69.65459442138672</v>
+        <v>-71.47807312011719</v>
       </c>
       <c r="W17" t="n">
-        <v>-70.40023803710938</v>
+        <v>-69.77063751220703</v>
       </c>
       <c r="X17" t="n">
-        <v>-67.80451965332031</v>
+        <v>-74.66117095947266</v>
       </c>
       <c r="Y17" t="n">
-        <v>-68.13453674316406</v>
+        <v>-78.35383605957031</v>
       </c>
       <c r="Z17" t="n">
-        <v>-71.50521087646484</v>
+        <v>-77.08119964599609</v>
       </c>
       <c r="AA17" t="n">
-        <v>-70.48492431640625</v>
+        <v>-77.66966247558594</v>
       </c>
       <c r="AB17" t="n">
-        <v>-71.12799072265625</v>
+        <v>-81.12178039550781</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-50.22522354125977</v>
+        <v>-65.31311798095703</v>
       </c>
       <c r="B18" t="n">
-        <v>-52.39974212646484</v>
+        <v>-63.76861572265625</v>
       </c>
       <c r="C18" t="n">
-        <v>-51.24489593505859</v>
+        <v>-63.66838455200195</v>
       </c>
       <c r="D18" t="n">
-        <v>-50.8704719543457</v>
+        <v>-72.85564422607422</v>
       </c>
       <c r="E18" t="n">
-        <v>-48.74613571166992</v>
+        <v>-72.21717071533203</v>
       </c>
       <c r="F18" t="n">
-        <v>-52.0855598449707</v>
+        <v>-66.15780639648438</v>
       </c>
       <c r="G18" t="n">
-        <v>-52.33549880981445</v>
+        <v>-76.66163635253906</v>
       </c>
       <c r="H18" t="n">
-        <v>-51.09739303588867</v>
+        <v>-67.28065490722656</v>
       </c>
       <c r="I18" t="n">
-        <v>-53.92757034301758</v>
+        <v>-74.11048126220703</v>
       </c>
       <c r="J18" t="n">
-        <v>-53.32944488525391</v>
+        <v>-69.05361175537109</v>
       </c>
       <c r="K18" t="n">
-        <v>-54.2873420715332</v>
+        <v>-70.09110260009766</v>
       </c>
       <c r="L18" t="n">
-        <v>-54.10322189331055</v>
+        <v>-72.82231140136719</v>
       </c>
       <c r="M18" t="n">
-        <v>-54.9906005859375</v>
+        <v>-76.77479553222656</v>
       </c>
       <c r="N18" t="n">
-        <v>-52.40690994262695</v>
+        <v>-74.06636047363281</v>
       </c>
       <c r="O18" t="n">
-        <v>-56.05599975585938</v>
+        <v>-72.00963592529297</v>
       </c>
       <c r="P18" t="n">
-        <v>-56.90422439575195</v>
+        <v>-75.54925537109375</v>
       </c>
       <c r="Q18" t="n">
-        <v>-53.20668792724609</v>
+        <v>-82.24881744384766</v>
       </c>
       <c r="R18" t="n">
-        <v>-53.0686149597168</v>
+        <v>-78.31232452392578</v>
       </c>
       <c r="S18" t="n">
-        <v>-69.54255676269531</v>
+        <v>-78.80725860595703</v>
       </c>
       <c r="T18" t="n">
-        <v>-67.00211334228516</v>
+        <v>-76.83089447021484</v>
       </c>
       <c r="U18" t="n">
-        <v>-68.93470001220703</v>
+        <v>-77.12928771972656</v>
       </c>
       <c r="V18" t="n">
-        <v>-72.82270812988281</v>
+        <v>-74.93341827392578</v>
       </c>
       <c r="W18" t="n">
-        <v>-72.58129119873047</v>
+        <v>-78.90205383300781</v>
       </c>
       <c r="X18" t="n">
-        <v>-68.9930419921875</v>
+        <v>-81.85106658935547</v>
       </c>
       <c r="Y18" t="n">
-        <v>-74.2125244140625</v>
+        <v>-79.16104888916016</v>
       </c>
       <c r="Z18" t="n">
-        <v>-71.84358215332031</v>
+        <v>-81.13334655761719</v>
       </c>
       <c r="AA18" t="n">
-        <v>-73.88484191894531</v>
+        <v>-74.83647155761719</v>
       </c>
       <c r="AB18" t="n">
-        <v>-69.86763000488281</v>
+        <v>-79.18666839599609</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-51.8220100402832</v>
+        <v>-66.79032897949219</v>
       </c>
       <c r="B19" t="n">
-        <v>-54.0688591003418</v>
+        <v>-64.10696411132812</v>
       </c>
       <c r="C19" t="n">
-        <v>-53.62754440307617</v>
+        <v>-64.89328002929688</v>
       </c>
       <c r="D19" t="n">
-        <v>-51.00857543945312</v>
+        <v>-68.12860870361328</v>
       </c>
       <c r="E19" t="n">
-        <v>-52.21724319458008</v>
+        <v>-67.15984344482422</v>
       </c>
       <c r="F19" t="n">
-        <v>-51.45005416870117</v>
+        <v>-61.35178756713867</v>
       </c>
       <c r="G19" t="n">
-        <v>-53.64345550537109</v>
+        <v>-72.44985961914062</v>
       </c>
       <c r="H19" t="n">
-        <v>-51.31417846679688</v>
+        <v>-77.168212890625</v>
       </c>
       <c r="I19" t="n">
-        <v>-54.69671630859375</v>
+        <v>-71.77815246582031</v>
       </c>
       <c r="J19" t="n">
-        <v>-55.79241943359375</v>
+        <v>-75.22441101074219</v>
       </c>
       <c r="K19" t="n">
-        <v>-49.70817947387695</v>
+        <v>-74.97821044921875</v>
       </c>
       <c r="L19" t="n">
-        <v>-53.22660446166992</v>
+        <v>-65.95177459716797</v>
       </c>
       <c r="M19" t="n">
-        <v>-54.73433303833008</v>
+        <v>-67.24836730957031</v>
       </c>
       <c r="N19" t="n">
-        <v>-53.19573974609375</v>
+        <v>-71.23987579345703</v>
       </c>
       <c r="O19" t="n">
-        <v>-53.80254364013672</v>
+        <v>-74.91899871826172</v>
       </c>
       <c r="P19" t="n">
-        <v>-56.6111946105957</v>
+        <v>-77.96307373046875</v>
       </c>
       <c r="Q19" t="n">
-        <v>-53.1603889465332</v>
+        <v>-77.86849212646484</v>
       </c>
       <c r="R19" t="n">
-        <v>-54.00318145751953</v>
+        <v>-69.42820739746094</v>
       </c>
       <c r="S19" t="n">
-        <v>-52.40974044799805</v>
+        <v>-76.13294982910156</v>
       </c>
       <c r="T19" t="n">
-        <v>-67.6348876953125</v>
+        <v>-76.82802581787109</v>
       </c>
       <c r="U19" t="n">
-        <v>-69.45948791503906</v>
+        <v>-66.33017730712891</v>
       </c>
       <c r="V19" t="n">
-        <v>-71.43819427490234</v>
+        <v>-76.88592529296875</v>
       </c>
       <c r="W19" t="n">
-        <v>-70.95841979980469</v>
+        <v>-76.68323516845703</v>
       </c>
       <c r="X19" t="n">
-        <v>-68.02742767333984</v>
+        <v>-70.59374237060547</v>
       </c>
       <c r="Y19" t="n">
-        <v>-70.29704284667969</v>
+        <v>-74.78986358642578</v>
       </c>
       <c r="Z19" t="n">
-        <v>-70.28620910644531</v>
+        <v>-79.62689208984375</v>
       </c>
       <c r="AA19" t="n">
-        <v>-75.09870910644531</v>
+        <v>-76.61350250244141</v>
       </c>
       <c r="AB19" t="n">
-        <v>-72.26210784912109</v>
+        <v>-74.13700103759766</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-51.86007690429688</v>
+        <v>-69.19445037841797</v>
       </c>
       <c r="B20" t="n">
-        <v>-50.71985244750977</v>
+        <v>-70.09120178222656</v>
       </c>
       <c r="C20" t="n">
-        <v>-52.65346145629883</v>
+        <v>-70.62313842773438</v>
       </c>
       <c r="D20" t="n">
-        <v>-51.3021125793457</v>
+        <v>-71.14609527587891</v>
       </c>
       <c r="E20" t="n">
-        <v>-52.71793746948242</v>
+        <v>-71.61843109130859</v>
       </c>
       <c r="F20" t="n">
-        <v>-51.7596435546875</v>
+        <v>-74.25933837890625</v>
       </c>
       <c r="G20" t="n">
-        <v>-54.6197395324707</v>
+        <v>-72.73231506347656</v>
       </c>
       <c r="H20" t="n">
-        <v>-52.5129280090332</v>
+        <v>-75.89063262939453</v>
       </c>
       <c r="I20" t="n">
-        <v>-49.82367324829102</v>
+        <v>-65.45096588134766</v>
       </c>
       <c r="J20" t="n">
-        <v>-52.21096038818359</v>
+        <v>-74.48847198486328</v>
       </c>
       <c r="K20" t="n">
-        <v>-52.77191162109375</v>
+        <v>-72.78018951416016</v>
       </c>
       <c r="L20" t="n">
-        <v>-55.56705856323242</v>
+        <v>-67.39141082763672</v>
       </c>
       <c r="M20" t="n">
-        <v>-51.00131988525391</v>
+        <v>-78.24031066894531</v>
       </c>
       <c r="N20" t="n">
-        <v>-57.55972290039062</v>
+        <v>-76.14033508300781</v>
       </c>
       <c r="O20" t="n">
-        <v>-55.5323600769043</v>
+        <v>-72.00341033935547</v>
       </c>
       <c r="P20" t="n">
-        <v>-54.222412109375</v>
+        <v>-75.53842926025391</v>
       </c>
       <c r="Q20" t="n">
-        <v>-56.64765167236328</v>
+        <v>-76.47935485839844</v>
       </c>
       <c r="R20" t="n">
-        <v>-56.49523162841797</v>
+        <v>-74.31663513183594</v>
       </c>
       <c r="S20" t="n">
-        <v>-55.24657440185547</v>
+        <v>-75.87551879882812</v>
       </c>
       <c r="T20" t="n">
-        <v>-56.3955192565918</v>
+        <v>-78.19466400146484</v>
       </c>
       <c r="U20" t="n">
-        <v>-72.59904479980469</v>
+        <v>-83.08384704589844</v>
       </c>
       <c r="V20" t="n">
-        <v>-68.02433776855469</v>
+        <v>-74.71315002441406</v>
       </c>
       <c r="W20" t="n">
-        <v>-68.01971435546875</v>
+        <v>-79.04471588134766</v>
       </c>
       <c r="X20" t="n">
-        <v>-71.76333618164062</v>
+        <v>-77.32603454589844</v>
       </c>
       <c r="Y20" t="n">
-        <v>-72.33756256103516</v>
+        <v>-82.80864715576172</v>
       </c>
       <c r="Z20" t="n">
-        <v>-71.67333984375</v>
+        <v>-81.03205871582031</v>
       </c>
       <c r="AA20" t="n">
-        <v>-69.76461029052734</v>
+        <v>-82.28289794921875</v>
       </c>
       <c r="AB20" t="n">
-        <v>-70.05943298339844</v>
+        <v>-74.00713348388672</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-52.76316452026367</v>
+        <v>-62.12210083007812</v>
       </c>
       <c r="B21" t="n">
-        <v>-52.73208618164062</v>
+        <v>-70.75299072265625</v>
       </c>
       <c r="C21" t="n">
-        <v>-49.40773773193359</v>
+        <v>-70.84905242919922</v>
       </c>
       <c r="D21" t="n">
-        <v>-52.82772064208984</v>
+        <v>-66.77519989013672</v>
       </c>
       <c r="E21" t="n">
-        <v>-52.23093795776367</v>
+        <v>-66.59580993652344</v>
       </c>
       <c r="F21" t="n">
-        <v>-49.32870483398438</v>
+        <v>-69.680419921875</v>
       </c>
       <c r="G21" t="n">
-        <v>-53.15692901611328</v>
+        <v>-68.89514923095703</v>
       </c>
       <c r="H21" t="n">
-        <v>-52.86566925048828</v>
+        <v>-69.98235321044922</v>
       </c>
       <c r="I21" t="n">
-        <v>-51.0093994140625</v>
+        <v>-75.34113311767578</v>
       </c>
       <c r="J21" t="n">
-        <v>-55.31232833862305</v>
+        <v>-72.14625549316406</v>
       </c>
       <c r="K21" t="n">
-        <v>-52.95493316650391</v>
+        <v>-62.98165893554688</v>
       </c>
       <c r="L21" t="n">
-        <v>-52.73116302490234</v>
+        <v>-73.54247283935547</v>
       </c>
       <c r="M21" t="n">
-        <v>-53.58528900146484</v>
+        <v>-76.55788421630859</v>
       </c>
       <c r="N21" t="n">
-        <v>-52.65914154052734</v>
+        <v>-74.85842895507812</v>
       </c>
       <c r="O21" t="n">
-        <v>-51.91030120849609</v>
+        <v>-79.01158905029297</v>
       </c>
       <c r="P21" t="n">
-        <v>-57.43411254882812</v>
+        <v>-77.89040374755859</v>
       </c>
       <c r="Q21" t="n">
-        <v>-52.95670318603516</v>
+        <v>-74.71357727050781</v>
       </c>
       <c r="R21" t="n">
-        <v>-55.65864181518555</v>
+        <v>-76.53818511962891</v>
       </c>
       <c r="S21" t="n">
-        <v>-54.75880813598633</v>
+        <v>-77.53732299804688</v>
       </c>
       <c r="T21" t="n">
-        <v>-56.77223968505859</v>
+        <v>-76.53264617919922</v>
       </c>
       <c r="U21" t="n">
-        <v>-55.72560882568359</v>
+        <v>-78.10859680175781</v>
       </c>
       <c r="V21" t="n">
-        <v>-70.88741302490234</v>
+        <v>-78.47980499267578</v>
       </c>
       <c r="W21" t="n">
-        <v>-68.90652465820312</v>
+        <v>-75.82328796386719</v>
       </c>
       <c r="X21" t="n">
-        <v>-69.91450500488281</v>
+        <v>-81.03277587890625</v>
       </c>
       <c r="Y21" t="n">
-        <v>-72.42574310302734</v>
+        <v>-82.76222229003906</v>
       </c>
       <c r="Z21" t="n">
-        <v>-69.37944030761719</v>
+        <v>-82.00117492675781</v>
       </c>
       <c r="AA21" t="n">
-        <v>-70.20404052734375</v>
+        <v>-75.52079772949219</v>
       </c>
       <c r="AB21" t="n">
-        <v>-67.81252288818359</v>
+        <v>-76.73686218261719</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-51.86664962768555</v>
+        <v>-69.25755310058594</v>
       </c>
       <c r="B22" t="n">
-        <v>-52.3482666015625</v>
+        <v>-69.69868469238281</v>
       </c>
       <c r="C22" t="n">
-        <v>-51.4198112487793</v>
+        <v>-65.98226928710938</v>
       </c>
       <c r="D22" t="n">
-        <v>-50.91972351074219</v>
+        <v>-69.40221405029297</v>
       </c>
       <c r="E22" t="n">
-        <v>-50.85391616821289</v>
+        <v>-68.28675842285156</v>
       </c>
       <c r="F22" t="n">
-        <v>-54.93390655517578</v>
+        <v>-71.6517333984375</v>
       </c>
       <c r="G22" t="n">
-        <v>-51.68154144287109</v>
+        <v>-72.18568420410156</v>
       </c>
       <c r="H22" t="n">
-        <v>-48.83151626586914</v>
+        <v>-71.74990844726562</v>
       </c>
       <c r="I22" t="n">
-        <v>-55.34709548950195</v>
+        <v>-77.23043060302734</v>
       </c>
       <c r="J22" t="n">
-        <v>-54.06611251831055</v>
+        <v>-69.07435607910156</v>
       </c>
       <c r="K22" t="n">
-        <v>-53.40439605712891</v>
+        <v>-71.66962432861328</v>
       </c>
       <c r="L22" t="n">
-        <v>-54.25374221801758</v>
+        <v>-74.93039703369141</v>
       </c>
       <c r="M22" t="n">
-        <v>-53.3216667175293</v>
+        <v>-72.94279479980469</v>
       </c>
       <c r="N22" t="n">
-        <v>-54.32076263427734</v>
+        <v>-81.60781097412109</v>
       </c>
       <c r="O22" t="n">
-        <v>-57.45117950439453</v>
+        <v>-79.35658264160156</v>
       </c>
       <c r="P22" t="n">
-        <v>-55.34222412109375</v>
+        <v>-74.35593414306641</v>
       </c>
       <c r="Q22" t="n">
-        <v>-57.0357666015625</v>
+        <v>-77.92617034912109</v>
       </c>
       <c r="R22" t="n">
-        <v>-54.44559478759766</v>
+        <v>-82.39788055419922</v>
       </c>
       <c r="S22" t="n">
-        <v>-56.39290618896484</v>
+        <v>-77.13516998291016</v>
       </c>
       <c r="T22" t="n">
-        <v>-55.75325775146484</v>
+        <v>-77.62151336669922</v>
       </c>
       <c r="U22" t="n">
-        <v>-57.2446403503418</v>
+        <v>-76.65674591064453</v>
       </c>
       <c r="V22" t="n">
-        <v>-57.35049438476562</v>
+        <v>-78.96795654296875</v>
       </c>
       <c r="W22" t="n">
-        <v>-72.70272064208984</v>
+        <v>-77.46343231201172</v>
       </c>
       <c r="X22" t="n">
-        <v>-72.92958068847656</v>
+        <v>-80.07427215576172</v>
       </c>
       <c r="Y22" t="n">
-        <v>-69.69307708740234</v>
+        <v>-77.30654144287109</v>
       </c>
       <c r="Z22" t="n">
-        <v>-69.01883697509766</v>
+        <v>-78.35537719726562</v>
       </c>
       <c r="AA22" t="n">
-        <v>-68.63764953613281</v>
+        <v>-78.97698211669922</v>
       </c>
       <c r="AB22" t="n">
-        <v>-73.05783843994141</v>
+        <v>-79.28042602539062</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-54.61175537109375</v>
+        <v>-70.67171478271484</v>
       </c>
       <c r="B23" t="n">
-        <v>-51.81267166137695</v>
+        <v>-67.84590911865234</v>
       </c>
       <c r="C23" t="n">
-        <v>-52.98918533325195</v>
+        <v>-66.41709136962891</v>
       </c>
       <c r="D23" t="n">
-        <v>-55.14949798583984</v>
+        <v>-77.64425659179688</v>
       </c>
       <c r="E23" t="n">
-        <v>-53.17409133911133</v>
+        <v>-74.07557678222656</v>
       </c>
       <c r="F23" t="n">
-        <v>-53.35282135009766</v>
+        <v>-69.33448791503906</v>
       </c>
       <c r="G23" t="n">
-        <v>-51.93437576293945</v>
+        <v>-78.68180084228516</v>
       </c>
       <c r="H23" t="n">
-        <v>-55.8218879699707</v>
+        <v>-78.31709289550781</v>
       </c>
       <c r="I23" t="n">
-        <v>-56.22738647460938</v>
+        <v>-68.78312683105469</v>
       </c>
       <c r="J23" t="n">
-        <v>-56.48784255981445</v>
+        <v>-79.84613800048828</v>
       </c>
       <c r="K23" t="n">
-        <v>-55.13801956176758</v>
+        <v>-75.21992492675781</v>
       </c>
       <c r="L23" t="n">
-        <v>-55.8057746887207</v>
+        <v>-72.95304870605469</v>
       </c>
       <c r="M23" t="n">
-        <v>-55.57235717773438</v>
+        <v>-78.92469787597656</v>
       </c>
       <c r="N23" t="n">
-        <v>-59.55754852294922</v>
+        <v>-78.29002380371094</v>
       </c>
       <c r="O23" t="n">
-        <v>-57.44136810302734</v>
+        <v>-74.52008056640625</v>
       </c>
       <c r="P23" t="n">
-        <v>-57.64064407348633</v>
+        <v>-74.10645294189453</v>
       </c>
       <c r="Q23" t="n">
-        <v>-55.66021728515625</v>
+        <v>-77.37165832519531</v>
       </c>
       <c r="R23" t="n">
-        <v>-57.94157791137695</v>
+        <v>-74.47071838378906</v>
       </c>
       <c r="S23" t="n">
-        <v>-55.06809234619141</v>
+        <v>-77.70725250244141</v>
       </c>
       <c r="T23" t="n">
-        <v>-57.89089965820312</v>
+        <v>-80.22353363037109</v>
       </c>
       <c r="U23" t="n">
-        <v>-57.5999641418457</v>
+        <v>-82.47676086425781</v>
       </c>
       <c r="V23" t="n">
-        <v>-55.96894073486328</v>
+        <v>-77.35444641113281</v>
       </c>
       <c r="W23" t="n">
-        <v>-54.72615814208984</v>
+        <v>-81.31758117675781</v>
       </c>
       <c r="X23" t="n">
-        <v>-70.33320617675781</v>
+        <v>-83.15696716308594</v>
       </c>
       <c r="Y23" t="n">
-        <v>-68.95033264160156</v>
+        <v>-78.31001281738281</v>
       </c>
       <c r="Z23" t="n">
-        <v>-69.90549468994141</v>
+        <v>-75.73466491699219</v>
       </c>
       <c r="AA23" t="n">
-        <v>-70.53894805908203</v>
+        <v>-80.08025360107422</v>
       </c>
       <c r="AB23" t="n">
-        <v>-69.39640808105469</v>
+        <v>-76.63936614990234</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-52.19430541992188</v>
+        <v>-72.28975677490234</v>
       </c>
       <c r="B24" t="n">
-        <v>-51.96906661987305</v>
+        <v>-73.87991333007812</v>
       </c>
       <c r="C24" t="n">
-        <v>-53.11777877807617</v>
+        <v>-73.07069396972656</v>
       </c>
       <c r="D24" t="n">
-        <v>-54.74143218994141</v>
+        <v>-68.76240539550781</v>
       </c>
       <c r="E24" t="n">
-        <v>-53.1979866027832</v>
+        <v>-69.83753204345703</v>
       </c>
       <c r="F24" t="n">
-        <v>-52.34109497070312</v>
+        <v>-63.77170562744141</v>
       </c>
       <c r="G24" t="n">
-        <v>-53.9310302734375</v>
+        <v>-72.21454620361328</v>
       </c>
       <c r="H24" t="n">
-        <v>-54.16803741455078</v>
+        <v>-67.45508575439453</v>
       </c>
       <c r="I24" t="n">
-        <v>-51.66147613525391</v>
+        <v>-71.37427520751953</v>
       </c>
       <c r="J24" t="n">
-        <v>-55.41135787963867</v>
+        <v>-70.49241638183594</v>
       </c>
       <c r="K24" t="n">
-        <v>-55.0040283203125</v>
+        <v>-74.87916564941406</v>
       </c>
       <c r="L24" t="n">
-        <v>-56.24602127075195</v>
+        <v>-71.18752288818359</v>
       </c>
       <c r="M24" t="n">
-        <v>-53.08217620849609</v>
+        <v>-74.05867767333984</v>
       </c>
       <c r="N24" t="n">
-        <v>-56.71810913085938</v>
+        <v>-78.70590972900391</v>
       </c>
       <c r="O24" t="n">
-        <v>-56.64687347412109</v>
+        <v>-74.71211242675781</v>
       </c>
       <c r="P24" t="n">
-        <v>-55.54531860351562</v>
+        <v>-78.48338317871094</v>
       </c>
       <c r="Q24" t="n">
-        <v>-55.42816925048828</v>
+        <v>-74.11367034912109</v>
       </c>
       <c r="R24" t="n">
-        <v>-55.80179595947266</v>
+        <v>-73.11134338378906</v>
       </c>
       <c r="S24" t="n">
-        <v>-57.04141235351562</v>
+        <v>-76.99702453613281</v>
       </c>
       <c r="T24" t="n">
-        <v>-57.05416870117188</v>
+        <v>-81.18013000488281</v>
       </c>
       <c r="U24" t="n">
-        <v>-54.4736213684082</v>
+        <v>-83.44010925292969</v>
       </c>
       <c r="V24" t="n">
-        <v>-56.85734176635742</v>
+        <v>-78.78141021728516</v>
       </c>
       <c r="W24" t="n">
-        <v>-55.1370735168457</v>
+        <v>-80.16419982910156</v>
       </c>
       <c r="X24" t="n">
-        <v>-57.75749588012695</v>
+        <v>-80.34409332275391</v>
       </c>
       <c r="Y24" t="n">
-        <v>-69.50279998779297</v>
+        <v>-79.87696838378906</v>
       </c>
       <c r="Z24" t="n">
-        <v>-75.34295654296875</v>
+        <v>-81.11655426025391</v>
       </c>
       <c r="AA24" t="n">
-        <v>-73.65448760986328</v>
+        <v>-73.86280822753906</v>
       </c>
       <c r="AB24" t="n">
-        <v>-70.92965698242188</v>
+        <v>-81.25486755371094</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-48.77504730224609</v>
+        <v>-76.96535491943359</v>
       </c>
       <c r="B25" t="n">
-        <v>-53.398681640625</v>
+        <v>-73.96211242675781</v>
       </c>
       <c r="C25" t="n">
-        <v>-54.9883918762207</v>
+        <v>-81.66281890869141</v>
       </c>
       <c r="D25" t="n">
-        <v>-55.47389984130859</v>
+        <v>-75.10211944580078</v>
       </c>
       <c r="E25" t="n">
-        <v>-50.65058135986328</v>
+        <v>-77.15845489501953</v>
       </c>
       <c r="F25" t="n">
-        <v>-50.44338226318359</v>
+        <v>-75.3392333984375</v>
       </c>
       <c r="G25" t="n">
-        <v>-53.81319046020508</v>
+        <v>-68.05390167236328</v>
       </c>
       <c r="H25" t="n">
-        <v>-57.38076019287109</v>
+        <v>-73.54861450195312</v>
       </c>
       <c r="I25" t="n">
-        <v>-53.24556350708008</v>
+        <v>-69.27752685546875</v>
       </c>
       <c r="J25" t="n">
-        <v>-53.29892730712891</v>
+        <v>-70.64653015136719</v>
       </c>
       <c r="K25" t="n">
-        <v>-56.98215866088867</v>
+        <v>-71.29738616943359</v>
       </c>
       <c r="L25" t="n">
-        <v>-55.66206741333008</v>
+        <v>-74.25828552246094</v>
       </c>
       <c r="M25" t="n">
-        <v>-54.9296875</v>
+        <v>-71.589599609375</v>
       </c>
       <c r="N25" t="n">
-        <v>-56.30830764770508</v>
+        <v>-71.18199157714844</v>
       </c>
       <c r="O25" t="n">
-        <v>-57.09574127197266</v>
+        <v>-82.20220947265625</v>
       </c>
       <c r="P25" t="n">
-        <v>-54.82368850708008</v>
+        <v>-80.72805023193359</v>
       </c>
       <c r="Q25" t="n">
-        <v>-58.25018310546875</v>
+        <v>-77.22388458251953</v>
       </c>
       <c r="R25" t="n">
-        <v>-55.84614181518555</v>
+        <v>-81.35929107666016</v>
       </c>
       <c r="S25" t="n">
-        <v>-56.07160186767578</v>
+        <v>-78.64192199707031</v>
       </c>
       <c r="T25" t="n">
-        <v>-50.93399429321289</v>
+        <v>-80.66094970703125</v>
       </c>
       <c r="U25" t="n">
-        <v>-57.90365600585938</v>
+        <v>-87.48114013671875</v>
       </c>
       <c r="V25" t="n">
-        <v>-60.25502395629883</v>
+        <v>-80.90873718261719</v>
       </c>
       <c r="W25" t="n">
-        <v>-60.11211395263672</v>
+        <v>-82.14198303222656</v>
       </c>
       <c r="X25" t="n">
-        <v>-56.45001220703125</v>
+        <v>-80.822998046875</v>
       </c>
       <c r="Y25" t="n">
-        <v>-58.03369140625</v>
+        <v>-79.74330902099609</v>
       </c>
       <c r="Z25" t="n">
-        <v>-70.56272888183594</v>
+        <v>-87.62091827392578</v>
       </c>
       <c r="AA25" t="n">
-        <v>-74.73351287841797</v>
+        <v>-81.56092834472656</v>
       </c>
       <c r="AB25" t="n">
-        <v>-72.53140258789062</v>
+        <v>-87.49952697753906</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-52.14778900146484</v>
+        <v>-69.78599548339844</v>
       </c>
       <c r="B26" t="n">
-        <v>-50.83913421630859</v>
+        <v>-73.35579681396484</v>
       </c>
       <c r="C26" t="n">
-        <v>-54.84902191162109</v>
+        <v>-71.23817443847656</v>
       </c>
       <c r="D26" t="n">
-        <v>-56.95793533325195</v>
+        <v>-77.42616271972656</v>
       </c>
       <c r="E26" t="n">
-        <v>-51.96546173095703</v>
+        <v>-78.60507965087891</v>
       </c>
       <c r="F26" t="n">
-        <v>-53.24138641357422</v>
+        <v>-80.22845458984375</v>
       </c>
       <c r="G26" t="n">
-        <v>-54.2042121887207</v>
+        <v>-72.73954772949219</v>
       </c>
       <c r="H26" t="n">
-        <v>-55.77830123901367</v>
+        <v>-71.75951385498047</v>
       </c>
       <c r="I26" t="n">
-        <v>-55.86244583129883</v>
+        <v>-67.08115386962891</v>
       </c>
       <c r="J26" t="n">
-        <v>-54.20487213134766</v>
+        <v>-68.78702545166016</v>
       </c>
       <c r="K26" t="n">
-        <v>-55.08611297607422</v>
+        <v>-70.5531005859375</v>
       </c>
       <c r="L26" t="n">
-        <v>-58.04201126098633</v>
+        <v>-73.90074157714844</v>
       </c>
       <c r="M26" t="n">
-        <v>-56.90396118164062</v>
+        <v>-79.98403167724609</v>
       </c>
       <c r="N26" t="n">
-        <v>-53.19670486450195</v>
+        <v>-72.69625091552734</v>
       </c>
       <c r="O26" t="n">
-        <v>-57.4512939453125</v>
+        <v>-87.54194641113281</v>
       </c>
       <c r="P26" t="n">
-        <v>-57.9738883972168</v>
+        <v>-73.49961853027344</v>
       </c>
       <c r="Q26" t="n">
-        <v>-58.69335174560547</v>
+        <v>-72.21620178222656</v>
       </c>
       <c r="R26" t="n">
-        <v>-54.32785797119141</v>
+        <v>-75.87650299072266</v>
       </c>
       <c r="S26" t="n">
-        <v>-55.04790115356445</v>
+        <v>-75.92710876464844</v>
       </c>
       <c r="T26" t="n">
-        <v>-54.99552154541016</v>
+        <v>-75.54086303710938</v>
       </c>
       <c r="U26" t="n">
-        <v>-52.24306488037109</v>
+        <v>-79.90215301513672</v>
       </c>
       <c r="V26" t="n">
-        <v>-54.45438766479492</v>
+        <v>-79.15306854248047</v>
       </c>
       <c r="W26" t="n">
-        <v>-58.28511428833008</v>
+        <v>-83.31874847412109</v>
       </c>
       <c r="X26" t="n">
-        <v>-55.89629364013672</v>
+        <v>-84.93759918212891</v>
       </c>
       <c r="Y26" t="n">
-        <v>-56.69658660888672</v>
+        <v>-81.24549865722656</v>
       </c>
       <c r="Z26" t="n">
-        <v>-58.54105377197266</v>
+        <v>-76.14341735839844</v>
       </c>
       <c r="AA26" t="n">
-        <v>-74.29019927978516</v>
+        <v>-79.16107940673828</v>
       </c>
       <c r="AB26" t="n">
-        <v>-70.38643646240234</v>
+        <v>-77.56710052490234</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-57.5158576965332</v>
+        <v>-70.2303466796875</v>
       </c>
       <c r="B27" t="n">
-        <v>-55.49120330810547</v>
+        <v>-70.01722717285156</v>
       </c>
       <c r="C27" t="n">
-        <v>-53.33394622802734</v>
+        <v>-71.91423034667969</v>
       </c>
       <c r="D27" t="n">
-        <v>-52.5635871887207</v>
+        <v>-70.12435913085938</v>
       </c>
       <c r="E27" t="n">
-        <v>-56.56888961791992</v>
+        <v>-69.56826019287109</v>
       </c>
       <c r="F27" t="n">
-        <v>-54.5594596862793</v>
+        <v>-73.55956268310547</v>
       </c>
       <c r="G27" t="n">
-        <v>-56.66851806640625</v>
+        <v>-77.85215759277344</v>
       </c>
       <c r="H27" t="n">
-        <v>-56.2935791015625</v>
+        <v>-73.20261383056641</v>
       </c>
       <c r="I27" t="n">
-        <v>-56.19706344604492</v>
+        <v>-69.56729125976562</v>
       </c>
       <c r="J27" t="n">
-        <v>-57.14913940429688</v>
+        <v>-66.50942993164062</v>
       </c>
       <c r="K27" t="n">
-        <v>-56.83437347412109</v>
+        <v>-78.52232360839844</v>
       </c>
       <c r="L27" t="n">
-        <v>-53.30596923828125</v>
+        <v>-78.84803771972656</v>
       </c>
       <c r="M27" t="n">
-        <v>-53.83443450927734</v>
+        <v>-75.43662261962891</v>
       </c>
       <c r="N27" t="n">
-        <v>-55.21277618408203</v>
+        <v>-69.69560241699219</v>
       </c>
       <c r="O27" t="n">
-        <v>-56.5864372253418</v>
+        <v>-80.03865051269531</v>
       </c>
       <c r="P27" t="n">
-        <v>-56.5009765625</v>
+        <v>-75.62673950195312</v>
       </c>
       <c r="Q27" t="n">
-        <v>-57.05280303955078</v>
+        <v>-73.30067443847656</v>
       </c>
       <c r="R27" t="n">
-        <v>-56.52701568603516</v>
+        <v>-73.36811828613281</v>
       </c>
       <c r="S27" t="n">
-        <v>-60.17999267578125</v>
+        <v>-79.48434448242188</v>
       </c>
       <c r="T27" t="n">
-        <v>-55.94407272338867</v>
+        <v>-78.21255493164062</v>
       </c>
       <c r="U27" t="n">
-        <v>-56.00505828857422</v>
+        <v>-79.93997955322266</v>
       </c>
       <c r="V27" t="n">
-        <v>-56.87162017822266</v>
+        <v>-82.44227600097656</v>
       </c>
       <c r="W27" t="n">
-        <v>-57.93756103515625</v>
+        <v>-86.32475280761719</v>
       </c>
       <c r="X27" t="n">
-        <v>-56.69522857666016</v>
+        <v>-82.90274810791016</v>
       </c>
       <c r="Y27" t="n">
-        <v>-58.19617462158203</v>
+        <v>-82.01158142089844</v>
       </c>
       <c r="Z27" t="n">
-        <v>-58.39019775390625</v>
+        <v>-83.44252777099609</v>
       </c>
       <c r="AA27" t="n">
-        <v>-57.28415679931641</v>
+        <v>-77.96221160888672</v>
       </c>
       <c r="AB27" t="n">
-        <v>-70.70953369140625</v>
+        <v>-83.16851806640625</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-57.16726684570312</v>
+        <v>-66.10008239746094</v>
       </c>
       <c r="B28" t="n">
-        <v>-54.3053092956543</v>
+        <v>-75.39016723632812</v>
       </c>
       <c r="C28" t="n">
-        <v>-55.60681915283203</v>
+        <v>-70.81501007080078</v>
       </c>
       <c r="D28" t="n">
-        <v>-55.0156135559082</v>
+        <v>-70.39385986328125</v>
       </c>
       <c r="E28" t="n">
-        <v>-55.93761444091797</v>
+        <v>-71.29540252685547</v>
       </c>
       <c r="F28" t="n">
-        <v>-57.15389251708984</v>
+        <v>-69.95278930664062</v>
       </c>
       <c r="G28" t="n">
-        <v>-53.85092926025391</v>
+        <v>-71.95045471191406</v>
       </c>
       <c r="H28" t="n">
-        <v>-57.5140380859375</v>
+        <v>-66.83616638183594</v>
       </c>
       <c r="I28" t="n">
-        <v>-55.10968017578125</v>
+        <v>-74.11933898925781</v>
       </c>
       <c r="J28" t="n">
-        <v>-56.17216873168945</v>
+        <v>-73.35271453857422</v>
       </c>
       <c r="K28" t="n">
-        <v>-51.51703643798828</v>
+        <v>-80.23941040039062</v>
       </c>
       <c r="L28" t="n">
-        <v>-53.84310150146484</v>
+        <v>-76.6512451171875</v>
       </c>
       <c r="M28" t="n">
-        <v>-57.86371994018555</v>
+        <v>-74.43103790283203</v>
       </c>
       <c r="N28" t="n">
-        <v>-56.8032341003418</v>
+        <v>-81.12487030029297</v>
       </c>
       <c r="O28" t="n">
-        <v>-55.06230545043945</v>
+        <v>-80.79627990722656</v>
       </c>
       <c r="P28" t="n">
-        <v>-57.23675537109375</v>
+        <v>-70.17593383789062</v>
       </c>
       <c r="Q28" t="n">
-        <v>-55.28859710693359</v>
+        <v>-82.41963958740234</v>
       </c>
       <c r="R28" t="n">
-        <v>-57.41031646728516</v>
+        <v>-78.68148040771484</v>
       </c>
       <c r="S28" t="n">
-        <v>-58.18102264404297</v>
+        <v>-78.21324157714844</v>
       </c>
       <c r="T28" t="n">
-        <v>-57.57196044921875</v>
+        <v>-80.35884094238281</v>
       </c>
       <c r="U28" t="n">
-        <v>-59.64554977416992</v>
+        <v>-80.75150299072266</v>
       </c>
       <c r="V28" t="n">
-        <v>-53.1104621887207</v>
+        <v>-81.73692321777344</v>
       </c>
       <c r="W28" t="n">
-        <v>-55.38903045654297</v>
+        <v>-82.49492645263672</v>
       </c>
       <c r="X28" t="n">
-        <v>-57.42118453979492</v>
+        <v>-84.84702301025391</v>
       </c>
       <c r="Y28" t="n">
-        <v>-54.16376876831055</v>
+        <v>-82.91275024414062</v>
       </c>
       <c r="Z28" t="n">
-        <v>-57.13166046142578</v>
+        <v>-84.71062469482422</v>
       </c>
       <c r="AA28" t="n">
-        <v>-58.08770751953125</v>
+        <v>-77.98387145996094</v>
       </c>
       <c r="AB28" t="n">
-        <v>-57.24158477783203</v>
+        <v>-76.26722717285156</v>
       </c>
     </row>
   </sheetData>

--- a/writerConference/rssi_output.xlsx
+++ b/writerConference/rssi_output.xlsx
@@ -2841,2410 +2841,2410 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>-34.11637115478516</v>
+        <v>-33.7098503112793</v>
       </c>
       <c r="B1" t="n">
-        <v>-36.6533088684082</v>
+        <v>-29.36517333984375</v>
       </c>
       <c r="C1" t="n">
-        <v>-45.87997817993164</v>
+        <v>-44.56256484985352</v>
       </c>
       <c r="D1" t="n">
-        <v>-40.43303680419922</v>
+        <v>-41.69289398193359</v>
       </c>
       <c r="E1" t="n">
-        <v>-48.62301635742188</v>
+        <v>-46.05231857299805</v>
       </c>
       <c r="F1" t="n">
-        <v>-46.73054122924805</v>
+        <v>-44.3223762512207</v>
       </c>
       <c r="G1" t="n">
-        <v>-58.0098762512207</v>
+        <v>-53.7462158203125</v>
       </c>
       <c r="H1" t="n">
-        <v>-54.2076301574707</v>
+        <v>-56.12018585205078</v>
       </c>
       <c r="I1" t="n">
-        <v>-49.12475204467773</v>
+        <v>-55.15571212768555</v>
       </c>
       <c r="J1" t="n">
-        <v>-62.18411254882812</v>
+        <v>-63.62122344970703</v>
       </c>
       <c r="K1" t="n">
-        <v>-61.45221710205078</v>
+        <v>-57.8695182800293</v>
       </c>
       <c r="L1" t="n">
-        <v>-59.2077522277832</v>
+        <v>-63.17186737060547</v>
       </c>
       <c r="M1" t="n">
-        <v>-63.49897003173828</v>
+        <v>-67.51364135742188</v>
       </c>
       <c r="N1" t="n">
-        <v>-61.66976165771484</v>
+        <v>-65.44786834716797</v>
       </c>
       <c r="O1" t="n">
-        <v>-57.34403610229492</v>
+        <v>-68.09762573242188</v>
       </c>
       <c r="P1" t="n">
-        <v>-64.26811218261719</v>
+        <v>-64.08045196533203</v>
       </c>
       <c r="Q1" t="n">
-        <v>-55.73726272583008</v>
+        <v>-71.36520385742188</v>
       </c>
       <c r="R1" t="n">
-        <v>-67.26081848144531</v>
+        <v>-67.76979064941406</v>
       </c>
       <c r="S1" t="n">
-        <v>-64.12453460693359</v>
+        <v>-66.32881927490234</v>
       </c>
       <c r="T1" t="n">
-        <v>-66.47541809082031</v>
+        <v>-65.18865966796875</v>
       </c>
       <c r="U1" t="n">
-        <v>-67.09975433349609</v>
+        <v>-63.65459060668945</v>
       </c>
       <c r="V1" t="n">
-        <v>-64.16859436035156</v>
+        <v>-66.86631011962891</v>
       </c>
       <c r="W1" t="n">
-        <v>-76.94157409667969</v>
+        <v>-69.75447082519531</v>
       </c>
       <c r="X1" t="n">
-        <v>-73.32273864746094</v>
+        <v>-70.02456665039062</v>
       </c>
       <c r="Y1" t="n">
-        <v>-72.23104095458984</v>
+        <v>-68.05355072021484</v>
       </c>
       <c r="Z1" t="n">
-        <v>-67.95345306396484</v>
+        <v>-67.30155944824219</v>
       </c>
       <c r="AA1" t="n">
-        <v>-74.85580444335938</v>
+        <v>-71.46757507324219</v>
       </c>
       <c r="AB1" t="n">
-        <v>-67.77872467041016</v>
+        <v>-75.35781860351562</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-38.22148895263672</v>
+        <v>-30.85965919494629</v>
       </c>
       <c r="B2" t="n">
-        <v>-37.307373046875</v>
+        <v>-36.96942520141602</v>
       </c>
       <c r="C2" t="n">
-        <v>-41.8782958984375</v>
+        <v>-41.33854293823242</v>
       </c>
       <c r="D2" t="n">
-        <v>-41.02332305908203</v>
+        <v>-41.73123931884766</v>
       </c>
       <c r="E2" t="n">
-        <v>-44.5108757019043</v>
+        <v>-51.06521606445312</v>
       </c>
       <c r="F2" t="n">
-        <v>-52.36992645263672</v>
+        <v>-51.75798797607422</v>
       </c>
       <c r="G2" t="n">
-        <v>-52.86273193359375</v>
+        <v>-59.0772819519043</v>
       </c>
       <c r="H2" t="n">
-        <v>-44.13032531738281</v>
+        <v>-57.61019897460938</v>
       </c>
       <c r="I2" t="n">
-        <v>-58.80984497070312</v>
+        <v>-55.0056266784668</v>
       </c>
       <c r="J2" t="n">
-        <v>-61.93291091918945</v>
+        <v>-58.08489990234375</v>
       </c>
       <c r="K2" t="n">
-        <v>-59.68865203857422</v>
+        <v>-63.36257171630859</v>
       </c>
       <c r="L2" t="n">
-        <v>-62.47419357299805</v>
+        <v>-59.57459259033203</v>
       </c>
       <c r="M2" t="n">
-        <v>-58.7570915222168</v>
+        <v>-65.30979156494141</v>
       </c>
       <c r="N2" t="n">
-        <v>-57.72348022460938</v>
+        <v>-64.82060241699219</v>
       </c>
       <c r="O2" t="n">
-        <v>-59.51596069335938</v>
+        <v>-62.64388275146484</v>
       </c>
       <c r="P2" t="n">
-        <v>-65.06832122802734</v>
+        <v>-62.96048736572266</v>
       </c>
       <c r="Q2" t="n">
-        <v>-60.81069183349609</v>
+        <v>-66.68401336669922</v>
       </c>
       <c r="R2" t="n">
-        <v>-66.96089172363281</v>
+        <v>-63.84293365478516</v>
       </c>
       <c r="S2" t="n">
-        <v>-74.45512390136719</v>
+        <v>-62.73199462890625</v>
       </c>
       <c r="T2" t="n">
-        <v>-71.00965881347656</v>
+        <v>-73.34713745117188</v>
       </c>
       <c r="U2" t="n">
-        <v>-74.88463592529297</v>
+        <v>-67.17170715332031</v>
       </c>
       <c r="V2" t="n">
-        <v>-70.10282135009766</v>
+        <v>-68.99310302734375</v>
       </c>
       <c r="W2" t="n">
-        <v>-75.24186706542969</v>
+        <v>-70.39007568359375</v>
       </c>
       <c r="X2" t="n">
-        <v>-70.05940246582031</v>
+        <v>-70.7625732421875</v>
       </c>
       <c r="Y2" t="n">
-        <v>-78.15744781494141</v>
+        <v>-76.14750671386719</v>
       </c>
       <c r="Z2" t="n">
-        <v>-73.27009582519531</v>
+        <v>-75.00096130371094</v>
       </c>
       <c r="AA2" t="n">
-        <v>-74.01828002929688</v>
+        <v>-70.79287719726562</v>
       </c>
       <c r="AB2" t="n">
-        <v>-78.10478210449219</v>
+        <v>-75.02851104736328</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-39.65427398681641</v>
+        <v>-38.23548126220703</v>
       </c>
       <c r="B3" t="n">
-        <v>-36.90192413330078</v>
+        <v>-39.13436126708984</v>
       </c>
       <c r="C3" t="n">
-        <v>-38.78023147583008</v>
+        <v>-37.41079330444336</v>
       </c>
       <c r="D3" t="n">
-        <v>-41.30951309204102</v>
+        <v>-52.24956512451172</v>
       </c>
       <c r="E3" t="n">
-        <v>-47.90862274169922</v>
+        <v>-52.27462768554688</v>
       </c>
       <c r="F3" t="n">
-        <v>-49.11072540283203</v>
+        <v>-55.68167877197266</v>
       </c>
       <c r="G3" t="n">
-        <v>-50.19905090332031</v>
+        <v>-52.0781135559082</v>
       </c>
       <c r="H3" t="n">
-        <v>-48.13653182983398</v>
+        <v>-57.10161209106445</v>
       </c>
       <c r="I3" t="n">
-        <v>-61.45248413085938</v>
+        <v>-51.69345855712891</v>
       </c>
       <c r="J3" t="n">
-        <v>-52.00173950195312</v>
+        <v>-61.1893196105957</v>
       </c>
       <c r="K3" t="n">
-        <v>-56.79397583007812</v>
+        <v>-55.89912033081055</v>
       </c>
       <c r="L3" t="n">
-        <v>-58.40578079223633</v>
+        <v>-64.31955718994141</v>
       </c>
       <c r="M3" t="n">
-        <v>-67.90570068359375</v>
+        <v>-60.7296257019043</v>
       </c>
       <c r="N3" t="n">
-        <v>-65.03328704833984</v>
+        <v>-62.29038619995117</v>
       </c>
       <c r="O3" t="n">
-        <v>-58.81159210205078</v>
+        <v>-59.91478729248047</v>
       </c>
       <c r="P3" t="n">
-        <v>-58.88004684448242</v>
+        <v>-65.24606323242188</v>
       </c>
       <c r="Q3" t="n">
-        <v>-67.30168151855469</v>
+        <v>-62.96253204345703</v>
       </c>
       <c r="R3" t="n">
-        <v>-63.71181488037109</v>
+        <v>-67.14942932128906</v>
       </c>
       <c r="S3" t="n">
-        <v>-67.26791381835938</v>
+        <v>-60.48241424560547</v>
       </c>
       <c r="T3" t="n">
-        <v>-72.96994018554688</v>
+        <v>-72.95016479492188</v>
       </c>
       <c r="U3" t="n">
-        <v>-75.73875427246094</v>
+        <v>-68.528076171875</v>
       </c>
       <c r="V3" t="n">
-        <v>-67.12599182128906</v>
+        <v>-72.83042907714844</v>
       </c>
       <c r="W3" t="n">
-        <v>-67.43167877197266</v>
+        <v>-68.66171264648438</v>
       </c>
       <c r="X3" t="n">
-        <v>-69.94474792480469</v>
+        <v>-67.11366271972656</v>
       </c>
       <c r="Y3" t="n">
-        <v>-72.42018127441406</v>
+        <v>-67.27769470214844</v>
       </c>
       <c r="Z3" t="n">
-        <v>-73.42662048339844</v>
+        <v>-67.19422912597656</v>
       </c>
       <c r="AA3" t="n">
-        <v>-76.06328582763672</v>
+        <v>-71.64076232910156</v>
       </c>
       <c r="AB3" t="n">
-        <v>-73.77793884277344</v>
+        <v>-77.34688568115234</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-42.30608367919922</v>
+        <v>-35.23579788208008</v>
       </c>
       <c r="B4" t="n">
-        <v>-40.14012908935547</v>
+        <v>-44.68349456787109</v>
       </c>
       <c r="C4" t="n">
-        <v>-43.38594055175781</v>
+        <v>-46.83379745483398</v>
       </c>
       <c r="D4" t="n">
-        <v>-43.13276290893555</v>
+        <v>-47.07064056396484</v>
       </c>
       <c r="E4" t="n">
-        <v>-48.0493278503418</v>
+        <v>-45.09615325927734</v>
       </c>
       <c r="F4" t="n">
-        <v>-56.07853317260742</v>
+        <v>-48.94282531738281</v>
       </c>
       <c r="G4" t="n">
-        <v>-57.60425567626953</v>
+        <v>-59.63515472412109</v>
       </c>
       <c r="H4" t="n">
-        <v>-53.7482795715332</v>
+        <v>-65.88605499267578</v>
       </c>
       <c r="I4" t="n">
-        <v>-59.43844604492188</v>
+        <v>-53.63178634643555</v>
       </c>
       <c r="J4" t="n">
-        <v>-56.68595504760742</v>
+        <v>-61.3350715637207</v>
       </c>
       <c r="K4" t="n">
-        <v>-56.51900100708008</v>
+        <v>-62.65914916992188</v>
       </c>
       <c r="L4" t="n">
-        <v>-61.55584716796875</v>
+        <v>-56.07980346679688</v>
       </c>
       <c r="M4" t="n">
-        <v>-60.51676177978516</v>
+        <v>-66.48919677734375</v>
       </c>
       <c r="N4" t="n">
-        <v>-65.96244812011719</v>
+        <v>-65.94012451171875</v>
       </c>
       <c r="O4" t="n">
-        <v>-64.90236663818359</v>
+        <v>-62.69511795043945</v>
       </c>
       <c r="P4" t="n">
-        <v>-66.82142639160156</v>
+        <v>-69.62189483642578</v>
       </c>
       <c r="Q4" t="n">
-        <v>-66.11281585693359</v>
+        <v>-63.83585739135742</v>
       </c>
       <c r="R4" t="n">
-        <v>-66.24061584472656</v>
+        <v>-63.78070068359375</v>
       </c>
       <c r="S4" t="n">
-        <v>-72.46485900878906</v>
+        <v>-69.29508209228516</v>
       </c>
       <c r="T4" t="n">
-        <v>-71.88596343994141</v>
+        <v>-71.72329711914062</v>
       </c>
       <c r="U4" t="n">
-        <v>-76.25927734375</v>
+        <v>-63.38232421875</v>
       </c>
       <c r="V4" t="n">
-        <v>-73.21586608886719</v>
+        <v>-72.17885589599609</v>
       </c>
       <c r="W4" t="n">
-        <v>-66.10075378417969</v>
+        <v>-63.01203155517578</v>
       </c>
       <c r="X4" t="n">
-        <v>-76.47300720214844</v>
+        <v>-66.27363586425781</v>
       </c>
       <c r="Y4" t="n">
-        <v>-69.06064605712891</v>
+        <v>-71.26071929931641</v>
       </c>
       <c r="Z4" t="n">
-        <v>-75.22959136962891</v>
+        <v>-76.22398376464844</v>
       </c>
       <c r="AA4" t="n">
-        <v>-74.0244140625</v>
+        <v>-68.18739318847656</v>
       </c>
       <c r="AB4" t="n">
-        <v>-70.76675415039062</v>
+        <v>-74.59661102294922</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-45.06870269775391</v>
+        <v>-47.60088729858398</v>
       </c>
       <c r="B5" t="n">
-        <v>-46.41352081298828</v>
+        <v>-47.15861129760742</v>
       </c>
       <c r="C5" t="n">
-        <v>-48.22005462646484</v>
+        <v>-45.10218048095703</v>
       </c>
       <c r="D5" t="n">
-        <v>-49.5151481628418</v>
+        <v>-47.25439071655273</v>
       </c>
       <c r="E5" t="n">
-        <v>-53.07341384887695</v>
+        <v>-48.21390914916992</v>
       </c>
       <c r="F5" t="n">
-        <v>-49.06997680664062</v>
+        <v>-51.10880279541016</v>
       </c>
       <c r="G5" t="n">
-        <v>-45.52576446533203</v>
+        <v>-56.2523307800293</v>
       </c>
       <c r="H5" t="n">
-        <v>-60.41010665893555</v>
+        <v>-60.5600700378418</v>
       </c>
       <c r="I5" t="n">
-        <v>-59.65986251831055</v>
+        <v>-66.45044708251953</v>
       </c>
       <c r="J5" t="n">
-        <v>-58.02349090576172</v>
+        <v>-66.66381072998047</v>
       </c>
       <c r="K5" t="n">
-        <v>-62.98993682861328</v>
+        <v>-64.53769683837891</v>
       </c>
       <c r="L5" t="n">
-        <v>-64.71311187744141</v>
+        <v>-66.48809814453125</v>
       </c>
       <c r="M5" t="n">
-        <v>-58.01709747314453</v>
+        <v>-66.71400451660156</v>
       </c>
       <c r="N5" t="n">
-        <v>-65.38529205322266</v>
+        <v>-64.395751953125</v>
       </c>
       <c r="O5" t="n">
-        <v>-60.28300857543945</v>
+        <v>-70.25916290283203</v>
       </c>
       <c r="P5" t="n">
-        <v>-65.58174133300781</v>
+        <v>-66.51358795166016</v>
       </c>
       <c r="Q5" t="n">
-        <v>-64.42340087890625</v>
+        <v>-69.20713806152344</v>
       </c>
       <c r="R5" t="n">
-        <v>-64.12812042236328</v>
+        <v>-73.30071258544922</v>
       </c>
       <c r="S5" t="n">
-        <v>-70.83783721923828</v>
+        <v>-68.76321411132812</v>
       </c>
       <c r="T5" t="n">
-        <v>-67.59728240966797</v>
+        <v>-64.04213714599609</v>
       </c>
       <c r="U5" t="n">
-        <v>-69.63531494140625</v>
+        <v>-67.09999847412109</v>
       </c>
       <c r="V5" t="n">
-        <v>-74.05799865722656</v>
+        <v>-69.40083312988281</v>
       </c>
       <c r="W5" t="n">
-        <v>-75.2901611328125</v>
+        <v>-74.05891418457031</v>
       </c>
       <c r="X5" t="n">
-        <v>-66.83589935302734</v>
+        <v>-69.41868591308594</v>
       </c>
       <c r="Y5" t="n">
-        <v>-80.40653991699219</v>
+        <v>-69.32427978515625</v>
       </c>
       <c r="Z5" t="n">
-        <v>-75.79234313964844</v>
+        <v>-73.94447326660156</v>
       </c>
       <c r="AA5" t="n">
-        <v>-73.58518981933594</v>
+        <v>-68.78302001953125</v>
       </c>
       <c r="AB5" t="n">
-        <v>-78.6878662109375</v>
+        <v>-66.93858337402344</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-45.83216094970703</v>
+        <v>-52.53848266601562</v>
       </c>
       <c r="B6" t="n">
-        <v>-45.21195220947266</v>
+        <v>-46.83024215698242</v>
       </c>
       <c r="C6" t="n">
-        <v>-48.22712326049805</v>
+        <v>-53.2105712890625</v>
       </c>
       <c r="D6" t="n">
-        <v>-49.01468658447266</v>
+        <v>-49.6555061340332</v>
       </c>
       <c r="E6" t="n">
-        <v>-52.32479095458984</v>
+        <v>-54.37044143676758</v>
       </c>
       <c r="F6" t="n">
-        <v>-47.5359001159668</v>
+        <v>-58.95313262939453</v>
       </c>
       <c r="G6" t="n">
-        <v>-58.75785446166992</v>
+        <v>-63.35646820068359</v>
       </c>
       <c r="H6" t="n">
-        <v>-52.70646286010742</v>
+        <v>-56.32136154174805</v>
       </c>
       <c r="I6" t="n">
-        <v>-60.93107986450195</v>
+        <v>-59.92595672607422</v>
       </c>
       <c r="J6" t="n">
-        <v>-62.14016723632812</v>
+        <v>-59.96498870849609</v>
       </c>
       <c r="K6" t="n">
-        <v>-58.11358642578125</v>
+        <v>-59.31481170654297</v>
       </c>
       <c r="L6" t="n">
-        <v>-58.88413238525391</v>
+        <v>-66.0804443359375</v>
       </c>
       <c r="M6" t="n">
-        <v>-60.73702239990234</v>
+        <v>-59.77975463867188</v>
       </c>
       <c r="N6" t="n">
-        <v>-66.95805358886719</v>
+        <v>-65.30616760253906</v>
       </c>
       <c r="O6" t="n">
-        <v>-62.501953125</v>
+        <v>-76.65522766113281</v>
       </c>
       <c r="P6" t="n">
-        <v>-62.71464920043945</v>
+        <v>-69.71105194091797</v>
       </c>
       <c r="Q6" t="n">
-        <v>-69.23302459716797</v>
+        <v>-66.25959777832031</v>
       </c>
       <c r="R6" t="n">
-        <v>-69.46364593505859</v>
+        <v>-68.55277252197266</v>
       </c>
       <c r="S6" t="n">
-        <v>-68.75613403320312</v>
+        <v>-64.92787170410156</v>
       </c>
       <c r="T6" t="n">
-        <v>-70.92040252685547</v>
+        <v>-70.91484832763672</v>
       </c>
       <c r="U6" t="n">
-        <v>-71.65497589111328</v>
+        <v>-75.66230010986328</v>
       </c>
       <c r="V6" t="n">
-        <v>-64.84494781494141</v>
+        <v>-70.07126617431641</v>
       </c>
       <c r="W6" t="n">
-        <v>-74.29389953613281</v>
+        <v>-74.82609558105469</v>
       </c>
       <c r="X6" t="n">
-        <v>-77.20683288574219</v>
+        <v>-69.87010192871094</v>
       </c>
       <c r="Y6" t="n">
-        <v>-73.67057800292969</v>
+        <v>-76.08921813964844</v>
       </c>
       <c r="Z6" t="n">
-        <v>-65.24075317382812</v>
+        <v>-75.25812530517578</v>
       </c>
       <c r="AA6" t="n">
-        <v>-73.52275085449219</v>
+        <v>-77.64463806152344</v>
       </c>
       <c r="AB6" t="n">
-        <v>-75.03868103027344</v>
+        <v>-72.55345153808594</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-52.55064010620117</v>
+        <v>-57.21350860595703</v>
       </c>
       <c r="B7" t="n">
-        <v>-44.36159515380859</v>
+        <v>-53.22647857666016</v>
       </c>
       <c r="C7" t="n">
-        <v>-46.95054626464844</v>
+        <v>-58.71112060546875</v>
       </c>
       <c r="D7" t="n">
-        <v>-52.7752799987793</v>
+        <v>-62.22270584106445</v>
       </c>
       <c r="E7" t="n">
-        <v>-59.0351676940918</v>
+        <v>-56.24955368041992</v>
       </c>
       <c r="F7" t="n">
-        <v>-56.33314895629883</v>
+        <v>-58.65511322021484</v>
       </c>
       <c r="G7" t="n">
-        <v>-62.00311279296875</v>
+        <v>-55.0084114074707</v>
       </c>
       <c r="H7" t="n">
-        <v>-54.91413116455078</v>
+        <v>-62.55127716064453</v>
       </c>
       <c r="I7" t="n">
-        <v>-55.67525482177734</v>
+        <v>-61.8798942565918</v>
       </c>
       <c r="J7" t="n">
-        <v>-60.29683303833008</v>
+        <v>-68.58695220947266</v>
       </c>
       <c r="K7" t="n">
-        <v>-63.53171920776367</v>
+        <v>-65.03408813476562</v>
       </c>
       <c r="L7" t="n">
-        <v>-59.90761566162109</v>
+        <v>-65.45881652832031</v>
       </c>
       <c r="M7" t="n">
-        <v>-70.68942260742188</v>
+        <v>-66.61933898925781</v>
       </c>
       <c r="N7" t="n">
-        <v>-63.30930709838867</v>
+        <v>-62.39210891723633</v>
       </c>
       <c r="O7" t="n">
-        <v>-65.38378143310547</v>
+        <v>-66.84602355957031</v>
       </c>
       <c r="P7" t="n">
-        <v>-64.64239501953125</v>
+        <v>-64.4493408203125</v>
       </c>
       <c r="Q7" t="n">
-        <v>-68.47403717041016</v>
+        <v>-68.92696380615234</v>
       </c>
       <c r="R7" t="n">
-        <v>-67.336181640625</v>
+        <v>-68.36653137207031</v>
       </c>
       <c r="S7" t="n">
-        <v>-69.46773529052734</v>
+        <v>-70.42939758300781</v>
       </c>
       <c r="T7" t="n">
-        <v>-70.10330200195312</v>
+        <v>-71.85982513427734</v>
       </c>
       <c r="U7" t="n">
-        <v>-75.05308532714844</v>
+        <v>-72.999755859375</v>
       </c>
       <c r="V7" t="n">
-        <v>-69.23465728759766</v>
+        <v>-74.6788330078125</v>
       </c>
       <c r="W7" t="n">
-        <v>-76.34042358398438</v>
+        <v>-70.94622039794922</v>
       </c>
       <c r="X7" t="n">
-        <v>-79.91173553466797</v>
+        <v>-69.48048400878906</v>
       </c>
       <c r="Y7" t="n">
-        <v>-77.07918548583984</v>
+        <v>-74.71916198730469</v>
       </c>
       <c r="Z7" t="n">
-        <v>-77.50023651123047</v>
+        <v>-68.60203552246094</v>
       </c>
       <c r="AA7" t="n">
-        <v>-72.87997436523438</v>
+        <v>-70.87339782714844</v>
       </c>
       <c r="AB7" t="n">
-        <v>-73.40400695800781</v>
+        <v>-74.88841247558594</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-58.90299606323242</v>
+        <v>-48.55022430419922</v>
       </c>
       <c r="B8" t="n">
-        <v>-54.50397491455078</v>
+        <v>-54.42799758911133</v>
       </c>
       <c r="C8" t="n">
-        <v>-51.81438064575195</v>
+        <v>-58.26270294189453</v>
       </c>
       <c r="D8" t="n">
-        <v>-56.38456344604492</v>
+        <v>-49.16904830932617</v>
       </c>
       <c r="E8" t="n">
-        <v>-54.65220260620117</v>
+        <v>-50.63866424560547</v>
       </c>
       <c r="F8" t="n">
-        <v>-52.44931793212891</v>
+        <v>-63.39951705932617</v>
       </c>
       <c r="G8" t="n">
-        <v>-62.03805541992188</v>
+        <v>-56.6962890625</v>
       </c>
       <c r="H8" t="n">
-        <v>-54.58379364013672</v>
+        <v>-59.72841644287109</v>
       </c>
       <c r="I8" t="n">
-        <v>-60.07946014404297</v>
+        <v>-61.46995162963867</v>
       </c>
       <c r="J8" t="n">
-        <v>-54.66326904296875</v>
+        <v>-59.7047004699707</v>
       </c>
       <c r="K8" t="n">
-        <v>-63.52217864990234</v>
+        <v>-65.81206512451172</v>
       </c>
       <c r="L8" t="n">
-        <v>-62.42234420776367</v>
+        <v>-59.70590209960938</v>
       </c>
       <c r="M8" t="n">
-        <v>-60.19309234619141</v>
+        <v>-63.42805099487305</v>
       </c>
       <c r="N8" t="n">
-        <v>-64.77719879150391</v>
+        <v>-66.50537109375</v>
       </c>
       <c r="O8" t="n">
-        <v>-66.37787628173828</v>
+        <v>-67.37957000732422</v>
       </c>
       <c r="P8" t="n">
-        <v>-66.99349975585938</v>
+        <v>-65.24763488769531</v>
       </c>
       <c r="Q8" t="n">
-        <v>-65.32234954833984</v>
+        <v>-62.12561798095703</v>
       </c>
       <c r="R8" t="n">
-        <v>-71.58641052246094</v>
+        <v>-76.23993682861328</v>
       </c>
       <c r="S8" t="n">
-        <v>-67.9176025390625</v>
+        <v>-66.34772491455078</v>
       </c>
       <c r="T8" t="n">
-        <v>-74.50788879394531</v>
+        <v>-70.30400848388672</v>
       </c>
       <c r="U8" t="n">
-        <v>-73.09005737304688</v>
+        <v>-66.37361907958984</v>
       </c>
       <c r="V8" t="n">
-        <v>-79.71280670166016</v>
+        <v>-73.42734527587891</v>
       </c>
       <c r="W8" t="n">
-        <v>-76.6611328125</v>
+        <v>-69.79655456542969</v>
       </c>
       <c r="X8" t="n">
-        <v>-80.03514099121094</v>
+        <v>-69.18862915039062</v>
       </c>
       <c r="Y8" t="n">
-        <v>-75.90629577636719</v>
+        <v>-68.59488677978516</v>
       </c>
       <c r="Z8" t="n">
-        <v>-82.63311767578125</v>
+        <v>-69.53178405761719</v>
       </c>
       <c r="AA8" t="n">
-        <v>-73.03665924072266</v>
+        <v>-69.28857421875</v>
       </c>
       <c r="AB8" t="n">
-        <v>-78.9610595703125</v>
+        <v>-73.88970184326172</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-54.93033981323242</v>
+        <v>-63.00504302978516</v>
       </c>
       <c r="B9" t="n">
-        <v>-63.51296234130859</v>
+        <v>-57.28912353515625</v>
       </c>
       <c r="C9" t="n">
-        <v>-45.91229248046875</v>
+        <v>-61.62161254882812</v>
       </c>
       <c r="D9" t="n">
-        <v>-50.96499252319336</v>
+        <v>-54.08329391479492</v>
       </c>
       <c r="E9" t="n">
-        <v>-54.72962188720703</v>
+        <v>-57.02082443237305</v>
       </c>
       <c r="F9" t="n">
-        <v>-61.21733856201172</v>
+        <v>-57.80374908447266</v>
       </c>
       <c r="G9" t="n">
-        <v>-54.1136589050293</v>
+        <v>-61.42966461181641</v>
       </c>
       <c r="H9" t="n">
-        <v>-57.64798736572266</v>
+        <v>-63.73186111450195</v>
       </c>
       <c r="I9" t="n">
-        <v>-66.20262145996094</v>
+        <v>-63.91861724853516</v>
       </c>
       <c r="J9" t="n">
-        <v>-61.69264602661133</v>
+        <v>-67.47383117675781</v>
       </c>
       <c r="K9" t="n">
-        <v>-61.90459442138672</v>
+        <v>-65.56980895996094</v>
       </c>
       <c r="L9" t="n">
-        <v>-67.56010437011719</v>
+        <v>-70.36894989013672</v>
       </c>
       <c r="M9" t="n">
-        <v>-64.25249481201172</v>
+        <v>-64.564697265625</v>
       </c>
       <c r="N9" t="n">
-        <v>-67.17228698730469</v>
+        <v>-64.54884338378906</v>
       </c>
       <c r="O9" t="n">
-        <v>-63.75237274169922</v>
+        <v>-66.99611663818359</v>
       </c>
       <c r="P9" t="n">
-        <v>-70.75910186767578</v>
+        <v>-69.41072082519531</v>
       </c>
       <c r="Q9" t="n">
-        <v>-63.83807373046875</v>
+        <v>-68.36259460449219</v>
       </c>
       <c r="R9" t="n">
-        <v>-72.48048400878906</v>
+        <v>-66.38052368164062</v>
       </c>
       <c r="S9" t="n">
-        <v>-73.07559967041016</v>
+        <v>-63.96812057495117</v>
       </c>
       <c r="T9" t="n">
-        <v>-68.86283874511719</v>
+        <v>-66.18257141113281</v>
       </c>
       <c r="U9" t="n">
-        <v>-68.93473815917969</v>
+        <v>-69.54689025878906</v>
       </c>
       <c r="V9" t="n">
-        <v>-75.88720703125</v>
+        <v>-69.84243774414062</v>
       </c>
       <c r="W9" t="n">
-        <v>-74.65080261230469</v>
+        <v>-70.81964111328125</v>
       </c>
       <c r="X9" t="n">
-        <v>-70.75167083740234</v>
+        <v>-70.88092041015625</v>
       </c>
       <c r="Y9" t="n">
-        <v>-77.44165802001953</v>
+        <v>-74.70520782470703</v>
       </c>
       <c r="Z9" t="n">
-        <v>-76.54146575927734</v>
+        <v>-66.07594299316406</v>
       </c>
       <c r="AA9" t="n">
-        <v>-79.22209167480469</v>
+        <v>-66.48365020751953</v>
       </c>
       <c r="AB9" t="n">
-        <v>-78.50932312011719</v>
+        <v>-73.66236114501953</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-53.9743537902832</v>
+        <v>-66.05857849121094</v>
       </c>
       <c r="B10" t="n">
-        <v>-52.66562652587891</v>
+        <v>-60.38192749023438</v>
       </c>
       <c r="C10" t="n">
-        <v>-51.15245056152344</v>
+        <v>-64.10606384277344</v>
       </c>
       <c r="D10" t="n">
-        <v>-61.33113479614258</v>
+        <v>-58.36000442504883</v>
       </c>
       <c r="E10" t="n">
-        <v>-67.76570129394531</v>
+        <v>-60.08909225463867</v>
       </c>
       <c r="F10" t="n">
-        <v>-65.94810485839844</v>
+        <v>-63.63720703125</v>
       </c>
       <c r="G10" t="n">
-        <v>-60.66793060302734</v>
+        <v>-64.06038665771484</v>
       </c>
       <c r="H10" t="n">
-        <v>-62.16201782226562</v>
+        <v>-66.1959228515625</v>
       </c>
       <c r="I10" t="n">
-        <v>-61.02276611328125</v>
+        <v>-66.69162750244141</v>
       </c>
       <c r="J10" t="n">
-        <v>-68.72425079345703</v>
+        <v>-61.68937301635742</v>
       </c>
       <c r="K10" t="n">
-        <v>-67.71443939208984</v>
+        <v>-60.19041061401367</v>
       </c>
       <c r="L10" t="n">
-        <v>-65.15165710449219</v>
+        <v>-67.71107482910156</v>
       </c>
       <c r="M10" t="n">
-        <v>-66.53916931152344</v>
+        <v>-68.14168548583984</v>
       </c>
       <c r="N10" t="n">
-        <v>-65.94584655761719</v>
+        <v>-68.77070617675781</v>
       </c>
       <c r="O10" t="n">
-        <v>-69.16143035888672</v>
+        <v>-65.34156036376953</v>
       </c>
       <c r="P10" t="n">
-        <v>-69.70945739746094</v>
+        <v>-68.22176361083984</v>
       </c>
       <c r="Q10" t="n">
-        <v>-66.43873596191406</v>
+        <v>-64.98366546630859</v>
       </c>
       <c r="R10" t="n">
-        <v>-69.97699737548828</v>
+        <v>-68.83249664306641</v>
       </c>
       <c r="S10" t="n">
-        <v>-70.95146942138672</v>
+        <v>-64.36537170410156</v>
       </c>
       <c r="T10" t="n">
-        <v>-71.34263610839844</v>
+        <v>-71.63359069824219</v>
       </c>
       <c r="U10" t="n">
-        <v>-73.86199188232422</v>
+        <v>-71.57039642333984</v>
       </c>
       <c r="V10" t="n">
-        <v>-74.97004699707031</v>
+        <v>-62.81288909912109</v>
       </c>
       <c r="W10" t="n">
-        <v>-65.27073669433594</v>
+        <v>-70.41670989990234</v>
       </c>
       <c r="X10" t="n">
-        <v>-74.90641784667969</v>
+        <v>-69.42076873779297</v>
       </c>
       <c r="Y10" t="n">
-        <v>-74.16950988769531</v>
+        <v>-71.97993469238281</v>
       </c>
       <c r="Z10" t="n">
-        <v>-74.47250366210938</v>
+        <v>-68.46501159667969</v>
       </c>
       <c r="AA10" t="n">
-        <v>-76.69729614257812</v>
+        <v>-66.9295654296875</v>
       </c>
       <c r="AB10" t="n">
-        <v>-81.33036041259766</v>
+        <v>-69.55608367919922</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-58.41929244995117</v>
+        <v>-61.63851928710938</v>
       </c>
       <c r="B11" t="n">
-        <v>-51.51115798950195</v>
+        <v>-62.16160202026367</v>
       </c>
       <c r="C11" t="n">
-        <v>-49.23949813842773</v>
+        <v>-60.33963012695312</v>
       </c>
       <c r="D11" t="n">
-        <v>-58.14957427978516</v>
+        <v>-62.09901809692383</v>
       </c>
       <c r="E11" t="n">
-        <v>-63.22345733642578</v>
+        <v>-61.06621551513672</v>
       </c>
       <c r="F11" t="n">
-        <v>-54.51686477661133</v>
+        <v>-64.29229736328125</v>
       </c>
       <c r="G11" t="n">
-        <v>-57.3114128112793</v>
+        <v>-66.19809722900391</v>
       </c>
       <c r="H11" t="n">
-        <v>-63.6290168762207</v>
+        <v>-62.49774932861328</v>
       </c>
       <c r="I11" t="n">
-        <v>-61.3636589050293</v>
+        <v>-65.69528961181641</v>
       </c>
       <c r="J11" t="n">
-        <v>-64.21614837646484</v>
+        <v>-67.13438415527344</v>
       </c>
       <c r="K11" t="n">
-        <v>-61.12168121337891</v>
+        <v>-68.74611663818359</v>
       </c>
       <c r="L11" t="n">
-        <v>-60.05228424072266</v>
+        <v>-66.99912261962891</v>
       </c>
       <c r="M11" t="n">
-        <v>-66.45494842529297</v>
+        <v>-72.17703247070312</v>
       </c>
       <c r="N11" t="n">
-        <v>-64.01594543457031</v>
+        <v>-67.05782318115234</v>
       </c>
       <c r="O11" t="n">
-        <v>-63.36746978759766</v>
+        <v>-64.50007629394531</v>
       </c>
       <c r="P11" t="n">
-        <v>-66.71738433837891</v>
+        <v>-65.7720947265625</v>
       </c>
       <c r="Q11" t="n">
-        <v>-69.00900268554688</v>
+        <v>-76.02210998535156</v>
       </c>
       <c r="R11" t="n">
-        <v>-68.34485626220703</v>
+        <v>-68.63703918457031</v>
       </c>
       <c r="S11" t="n">
-        <v>-70.28801727294922</v>
+        <v>-68.88960266113281</v>
       </c>
       <c r="T11" t="n">
-        <v>-69.07244110107422</v>
+        <v>-72.38954162597656</v>
       </c>
       <c r="U11" t="n">
-        <v>-67.63325500488281</v>
+        <v>-60.68074798583984</v>
       </c>
       <c r="V11" t="n">
-        <v>-77.52460479736328</v>
+        <v>-68.55519104003906</v>
       </c>
       <c r="W11" t="n">
-        <v>-72.37155151367188</v>
+        <v>-66.04866790771484</v>
       </c>
       <c r="X11" t="n">
-        <v>-67.98761749267578</v>
+        <v>-73.74510192871094</v>
       </c>
       <c r="Y11" t="n">
-        <v>-76.34034729003906</v>
+        <v>-74.21844482421875</v>
       </c>
       <c r="Z11" t="n">
-        <v>-72.62679290771484</v>
+        <v>-67.74082946777344</v>
       </c>
       <c r="AA11" t="n">
-        <v>-78.50975799560547</v>
+        <v>-73.87210845947266</v>
       </c>
       <c r="AB11" t="n">
-        <v>-77.57418060302734</v>
+        <v>-75.00733947753906</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-60.5819091796875</v>
+        <v>-61.02529907226562</v>
       </c>
       <c r="B12" t="n">
-        <v>-59.75081253051758</v>
+        <v>-51.60551071166992</v>
       </c>
       <c r="C12" t="n">
-        <v>-65.18190765380859</v>
+        <v>-67.40309906005859</v>
       </c>
       <c r="D12" t="n">
-        <v>-60.92673492431641</v>
+        <v>-67.27445220947266</v>
       </c>
       <c r="E12" t="n">
-        <v>-56.57034301757812</v>
+        <v>-64.01358795166016</v>
       </c>
       <c r="F12" t="n">
-        <v>-64.231201171875</v>
+        <v>-66.53683471679688</v>
       </c>
       <c r="G12" t="n">
-        <v>-65.41545867919922</v>
+        <v>-64.985107421875</v>
       </c>
       <c r="H12" t="n">
-        <v>-65.32072448730469</v>
+        <v>-65.36081695556641</v>
       </c>
       <c r="I12" t="n">
-        <v>-65.29581451416016</v>
+        <v>-66.04640960693359</v>
       </c>
       <c r="J12" t="n">
-        <v>-59.62632369995117</v>
+        <v>-68.80641174316406</v>
       </c>
       <c r="K12" t="n">
-        <v>-63.64745330810547</v>
+        <v>-66.21196746826172</v>
       </c>
       <c r="L12" t="n">
-        <v>-66.81346893310547</v>
+        <v>-66.38868713378906</v>
       </c>
       <c r="M12" t="n">
-        <v>-61.53045654296875</v>
+        <v>-65.52293395996094</v>
       </c>
       <c r="N12" t="n">
-        <v>-68.79829406738281</v>
+        <v>-72.50365447998047</v>
       </c>
       <c r="O12" t="n">
-        <v>-66.03692626953125</v>
+        <v>-59.7730827331543</v>
       </c>
       <c r="P12" t="n">
-        <v>-66.28581237792969</v>
+        <v>-68.51149749755859</v>
       </c>
       <c r="Q12" t="n">
-        <v>-71.20291900634766</v>
+        <v>-64.38053131103516</v>
       </c>
       <c r="R12" t="n">
-        <v>-72.65174865722656</v>
+        <v>-72.40220642089844</v>
       </c>
       <c r="S12" t="n">
-        <v>-65.07954406738281</v>
+        <v>-68.75942993164062</v>
       </c>
       <c r="T12" t="n">
-        <v>-71.67091369628906</v>
+        <v>-67.91849517822266</v>
       </c>
       <c r="U12" t="n">
-        <v>-75.44611358642578</v>
+        <v>-70.07183074951172</v>
       </c>
       <c r="V12" t="n">
-        <v>-71.52532196044922</v>
+        <v>-70.09879302978516</v>
       </c>
       <c r="W12" t="n">
-        <v>-74.06021881103516</v>
+        <v>-71.95429229736328</v>
       </c>
       <c r="X12" t="n">
-        <v>-70.15785980224609</v>
+        <v>-70.65775299072266</v>
       </c>
       <c r="Y12" t="n">
-        <v>-74.05391693115234</v>
+        <v>-70.68893432617188</v>
       </c>
       <c r="Z12" t="n">
-        <v>-74.82475280761719</v>
+        <v>-73.84772491455078</v>
       </c>
       <c r="AA12" t="n">
-        <v>-69.72624206542969</v>
+        <v>-71.39455413818359</v>
       </c>
       <c r="AB12" t="n">
-        <v>-85.77940368652344</v>
+        <v>-78.66481018066406</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-66.10333251953125</v>
+        <v>-68.71748352050781</v>
       </c>
       <c r="B13" t="n">
-        <v>-65.132568359375</v>
+        <v>-64.83194732666016</v>
       </c>
       <c r="C13" t="n">
-        <v>-60.55240631103516</v>
+        <v>-61.96004104614258</v>
       </c>
       <c r="D13" t="n">
-        <v>-60.28391265869141</v>
+        <v>-69.94150543212891</v>
       </c>
       <c r="E13" t="n">
-        <v>-63.48889923095703</v>
+        <v>-62.87835693359375</v>
       </c>
       <c r="F13" t="n">
-        <v>-67.64989471435547</v>
+        <v>-70.60520935058594</v>
       </c>
       <c r="G13" t="n">
-        <v>-67.74240875244141</v>
+        <v>-66.21601867675781</v>
       </c>
       <c r="H13" t="n">
-        <v>-64.08216857910156</v>
+        <v>-65.4014892578125</v>
       </c>
       <c r="I13" t="n">
-        <v>-61.44413375854492</v>
+        <v>-70.00236511230469</v>
       </c>
       <c r="J13" t="n">
-        <v>-66.57853698730469</v>
+        <v>-65.30608367919922</v>
       </c>
       <c r="K13" t="n">
-        <v>-59.67586135864258</v>
+        <v>-67.26004791259766</v>
       </c>
       <c r="L13" t="n">
-        <v>-64.68779754638672</v>
+        <v>-71.17364501953125</v>
       </c>
       <c r="M13" t="n">
-        <v>-60.31438064575195</v>
+        <v>-67.02207183837891</v>
       </c>
       <c r="N13" t="n">
-        <v>-63.5710334777832</v>
+        <v>-65.50791931152344</v>
       </c>
       <c r="O13" t="n">
-        <v>-68.38706207275391</v>
+        <v>-62.08211135864258</v>
       </c>
       <c r="P13" t="n">
-        <v>-73.76930236816406</v>
+        <v>-68.62937164306641</v>
       </c>
       <c r="Q13" t="n">
-        <v>-67.16481781005859</v>
+        <v>-67.79485321044922</v>
       </c>
       <c r="R13" t="n">
-        <v>-67.60848236083984</v>
+        <v>-69.60890197753906</v>
       </c>
       <c r="S13" t="n">
-        <v>-68.75886535644531</v>
+        <v>-68.55556488037109</v>
       </c>
       <c r="T13" t="n">
-        <v>-74.66067504882812</v>
+        <v>-71.31977081298828</v>
       </c>
       <c r="U13" t="n">
-        <v>-76.5196533203125</v>
+        <v>-71.38316345214844</v>
       </c>
       <c r="V13" t="n">
-        <v>-69.67460632324219</v>
+        <v>-68.16362762451172</v>
       </c>
       <c r="W13" t="n">
-        <v>-69.29115295410156</v>
+        <v>-69.68831634521484</v>
       </c>
       <c r="X13" t="n">
-        <v>-71.65747833251953</v>
+        <v>-71.29336547851562</v>
       </c>
       <c r="Y13" t="n">
-        <v>-82.18756866455078</v>
+        <v>-71.71079254150391</v>
       </c>
       <c r="Z13" t="n">
-        <v>-75.29896545410156</v>
+        <v>-73.06523895263672</v>
       </c>
       <c r="AA13" t="n">
-        <v>-76.22628784179688</v>
+        <v>-73.63838958740234</v>
       </c>
       <c r="AB13" t="n">
-        <v>-73.98787689208984</v>
+        <v>-71.04493713378906</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-54.52248382568359</v>
+        <v>-60.71237182617188</v>
       </c>
       <c r="B14" t="n">
-        <v>-58.80188751220703</v>
+        <v>-67.46517944335938</v>
       </c>
       <c r="C14" t="n">
-        <v>-64.53090667724609</v>
+        <v>-66.25839996337891</v>
       </c>
       <c r="D14" t="n">
-        <v>-65.10008239746094</v>
+        <v>-56.92254638671875</v>
       </c>
       <c r="E14" t="n">
-        <v>-63.56110763549805</v>
+        <v>-65.44233703613281</v>
       </c>
       <c r="F14" t="n">
-        <v>-67.47025299072266</v>
+        <v>-65.80440521240234</v>
       </c>
       <c r="G14" t="n">
-        <v>-63.78549194335938</v>
+        <v>-67.04121398925781</v>
       </c>
       <c r="H14" t="n">
-        <v>-65.67814636230469</v>
+        <v>-63.65402221679688</v>
       </c>
       <c r="I14" t="n">
-        <v>-69.32896423339844</v>
+        <v>-64.78574371337891</v>
       </c>
       <c r="J14" t="n">
-        <v>-73.18755340576172</v>
+        <v>-72.35047149658203</v>
       </c>
       <c r="K14" t="n">
-        <v>-67.50411224365234</v>
+        <v>-70.4326171875</v>
       </c>
       <c r="L14" t="n">
-        <v>-58.53595733642578</v>
+        <v>-66.74758911132812</v>
       </c>
       <c r="M14" t="n">
-        <v>-67.48514556884766</v>
+        <v>-69.83165740966797</v>
       </c>
       <c r="N14" t="n">
-        <v>-69.27976989746094</v>
+        <v>-68.89837646484375</v>
       </c>
       <c r="O14" t="n">
-        <v>-70.97752380371094</v>
+        <v>-68.84629821777344</v>
       </c>
       <c r="P14" t="n">
-        <v>-74.61062622070312</v>
+        <v>-61.61391067504883</v>
       </c>
       <c r="Q14" t="n">
-        <v>-75.02696228027344</v>
+        <v>-67.90733337402344</v>
       </c>
       <c r="R14" t="n">
-        <v>-65.50127410888672</v>
+        <v>-66.76154327392578</v>
       </c>
       <c r="S14" t="n">
-        <v>-66.63320159912109</v>
+        <v>-67.06711578369141</v>
       </c>
       <c r="T14" t="n">
-        <v>-74.39483642578125</v>
+        <v>-71.03845977783203</v>
       </c>
       <c r="U14" t="n">
-        <v>-76.00064086914062</v>
+        <v>-67.90599060058594</v>
       </c>
       <c r="V14" t="n">
-        <v>-75.00688934326172</v>
+        <v>-65.19773864746094</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.16098022460938</v>
+        <v>-65.52643585205078</v>
       </c>
       <c r="X14" t="n">
-        <v>-76.37614440917969</v>
+        <v>-73.27798461914062</v>
       </c>
       <c r="Y14" t="n">
-        <v>-78.99638366699219</v>
+        <v>-68.60185241699219</v>
       </c>
       <c r="Z14" t="n">
-        <v>-73.80770874023438</v>
+        <v>-67.3868408203125</v>
       </c>
       <c r="AA14" t="n">
-        <v>-73.95625305175781</v>
+        <v>-70.34724426269531</v>
       </c>
       <c r="AB14" t="n">
-        <v>-75.29637145996094</v>
+        <v>-74.90477752685547</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-62.79875564575195</v>
+        <v>-70.56026458740234</v>
       </c>
       <c r="B15" t="n">
-        <v>-62.30280685424805</v>
+        <v>-71.41136169433594</v>
       </c>
       <c r="C15" t="n">
-        <v>-60.66049957275391</v>
+        <v>-71.40203094482422</v>
       </c>
       <c r="D15" t="n">
-        <v>-61.54913330078125</v>
+        <v>-65.76118469238281</v>
       </c>
       <c r="E15" t="n">
-        <v>-63.65618896484375</v>
+        <v>-73.48091125488281</v>
       </c>
       <c r="F15" t="n">
-        <v>-57.12605667114258</v>
+        <v>-69.43849182128906</v>
       </c>
       <c r="G15" t="n">
-        <v>-72.72144317626953</v>
+        <v>-70.3570556640625</v>
       </c>
       <c r="H15" t="n">
-        <v>-61.99558639526367</v>
+        <v>-69.59553527832031</v>
       </c>
       <c r="I15" t="n">
-        <v>-68.49256896972656</v>
+        <v>-68.26966857910156</v>
       </c>
       <c r="J15" t="n">
-        <v>-67.61899566650391</v>
+        <v>-71.98405456542969</v>
       </c>
       <c r="K15" t="n">
-        <v>-65.04885101318359</v>
+        <v>-75.46871185302734</v>
       </c>
       <c r="L15" t="n">
-        <v>-68.93846130371094</v>
+        <v>-73.31890106201172</v>
       </c>
       <c r="M15" t="n">
-        <v>-65.11258697509766</v>
+        <v>-71.85759735107422</v>
       </c>
       <c r="N15" t="n">
-        <v>-66.74104309082031</v>
+        <v>-71.94322967529297</v>
       </c>
       <c r="O15" t="n">
-        <v>-75.58149719238281</v>
+        <v>-73.79487609863281</v>
       </c>
       <c r="P15" t="n">
-        <v>-78.36625671386719</v>
+        <v>-74.73420715332031</v>
       </c>
       <c r="Q15" t="n">
-        <v>-76.46271514892578</v>
+        <v>-69.60689544677734</v>
       </c>
       <c r="R15" t="n">
-        <v>-73.13027191162109</v>
+        <v>-69.30638885498047</v>
       </c>
       <c r="S15" t="n">
-        <v>-69.25746917724609</v>
+        <v>-69.95090484619141</v>
       </c>
       <c r="T15" t="n">
-        <v>-78.64080810546875</v>
+        <v>-74.24980926513672</v>
       </c>
       <c r="U15" t="n">
-        <v>-71.73487854003906</v>
+        <v>-71.64653015136719</v>
       </c>
       <c r="V15" t="n">
-        <v>-72.58130645751953</v>
+        <v>-69.10652160644531</v>
       </c>
       <c r="W15" t="n">
-        <v>-74.39270782470703</v>
+        <v>-73.43485260009766</v>
       </c>
       <c r="X15" t="n">
-        <v>-71.67909240722656</v>
+        <v>-69.68348693847656</v>
       </c>
       <c r="Y15" t="n">
-        <v>-73.18355560302734</v>
+        <v>-78.33647155761719</v>
       </c>
       <c r="Z15" t="n">
-        <v>-76.16712188720703</v>
+        <v>-71.61546325683594</v>
       </c>
       <c r="AA15" t="n">
-        <v>-74.42573547363281</v>
+        <v>-68.41701507568359</v>
       </c>
       <c r="AB15" t="n">
-        <v>-80.55986022949219</v>
+        <v>-73.32344818115234</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-72.00758361816406</v>
+        <v>-65.66287231445312</v>
       </c>
       <c r="B16" t="n">
-        <v>-60.17617797851562</v>
+        <v>-74.1400146484375</v>
       </c>
       <c r="C16" t="n">
-        <v>-70.04421234130859</v>
+        <v>-73.08901977539062</v>
       </c>
       <c r="D16" t="n">
-        <v>-69.25435638427734</v>
+        <v>-76.04224395751953</v>
       </c>
       <c r="E16" t="n">
-        <v>-63.2730827331543</v>
+        <v>-69.83625030517578</v>
       </c>
       <c r="F16" t="n">
-        <v>-63.0435676574707</v>
+        <v>-71.0516357421875</v>
       </c>
       <c r="G16" t="n">
-        <v>-66.91072845458984</v>
+        <v>-70.30686187744141</v>
       </c>
       <c r="H16" t="n">
-        <v>-72.24715423583984</v>
+        <v>-66.05747985839844</v>
       </c>
       <c r="I16" t="n">
-        <v>-66.65049743652344</v>
+        <v>-74.92098236083984</v>
       </c>
       <c r="J16" t="n">
-        <v>-68.80075836181641</v>
+        <v>-75.7718505859375</v>
       </c>
       <c r="K16" t="n">
-        <v>-74.02100372314453</v>
+        <v>-73.16789245605469</v>
       </c>
       <c r="L16" t="n">
-        <v>-68.44707489013672</v>
+        <v>-71.30830383300781</v>
       </c>
       <c r="M16" t="n">
-        <v>-69.06774139404297</v>
+        <v>-75.99625396728516</v>
       </c>
       <c r="N16" t="n">
-        <v>-70.98493957519531</v>
+        <v>-75.63008880615234</v>
       </c>
       <c r="O16" t="n">
-        <v>-75.32363891601562</v>
+        <v>-78.39583587646484</v>
       </c>
       <c r="P16" t="n">
-        <v>-83.80572509765625</v>
+        <v>-73.85528564453125</v>
       </c>
       <c r="Q16" t="n">
-        <v>-75.67152404785156</v>
+        <v>-69.53143310546875</v>
       </c>
       <c r="R16" t="n">
-        <v>-74.83447265625</v>
+        <v>-69.4432373046875</v>
       </c>
       <c r="S16" t="n">
-        <v>-74.71366882324219</v>
+        <v>-70.66081237792969</v>
       </c>
       <c r="T16" t="n">
-        <v>-70.07478332519531</v>
+        <v>-73.33457946777344</v>
       </c>
       <c r="U16" t="n">
-        <v>-77.15499877929688</v>
+        <v>-70.26005554199219</v>
       </c>
       <c r="V16" t="n">
-        <v>-72.09336853027344</v>
+        <v>-73.38973999023438</v>
       </c>
       <c r="W16" t="n">
-        <v>-75.51203155517578</v>
+        <v>-71.27129364013672</v>
       </c>
       <c r="X16" t="n">
-        <v>-76.56692504882812</v>
+        <v>-69.18337249755859</v>
       </c>
       <c r="Y16" t="n">
-        <v>-80.41970062255859</v>
+        <v>-70.40149688720703</v>
       </c>
       <c r="Z16" t="n">
-        <v>-81.08265686035156</v>
+        <v>-80.86421203613281</v>
       </c>
       <c r="AA16" t="n">
-        <v>-72.39835357666016</v>
+        <v>-72.11105346679688</v>
       </c>
       <c r="AB16" t="n">
-        <v>-76.18902587890625</v>
+        <v>-72.83988952636719</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-66.08208465576172</v>
+        <v>-67.95009613037109</v>
       </c>
       <c r="B17" t="n">
-        <v>-67.19593811035156</v>
+        <v>-75.29545593261719</v>
       </c>
       <c r="C17" t="n">
-        <v>-66.69944000244141</v>
+        <v>-71.95643615722656</v>
       </c>
       <c r="D17" t="n">
-        <v>-69.75330352783203</v>
+        <v>-75.17889404296875</v>
       </c>
       <c r="E17" t="n">
-        <v>-64.92133331298828</v>
+        <v>-76.40382385253906</v>
       </c>
       <c r="F17" t="n">
-        <v>-72.8037109375</v>
+        <v>-65.51237487792969</v>
       </c>
       <c r="G17" t="n">
-        <v>-69.7442626953125</v>
+        <v>-70.25747680664062</v>
       </c>
       <c r="H17" t="n">
-        <v>-67.11502838134766</v>
+        <v>-63.54871368408203</v>
       </c>
       <c r="I17" t="n">
-        <v>-71.09755706787109</v>
+        <v>-79.65044403076172</v>
       </c>
       <c r="J17" t="n">
-        <v>-74.00000762939453</v>
+        <v>-78.04311370849609</v>
       </c>
       <c r="K17" t="n">
-        <v>-69.71230316162109</v>
+        <v>-73.05531311035156</v>
       </c>
       <c r="L17" t="n">
-        <v>-73.02872467041016</v>
+        <v>-78.42352294921875</v>
       </c>
       <c r="M17" t="n">
-        <v>-72.77823638916016</v>
+        <v>-79.16069793701172</v>
       </c>
       <c r="N17" t="n">
-        <v>-72.52186584472656</v>
+        <v>-80.88692474365234</v>
       </c>
       <c r="O17" t="n">
-        <v>-69.93449401855469</v>
+        <v>-80.92038726806641</v>
       </c>
       <c r="P17" t="n">
-        <v>-74.63346862792969</v>
+        <v>-78.53007507324219</v>
       </c>
       <c r="Q17" t="n">
-        <v>-70.41405487060547</v>
+        <v>-76.06574249267578</v>
       </c>
       <c r="R17" t="n">
-        <v>-74.89646911621094</v>
+        <v>-72.85861206054688</v>
       </c>
       <c r="S17" t="n">
-        <v>-78.45729064941406</v>
+        <v>-74.84043121337891</v>
       </c>
       <c r="T17" t="n">
-        <v>-73.927734375</v>
+        <v>-66.95240020751953</v>
       </c>
       <c r="U17" t="n">
-        <v>-75.72846984863281</v>
+        <v>-72.87763214111328</v>
       </c>
       <c r="V17" t="n">
-        <v>-71.47807312011719</v>
+        <v>-73.02011108398438</v>
       </c>
       <c r="W17" t="n">
-        <v>-69.77063751220703</v>
+        <v>-74.58713531494141</v>
       </c>
       <c r="X17" t="n">
-        <v>-74.66117095947266</v>
+        <v>-73.24288940429688</v>
       </c>
       <c r="Y17" t="n">
-        <v>-78.35383605957031</v>
+        <v>-72.89736938476562</v>
       </c>
       <c r="Z17" t="n">
-        <v>-77.08119964599609</v>
+        <v>-71.64860534667969</v>
       </c>
       <c r="AA17" t="n">
-        <v>-77.66966247558594</v>
+        <v>-75.35336303710938</v>
       </c>
       <c r="AB17" t="n">
-        <v>-81.12178039550781</v>
+        <v>-73.84610748291016</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-65.31311798095703</v>
+        <v>-82.56191253662109</v>
       </c>
       <c r="B18" t="n">
-        <v>-63.76861572265625</v>
+        <v>-72.20119476318359</v>
       </c>
       <c r="C18" t="n">
-        <v>-63.66838455200195</v>
+        <v>-74.60499572753906</v>
       </c>
       <c r="D18" t="n">
-        <v>-72.85564422607422</v>
+        <v>-73.46527099609375</v>
       </c>
       <c r="E18" t="n">
-        <v>-72.21717071533203</v>
+        <v>-80.53417205810547</v>
       </c>
       <c r="F18" t="n">
-        <v>-66.15780639648438</v>
+        <v>-77.35057067871094</v>
       </c>
       <c r="G18" t="n">
-        <v>-76.66163635253906</v>
+        <v>-71.52903747558594</v>
       </c>
       <c r="H18" t="n">
-        <v>-67.28065490722656</v>
+        <v>-77.147216796875</v>
       </c>
       <c r="I18" t="n">
-        <v>-74.11048126220703</v>
+        <v>-72.57780456542969</v>
       </c>
       <c r="J18" t="n">
-        <v>-69.05361175537109</v>
+        <v>-69.85655212402344</v>
       </c>
       <c r="K18" t="n">
-        <v>-70.09110260009766</v>
+        <v>-69.05537414550781</v>
       </c>
       <c r="L18" t="n">
-        <v>-72.82231140136719</v>
+        <v>-82.39275360107422</v>
       </c>
       <c r="M18" t="n">
-        <v>-76.77479553222656</v>
+        <v>-72.28077697753906</v>
       </c>
       <c r="N18" t="n">
-        <v>-74.06636047363281</v>
+        <v>-76.44526672363281</v>
       </c>
       <c r="O18" t="n">
-        <v>-72.00963592529297</v>
+        <v>-81.57005310058594</v>
       </c>
       <c r="P18" t="n">
-        <v>-75.54925537109375</v>
+        <v>-79.78741455078125</v>
       </c>
       <c r="Q18" t="n">
-        <v>-82.24881744384766</v>
+        <v>-82.02322387695312</v>
       </c>
       <c r="R18" t="n">
-        <v>-78.31232452392578</v>
+        <v>-70.65764617919922</v>
       </c>
       <c r="S18" t="n">
-        <v>-78.80725860595703</v>
+        <v>-66.58204650878906</v>
       </c>
       <c r="T18" t="n">
-        <v>-76.83089447021484</v>
+        <v>-67.19918823242188</v>
       </c>
       <c r="U18" t="n">
-        <v>-77.12928771972656</v>
+        <v>-72.55812072753906</v>
       </c>
       <c r="V18" t="n">
-        <v>-74.93341827392578</v>
+        <v>-71.01139068603516</v>
       </c>
       <c r="W18" t="n">
-        <v>-78.90205383300781</v>
+        <v>-68.61624908447266</v>
       </c>
       <c r="X18" t="n">
-        <v>-81.85106658935547</v>
+        <v>-74.5089111328125</v>
       </c>
       <c r="Y18" t="n">
-        <v>-79.16104888916016</v>
+        <v>-74.5421142578125</v>
       </c>
       <c r="Z18" t="n">
-        <v>-81.13334655761719</v>
+        <v>-77.44527435302734</v>
       </c>
       <c r="AA18" t="n">
-        <v>-74.83647155761719</v>
+        <v>-78.48726654052734</v>
       </c>
       <c r="AB18" t="n">
-        <v>-79.18666839599609</v>
+        <v>-71.149658203125</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-66.79032897949219</v>
+        <v>-74.41789245605469</v>
       </c>
       <c r="B19" t="n">
-        <v>-64.10696411132812</v>
+        <v>-73.47636413574219</v>
       </c>
       <c r="C19" t="n">
-        <v>-64.89328002929688</v>
+        <v>-68.04264068603516</v>
       </c>
       <c r="D19" t="n">
-        <v>-68.12860870361328</v>
+        <v>-73.44758605957031</v>
       </c>
       <c r="E19" t="n">
-        <v>-67.15984344482422</v>
+        <v>-69.08865356445312</v>
       </c>
       <c r="F19" t="n">
-        <v>-61.35178756713867</v>
+        <v>-78.30683135986328</v>
       </c>
       <c r="G19" t="n">
-        <v>-72.44985961914062</v>
+        <v>-72.84080505371094</v>
       </c>
       <c r="H19" t="n">
-        <v>-77.168212890625</v>
+        <v>-70.41705322265625</v>
       </c>
       <c r="I19" t="n">
-        <v>-71.77815246582031</v>
+        <v>-77.15754699707031</v>
       </c>
       <c r="J19" t="n">
-        <v>-75.22441101074219</v>
+        <v>-75.369873046875</v>
       </c>
       <c r="K19" t="n">
-        <v>-74.97821044921875</v>
+        <v>-80.79496765136719</v>
       </c>
       <c r="L19" t="n">
-        <v>-65.95177459716797</v>
+        <v>-75.77071380615234</v>
       </c>
       <c r="M19" t="n">
-        <v>-67.24836730957031</v>
+        <v>-73.40704345703125</v>
       </c>
       <c r="N19" t="n">
-        <v>-71.23987579345703</v>
+        <v>-72.61399841308594</v>
       </c>
       <c r="O19" t="n">
-        <v>-74.91899871826172</v>
+        <v>-76.84849548339844</v>
       </c>
       <c r="P19" t="n">
-        <v>-77.96307373046875</v>
+        <v>-81.23288726806641</v>
       </c>
       <c r="Q19" t="n">
-        <v>-77.86849212646484</v>
+        <v>-86.36928558349609</v>
       </c>
       <c r="R19" t="n">
-        <v>-69.42820739746094</v>
+        <v>-78.02260589599609</v>
       </c>
       <c r="S19" t="n">
-        <v>-76.13294982910156</v>
+        <v>-80.96835327148438</v>
       </c>
       <c r="T19" t="n">
-        <v>-76.82802581787109</v>
+        <v>-71.13746643066406</v>
       </c>
       <c r="U19" t="n">
-        <v>-66.33017730712891</v>
+        <v>-69.37747955322266</v>
       </c>
       <c r="V19" t="n">
-        <v>-76.88592529296875</v>
+        <v>-66.08702087402344</v>
       </c>
       <c r="W19" t="n">
-        <v>-76.68323516845703</v>
+        <v>-70.67255401611328</v>
       </c>
       <c r="X19" t="n">
-        <v>-70.59374237060547</v>
+        <v>-72.57991027832031</v>
       </c>
       <c r="Y19" t="n">
-        <v>-74.78986358642578</v>
+        <v>-74.16518402099609</v>
       </c>
       <c r="Z19" t="n">
-        <v>-79.62689208984375</v>
+        <v>-71.53642272949219</v>
       </c>
       <c r="AA19" t="n">
-        <v>-76.61350250244141</v>
+        <v>-76.15592956542969</v>
       </c>
       <c r="AB19" t="n">
-        <v>-74.13700103759766</v>
+        <v>-77.76552581787109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-69.19445037841797</v>
+        <v>-78.13078308105469</v>
       </c>
       <c r="B20" t="n">
-        <v>-70.09120178222656</v>
+        <v>-74.48893737792969</v>
       </c>
       <c r="C20" t="n">
-        <v>-70.62313842773438</v>
+        <v>-75.18788146972656</v>
       </c>
       <c r="D20" t="n">
-        <v>-71.14609527587891</v>
+        <v>-76.584716796875</v>
       </c>
       <c r="E20" t="n">
-        <v>-71.61843109130859</v>
+        <v>-73.81916046142578</v>
       </c>
       <c r="F20" t="n">
-        <v>-74.25933837890625</v>
+        <v>-73.4073486328125</v>
       </c>
       <c r="G20" t="n">
-        <v>-72.73231506347656</v>
+        <v>-76.08621978759766</v>
       </c>
       <c r="H20" t="n">
-        <v>-75.89063262939453</v>
+        <v>-63.05192947387695</v>
       </c>
       <c r="I20" t="n">
-        <v>-65.45096588134766</v>
+        <v>-75.05297088623047</v>
       </c>
       <c r="J20" t="n">
-        <v>-74.48847198486328</v>
+        <v>-78.28858184814453</v>
       </c>
       <c r="K20" t="n">
-        <v>-72.78018951416016</v>
+        <v>-79.66801452636719</v>
       </c>
       <c r="L20" t="n">
-        <v>-67.39141082763672</v>
+        <v>-73.56180572509766</v>
       </c>
       <c r="M20" t="n">
-        <v>-78.24031066894531</v>
+        <v>-79.36619567871094</v>
       </c>
       <c r="N20" t="n">
-        <v>-76.14033508300781</v>
+        <v>-74.29719543457031</v>
       </c>
       <c r="O20" t="n">
-        <v>-72.00341033935547</v>
+        <v>-77.61293029785156</v>
       </c>
       <c r="P20" t="n">
-        <v>-75.53842926025391</v>
+        <v>-76.37906646728516</v>
       </c>
       <c r="Q20" t="n">
-        <v>-76.47935485839844</v>
+        <v>-81.30924987792969</v>
       </c>
       <c r="R20" t="n">
-        <v>-74.31663513183594</v>
+        <v>-75.63078308105469</v>
       </c>
       <c r="S20" t="n">
-        <v>-75.87551879882812</v>
+        <v>-83.06260681152344</v>
       </c>
       <c r="T20" t="n">
-        <v>-78.19466400146484</v>
+        <v>-75.07057952880859</v>
       </c>
       <c r="U20" t="n">
-        <v>-83.08384704589844</v>
+        <v>-66.76954650878906</v>
       </c>
       <c r="V20" t="n">
-        <v>-74.71315002441406</v>
+        <v>-70.70344543457031</v>
       </c>
       <c r="W20" t="n">
-        <v>-79.04471588134766</v>
+        <v>-68.56224060058594</v>
       </c>
       <c r="X20" t="n">
-        <v>-77.32603454589844</v>
+        <v>-69.66465759277344</v>
       </c>
       <c r="Y20" t="n">
-        <v>-82.80864715576172</v>
+        <v>-68.60409545898438</v>
       </c>
       <c r="Z20" t="n">
-        <v>-81.03205871582031</v>
+        <v>-78.17012023925781</v>
       </c>
       <c r="AA20" t="n">
-        <v>-82.28289794921875</v>
+        <v>-68.19345092773438</v>
       </c>
       <c r="AB20" t="n">
-        <v>-74.00713348388672</v>
+        <v>-82.45644378662109</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-62.12210083007812</v>
+        <v>-81.25498962402344</v>
       </c>
       <c r="B21" t="n">
-        <v>-70.75299072265625</v>
+        <v>-76.91462707519531</v>
       </c>
       <c r="C21" t="n">
-        <v>-70.84905242919922</v>
+        <v>-71.46345520019531</v>
       </c>
       <c r="D21" t="n">
-        <v>-66.77519989013672</v>
+        <v>-72.30067443847656</v>
       </c>
       <c r="E21" t="n">
-        <v>-66.59580993652344</v>
+        <v>-75.72108459472656</v>
       </c>
       <c r="F21" t="n">
-        <v>-69.680419921875</v>
+        <v>-75.314453125</v>
       </c>
       <c r="G21" t="n">
-        <v>-68.89514923095703</v>
+        <v>-75.16545104980469</v>
       </c>
       <c r="H21" t="n">
-        <v>-69.98235321044922</v>
+        <v>-75.27019500732422</v>
       </c>
       <c r="I21" t="n">
-        <v>-75.34113311767578</v>
+        <v>-75.78343200683594</v>
       </c>
       <c r="J21" t="n">
-        <v>-72.14625549316406</v>
+        <v>-74.12216186523438</v>
       </c>
       <c r="K21" t="n">
-        <v>-62.98165893554688</v>
+        <v>-77.87333679199219</v>
       </c>
       <c r="L21" t="n">
-        <v>-73.54247283935547</v>
+        <v>-79.26020050048828</v>
       </c>
       <c r="M21" t="n">
-        <v>-76.55788421630859</v>
+        <v>-69.97673797607422</v>
       </c>
       <c r="N21" t="n">
-        <v>-74.85842895507812</v>
+        <v>-71.88005065917969</v>
       </c>
       <c r="O21" t="n">
-        <v>-79.01158905029297</v>
+        <v>-76.9571533203125</v>
       </c>
       <c r="P21" t="n">
-        <v>-77.89040374755859</v>
+        <v>-80.57804870605469</v>
       </c>
       <c r="Q21" t="n">
-        <v>-74.71357727050781</v>
+        <v>-79.56877899169922</v>
       </c>
       <c r="R21" t="n">
-        <v>-76.53818511962891</v>
+        <v>-80.63559722900391</v>
       </c>
       <c r="S21" t="n">
-        <v>-77.53732299804688</v>
+        <v>-77.79786682128906</v>
       </c>
       <c r="T21" t="n">
-        <v>-76.53264617919922</v>
+        <v>-74.81257629394531</v>
       </c>
       <c r="U21" t="n">
-        <v>-78.10859680175781</v>
+        <v>-81.29903411865234</v>
       </c>
       <c r="V21" t="n">
-        <v>-78.47980499267578</v>
+        <v>-72.70610046386719</v>
       </c>
       <c r="W21" t="n">
-        <v>-75.82328796386719</v>
+        <v>-69.62628936767578</v>
       </c>
       <c r="X21" t="n">
-        <v>-81.03277587890625</v>
+        <v>-72.96126556396484</v>
       </c>
       <c r="Y21" t="n">
-        <v>-82.76222229003906</v>
+        <v>-75.46872711181641</v>
       </c>
       <c r="Z21" t="n">
-        <v>-82.00117492675781</v>
+        <v>-71.05309295654297</v>
       </c>
       <c r="AA21" t="n">
-        <v>-75.52079772949219</v>
+        <v>-72.76422882080078</v>
       </c>
       <c r="AB21" t="n">
-        <v>-76.73686218261719</v>
+        <v>-75.57295227050781</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-69.25755310058594</v>
+        <v>-74.26811218261719</v>
       </c>
       <c r="B22" t="n">
-        <v>-69.69868469238281</v>
+        <v>-74.19389343261719</v>
       </c>
       <c r="C22" t="n">
-        <v>-65.98226928710938</v>
+        <v>-72.19647979736328</v>
       </c>
       <c r="D22" t="n">
-        <v>-69.40221405029297</v>
+        <v>-74.61298370361328</v>
       </c>
       <c r="E22" t="n">
-        <v>-68.28675842285156</v>
+        <v>-73.31517028808594</v>
       </c>
       <c r="F22" t="n">
-        <v>-71.6517333984375</v>
+        <v>-75.6357421875</v>
       </c>
       <c r="G22" t="n">
-        <v>-72.18568420410156</v>
+        <v>-78.01568603515625</v>
       </c>
       <c r="H22" t="n">
-        <v>-71.74990844726562</v>
+        <v>-76.47563171386719</v>
       </c>
       <c r="I22" t="n">
-        <v>-77.23043060302734</v>
+        <v>-77.82705688476562</v>
       </c>
       <c r="J22" t="n">
-        <v>-69.07435607910156</v>
+        <v>-79.25778961181641</v>
       </c>
       <c r="K22" t="n">
-        <v>-71.66962432861328</v>
+        <v>-73.12360382080078</v>
       </c>
       <c r="L22" t="n">
-        <v>-74.93039703369141</v>
+        <v>-79.40827941894531</v>
       </c>
       <c r="M22" t="n">
-        <v>-72.94279479980469</v>
+        <v>-75.55934906005859</v>
       </c>
       <c r="N22" t="n">
-        <v>-81.60781097412109</v>
+        <v>-75.06697082519531</v>
       </c>
       <c r="O22" t="n">
-        <v>-79.35658264160156</v>
+        <v>-76.51625823974609</v>
       </c>
       <c r="P22" t="n">
-        <v>-74.35593414306641</v>
+        <v>-79.88783264160156</v>
       </c>
       <c r="Q22" t="n">
-        <v>-77.92617034912109</v>
+        <v>-79.71443939208984</v>
       </c>
       <c r="R22" t="n">
-        <v>-82.39788055419922</v>
+        <v>-80.95819091796875</v>
       </c>
       <c r="S22" t="n">
-        <v>-77.13516998291016</v>
+        <v>-87.47231292724609</v>
       </c>
       <c r="T22" t="n">
-        <v>-77.62151336669922</v>
+        <v>-77.90341949462891</v>
       </c>
       <c r="U22" t="n">
-        <v>-76.65674591064453</v>
+        <v>-84.17408752441406</v>
       </c>
       <c r="V22" t="n">
-        <v>-78.96795654296875</v>
+        <v>-87.38719177246094</v>
       </c>
       <c r="W22" t="n">
-        <v>-77.46343231201172</v>
+        <v>-68.70097351074219</v>
       </c>
       <c r="X22" t="n">
-        <v>-80.07427215576172</v>
+        <v>-71.67454528808594</v>
       </c>
       <c r="Y22" t="n">
-        <v>-77.30654144287109</v>
+        <v>-70.12554168701172</v>
       </c>
       <c r="Z22" t="n">
-        <v>-78.35537719726562</v>
+        <v>-70.05418395996094</v>
       </c>
       <c r="AA22" t="n">
-        <v>-78.97698211669922</v>
+        <v>-74.94514465332031</v>
       </c>
       <c r="AB22" t="n">
-        <v>-79.28042602539062</v>
+        <v>-82.58702850341797</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-70.67171478271484</v>
+        <v>-77.39276123046875</v>
       </c>
       <c r="B23" t="n">
-        <v>-67.84590911865234</v>
+        <v>-83.15900421142578</v>
       </c>
       <c r="C23" t="n">
-        <v>-66.41709136962891</v>
+        <v>-74.92586517333984</v>
       </c>
       <c r="D23" t="n">
-        <v>-77.64425659179688</v>
+        <v>-73.15699768066406</v>
       </c>
       <c r="E23" t="n">
-        <v>-74.07557678222656</v>
+        <v>-75.27000427246094</v>
       </c>
       <c r="F23" t="n">
-        <v>-69.33448791503906</v>
+        <v>-79.62995910644531</v>
       </c>
       <c r="G23" t="n">
-        <v>-78.68180084228516</v>
+        <v>-74.59681701660156</v>
       </c>
       <c r="H23" t="n">
-        <v>-78.31709289550781</v>
+        <v>-73.40852355957031</v>
       </c>
       <c r="I23" t="n">
-        <v>-68.78312683105469</v>
+        <v>-80.91252899169922</v>
       </c>
       <c r="J23" t="n">
-        <v>-79.84613800048828</v>
+        <v>-81.32289123535156</v>
       </c>
       <c r="K23" t="n">
-        <v>-75.21992492675781</v>
+        <v>-77.43226623535156</v>
       </c>
       <c r="L23" t="n">
-        <v>-72.95304870605469</v>
+        <v>-74.85385131835938</v>
       </c>
       <c r="M23" t="n">
-        <v>-78.92469787597656</v>
+        <v>-74.42857360839844</v>
       </c>
       <c r="N23" t="n">
-        <v>-78.29002380371094</v>
+        <v>-77.00340270996094</v>
       </c>
       <c r="O23" t="n">
-        <v>-74.52008056640625</v>
+        <v>-77.91706085205078</v>
       </c>
       <c r="P23" t="n">
-        <v>-74.10645294189453</v>
+        <v>-81.96080017089844</v>
       </c>
       <c r="Q23" t="n">
-        <v>-77.37165832519531</v>
+        <v>-86.45185852050781</v>
       </c>
       <c r="R23" t="n">
-        <v>-74.47071838378906</v>
+        <v>-84.11820220947266</v>
       </c>
       <c r="S23" t="n">
-        <v>-77.70725250244141</v>
+        <v>-82.88856506347656</v>
       </c>
       <c r="T23" t="n">
-        <v>-80.22353363037109</v>
+        <v>-84.94425964355469</v>
       </c>
       <c r="U23" t="n">
-        <v>-82.47676086425781</v>
+        <v>-85.67079162597656</v>
       </c>
       <c r="V23" t="n">
-        <v>-77.35444641113281</v>
+        <v>-87.08745574951172</v>
       </c>
       <c r="W23" t="n">
-        <v>-81.31758117675781</v>
+        <v>-86.90181732177734</v>
       </c>
       <c r="X23" t="n">
-        <v>-83.15696716308594</v>
+        <v>-73.81581115722656</v>
       </c>
       <c r="Y23" t="n">
-        <v>-78.31001281738281</v>
+        <v>-78.70712280273438</v>
       </c>
       <c r="Z23" t="n">
-        <v>-75.73466491699219</v>
+        <v>-70.16224670410156</v>
       </c>
       <c r="AA23" t="n">
-        <v>-80.08025360107422</v>
+        <v>-77.04498291015625</v>
       </c>
       <c r="AB23" t="n">
-        <v>-76.63936614990234</v>
+        <v>-76.87382507324219</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-72.28975677490234</v>
+        <v>-76.67024230957031</v>
       </c>
       <c r="B24" t="n">
-        <v>-73.87991333007812</v>
+        <v>-79.9002685546875</v>
       </c>
       <c r="C24" t="n">
-        <v>-73.07069396972656</v>
+        <v>-74.27772521972656</v>
       </c>
       <c r="D24" t="n">
-        <v>-68.76240539550781</v>
+        <v>-74.14283752441406</v>
       </c>
       <c r="E24" t="n">
-        <v>-69.83753204345703</v>
+        <v>-76.52529144287109</v>
       </c>
       <c r="F24" t="n">
-        <v>-63.77170562744141</v>
+        <v>-74.91453552246094</v>
       </c>
       <c r="G24" t="n">
-        <v>-72.21454620361328</v>
+        <v>-83.20436096191406</v>
       </c>
       <c r="H24" t="n">
-        <v>-67.45508575439453</v>
+        <v>-81.90430450439453</v>
       </c>
       <c r="I24" t="n">
-        <v>-71.37427520751953</v>
+        <v>-82.64316558837891</v>
       </c>
       <c r="J24" t="n">
-        <v>-70.49241638183594</v>
+        <v>-72.14088439941406</v>
       </c>
       <c r="K24" t="n">
-        <v>-74.87916564941406</v>
+        <v>-76.89967346191406</v>
       </c>
       <c r="L24" t="n">
-        <v>-71.18752288818359</v>
+        <v>-75.26759338378906</v>
       </c>
       <c r="M24" t="n">
-        <v>-74.05867767333984</v>
+        <v>-77.96434783935547</v>
       </c>
       <c r="N24" t="n">
-        <v>-78.70590972900391</v>
+        <v>-76.67836761474609</v>
       </c>
       <c r="O24" t="n">
-        <v>-74.71211242675781</v>
+        <v>-82.77848052978516</v>
       </c>
       <c r="P24" t="n">
-        <v>-78.48338317871094</v>
+        <v>-80.51214599609375</v>
       </c>
       <c r="Q24" t="n">
-        <v>-74.11367034912109</v>
+        <v>-81.54441070556641</v>
       </c>
       <c r="R24" t="n">
-        <v>-73.11134338378906</v>
+        <v>-76.419677734375</v>
       </c>
       <c r="S24" t="n">
-        <v>-76.99702453613281</v>
+        <v>-87.37319946289062</v>
       </c>
       <c r="T24" t="n">
-        <v>-81.18013000488281</v>
+        <v>-87.19925689697266</v>
       </c>
       <c r="U24" t="n">
-        <v>-83.44010925292969</v>
+        <v>-79.72039031982422</v>
       </c>
       <c r="V24" t="n">
-        <v>-78.78141021728516</v>
+        <v>-86.14324951171875</v>
       </c>
       <c r="W24" t="n">
-        <v>-80.16419982910156</v>
+        <v>-81.86113739013672</v>
       </c>
       <c r="X24" t="n">
-        <v>-80.34409332275391</v>
+        <v>-81.09801483154297</v>
       </c>
       <c r="Y24" t="n">
-        <v>-79.87696838378906</v>
+        <v>-73.15705108642578</v>
       </c>
       <c r="Z24" t="n">
-        <v>-81.11655426025391</v>
+        <v>-75.04213714599609</v>
       </c>
       <c r="AA24" t="n">
-        <v>-73.86280822753906</v>
+        <v>-75.37068176269531</v>
       </c>
       <c r="AB24" t="n">
-        <v>-81.25486755371094</v>
+        <v>-78.66026306152344</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-76.96535491943359</v>
+        <v>-76.23153686523438</v>
       </c>
       <c r="B25" t="n">
-        <v>-73.96211242675781</v>
+        <v>-72.52291107177734</v>
       </c>
       <c r="C25" t="n">
-        <v>-81.66281890869141</v>
+        <v>-74.42781066894531</v>
       </c>
       <c r="D25" t="n">
-        <v>-75.10211944580078</v>
+        <v>-82.74723815917969</v>
       </c>
       <c r="E25" t="n">
-        <v>-77.15845489501953</v>
+        <v>-76.66915893554688</v>
       </c>
       <c r="F25" t="n">
-        <v>-75.3392333984375</v>
+        <v>-76.73323059082031</v>
       </c>
       <c r="G25" t="n">
-        <v>-68.05390167236328</v>
+        <v>-81.51185607910156</v>
       </c>
       <c r="H25" t="n">
-        <v>-73.54861450195312</v>
+        <v>-76.85637664794922</v>
       </c>
       <c r="I25" t="n">
-        <v>-69.27752685546875</v>
+        <v>-76.03464508056641</v>
       </c>
       <c r="J25" t="n">
-        <v>-70.64653015136719</v>
+        <v>-79.20720672607422</v>
       </c>
       <c r="K25" t="n">
-        <v>-71.29738616943359</v>
+        <v>-79.09215545654297</v>
       </c>
       <c r="L25" t="n">
-        <v>-74.25828552246094</v>
+        <v>-79.52674102783203</v>
       </c>
       <c r="M25" t="n">
-        <v>-71.589599609375</v>
+        <v>-77.28958892822266</v>
       </c>
       <c r="N25" t="n">
-        <v>-71.18199157714844</v>
+        <v>-78.24336242675781</v>
       </c>
       <c r="O25" t="n">
-        <v>-82.20220947265625</v>
+        <v>-84.74198150634766</v>
       </c>
       <c r="P25" t="n">
-        <v>-80.72805023193359</v>
+        <v>-79.45770263671875</v>
       </c>
       <c r="Q25" t="n">
-        <v>-77.22388458251953</v>
+        <v>-87.35588836669922</v>
       </c>
       <c r="R25" t="n">
-        <v>-81.35929107666016</v>
+        <v>-82.26923370361328</v>
       </c>
       <c r="S25" t="n">
-        <v>-78.64192199707031</v>
+        <v>-87.75522613525391</v>
       </c>
       <c r="T25" t="n">
-        <v>-80.66094970703125</v>
+        <v>-85.86707305908203</v>
       </c>
       <c r="U25" t="n">
-        <v>-87.48114013671875</v>
+        <v>-85.23875427246094</v>
       </c>
       <c r="V25" t="n">
-        <v>-80.90873718261719</v>
+        <v>-85.22197723388672</v>
       </c>
       <c r="W25" t="n">
-        <v>-82.14198303222656</v>
+        <v>-87.51824951171875</v>
       </c>
       <c r="X25" t="n">
-        <v>-80.822998046875</v>
+        <v>-81.37672424316406</v>
       </c>
       <c r="Y25" t="n">
-        <v>-79.74330902099609</v>
+        <v>-90.94090270996094</v>
       </c>
       <c r="Z25" t="n">
-        <v>-87.62091827392578</v>
+        <v>-77.40787506103516</v>
       </c>
       <c r="AA25" t="n">
-        <v>-81.56092834472656</v>
+        <v>-75.83223724365234</v>
       </c>
       <c r="AB25" t="n">
-        <v>-87.49952697753906</v>
+        <v>-75.01430511474609</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-69.78599548339844</v>
+        <v>-74.29132843017578</v>
       </c>
       <c r="B26" t="n">
-        <v>-73.35579681396484</v>
+        <v>-80.24071502685547</v>
       </c>
       <c r="C26" t="n">
-        <v>-71.23817443847656</v>
+        <v>-77.15879821777344</v>
       </c>
       <c r="D26" t="n">
-        <v>-77.42616271972656</v>
+        <v>-76.77176666259766</v>
       </c>
       <c r="E26" t="n">
-        <v>-78.60507965087891</v>
+        <v>-78.02944946289062</v>
       </c>
       <c r="F26" t="n">
-        <v>-80.22845458984375</v>
+        <v>-81.79370880126953</v>
       </c>
       <c r="G26" t="n">
-        <v>-72.73954772949219</v>
+        <v>-78.412841796875</v>
       </c>
       <c r="H26" t="n">
-        <v>-71.75951385498047</v>
+        <v>-80.414306640625</v>
       </c>
       <c r="I26" t="n">
-        <v>-67.08115386962891</v>
+        <v>-77.97597503662109</v>
       </c>
       <c r="J26" t="n">
-        <v>-68.78702545166016</v>
+        <v>-78.37715911865234</v>
       </c>
       <c r="K26" t="n">
-        <v>-70.5531005859375</v>
+        <v>-81.33338928222656</v>
       </c>
       <c r="L26" t="n">
-        <v>-73.90074157714844</v>
+        <v>-66.50273132324219</v>
       </c>
       <c r="M26" t="n">
-        <v>-79.98403167724609</v>
+        <v>-77.17381286621094</v>
       </c>
       <c r="N26" t="n">
-        <v>-72.69625091552734</v>
+        <v>-76.94549560546875</v>
       </c>
       <c r="O26" t="n">
-        <v>-87.54194641113281</v>
+        <v>-88.76499938964844</v>
       </c>
       <c r="P26" t="n">
-        <v>-73.49961853027344</v>
+        <v>-82.71668243408203</v>
       </c>
       <c r="Q26" t="n">
-        <v>-72.21620178222656</v>
+        <v>-83.26509857177734</v>
       </c>
       <c r="R26" t="n">
-        <v>-75.87650299072266</v>
+        <v>-86.57534790039062</v>
       </c>
       <c r="S26" t="n">
-        <v>-75.92710876464844</v>
+        <v>-85.53096771240234</v>
       </c>
       <c r="T26" t="n">
-        <v>-75.54086303710938</v>
+        <v>-85.93826293945312</v>
       </c>
       <c r="U26" t="n">
-        <v>-79.90215301513672</v>
+        <v>-82.84851837158203</v>
       </c>
       <c r="V26" t="n">
-        <v>-79.15306854248047</v>
+        <v>-86.25467681884766</v>
       </c>
       <c r="W26" t="n">
-        <v>-83.31874847412109</v>
+        <v>-87.52857971191406</v>
       </c>
       <c r="X26" t="n">
-        <v>-84.93759918212891</v>
+        <v>-89.84626007080078</v>
       </c>
       <c r="Y26" t="n">
-        <v>-81.24549865722656</v>
+        <v>-88.46855926513672</v>
       </c>
       <c r="Z26" t="n">
-        <v>-76.14341735839844</v>
+        <v>-88.92632293701172</v>
       </c>
       <c r="AA26" t="n">
-        <v>-79.16107940673828</v>
+        <v>-72.06128692626953</v>
       </c>
       <c r="AB26" t="n">
-        <v>-77.56710052490234</v>
+        <v>-79.03414154052734</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-70.2303466796875</v>
+        <v>-80.49584197998047</v>
       </c>
       <c r="B27" t="n">
-        <v>-70.01722717285156</v>
+        <v>-78.48761749267578</v>
       </c>
       <c r="C27" t="n">
-        <v>-71.91423034667969</v>
+        <v>-76.74382019042969</v>
       </c>
       <c r="D27" t="n">
-        <v>-70.12435913085938</v>
+        <v>-73.02796936035156</v>
       </c>
       <c r="E27" t="n">
-        <v>-69.56826019287109</v>
+        <v>-77.58210754394531</v>
       </c>
       <c r="F27" t="n">
-        <v>-73.55956268310547</v>
+        <v>-80.16930389404297</v>
       </c>
       <c r="G27" t="n">
-        <v>-77.85215759277344</v>
+        <v>-86.05076599121094</v>
       </c>
       <c r="H27" t="n">
-        <v>-73.20261383056641</v>
+        <v>-75.11082458496094</v>
       </c>
       <c r="I27" t="n">
-        <v>-69.56729125976562</v>
+        <v>-78.75054168701172</v>
       </c>
       <c r="J27" t="n">
-        <v>-66.50942993164062</v>
+        <v>-78.99031829833984</v>
       </c>
       <c r="K27" t="n">
-        <v>-78.52232360839844</v>
+        <v>-78.73844909667969</v>
       </c>
       <c r="L27" t="n">
-        <v>-78.84803771972656</v>
+        <v>-78.65528106689453</v>
       </c>
       <c r="M27" t="n">
-        <v>-75.43662261962891</v>
+        <v>-75.02451324462891</v>
       </c>
       <c r="N27" t="n">
-        <v>-69.69560241699219</v>
+        <v>-74.71725463867188</v>
       </c>
       <c r="O27" t="n">
-        <v>-80.03865051269531</v>
+        <v>-84.08021545410156</v>
       </c>
       <c r="P27" t="n">
-        <v>-75.62673950195312</v>
+        <v>-83.62667083740234</v>
       </c>
       <c r="Q27" t="n">
-        <v>-73.30067443847656</v>
+        <v>-84.29795837402344</v>
       </c>
       <c r="R27" t="n">
-        <v>-73.36811828613281</v>
+        <v>-83.70762634277344</v>
       </c>
       <c r="S27" t="n">
-        <v>-79.48434448242188</v>
+        <v>-83.39666748046875</v>
       </c>
       <c r="T27" t="n">
-        <v>-78.21255493164062</v>
+        <v>-87.91719818115234</v>
       </c>
       <c r="U27" t="n">
-        <v>-79.93997955322266</v>
+        <v>-81.22193145751953</v>
       </c>
       <c r="V27" t="n">
-        <v>-82.44227600097656</v>
+        <v>-88.93115234375</v>
       </c>
       <c r="W27" t="n">
-        <v>-86.32475280761719</v>
+        <v>-88.05735778808594</v>
       </c>
       <c r="X27" t="n">
-        <v>-82.90274810791016</v>
+        <v>-82.34342956542969</v>
       </c>
       <c r="Y27" t="n">
-        <v>-82.01158142089844</v>
+        <v>-84.57770538330078</v>
       </c>
       <c r="Z27" t="n">
-        <v>-83.44252777099609</v>
+        <v>-85.90391540527344</v>
       </c>
       <c r="AA27" t="n">
-        <v>-77.96221160888672</v>
+        <v>-85.10020446777344</v>
       </c>
       <c r="AB27" t="n">
-        <v>-83.16851806640625</v>
+        <v>-79.46134185791016</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-66.10008239746094</v>
+        <v>-76.22833251953125</v>
       </c>
       <c r="B28" t="n">
-        <v>-75.39016723632812</v>
+        <v>-72.55656433105469</v>
       </c>
       <c r="C28" t="n">
-        <v>-70.81501007080078</v>
+        <v>-77.59907531738281</v>
       </c>
       <c r="D28" t="n">
-        <v>-70.39385986328125</v>
+        <v>-79.01795959472656</v>
       </c>
       <c r="E28" t="n">
-        <v>-71.29540252685547</v>
+        <v>-78.68472290039062</v>
       </c>
       <c r="F28" t="n">
-        <v>-69.95278930664062</v>
+        <v>-80.22959899902344</v>
       </c>
       <c r="G28" t="n">
-        <v>-71.95045471191406</v>
+        <v>-76.28404235839844</v>
       </c>
       <c r="H28" t="n">
-        <v>-66.83616638183594</v>
+        <v>-78.40287780761719</v>
       </c>
       <c r="I28" t="n">
-        <v>-74.11933898925781</v>
+        <v>-81.43287658691406</v>
       </c>
       <c r="J28" t="n">
-        <v>-73.35271453857422</v>
+        <v>-74.13648986816406</v>
       </c>
       <c r="K28" t="n">
-        <v>-80.23941040039062</v>
+        <v>-79.97368621826172</v>
       </c>
       <c r="L28" t="n">
-        <v>-76.6512451171875</v>
+        <v>-81.86325836181641</v>
       </c>
       <c r="M28" t="n">
-        <v>-74.43103790283203</v>
+        <v>-84.93480682373047</v>
       </c>
       <c r="N28" t="n">
-        <v>-81.12487030029297</v>
+        <v>-77.77055358886719</v>
       </c>
       <c r="O28" t="n">
-        <v>-80.79627990722656</v>
+        <v>-74.91010284423828</v>
       </c>
       <c r="P28" t="n">
-        <v>-70.17593383789062</v>
+        <v>-86.13667297363281</v>
       </c>
       <c r="Q28" t="n">
-        <v>-82.41963958740234</v>
+        <v>-84.73651123046875</v>
       </c>
       <c r="R28" t="n">
-        <v>-78.68148040771484</v>
+        <v>-81.89016723632812</v>
       </c>
       <c r="S28" t="n">
-        <v>-78.21324157714844</v>
+        <v>-86.90323638916016</v>
       </c>
       <c r="T28" t="n">
-        <v>-80.35884094238281</v>
+        <v>-89.05724334716797</v>
       </c>
       <c r="U28" t="n">
-        <v>-80.75150299072266</v>
+        <v>-80.47806549072266</v>
       </c>
       <c r="V28" t="n">
-        <v>-81.73692321777344</v>
+        <v>-83.67282867431641</v>
       </c>
       <c r="W28" t="n">
-        <v>-82.49492645263672</v>
+        <v>-82.46327209472656</v>
       </c>
       <c r="X28" t="n">
-        <v>-84.84702301025391</v>
+        <v>-80.32495880126953</v>
       </c>
       <c r="Y28" t="n">
-        <v>-82.91275024414062</v>
+        <v>-89.03594970703125</v>
       </c>
       <c r="Z28" t="n">
-        <v>-84.71062469482422</v>
+        <v>-83.90570831298828</v>
       </c>
       <c r="AA28" t="n">
-        <v>-77.98387145996094</v>
+        <v>-89.82203674316406</v>
       </c>
       <c r="AB28" t="n">
-        <v>-76.26722717285156</v>
+        <v>-82.16972351074219</v>
       </c>
     </row>
   </sheetData>

--- a/writerConference/rssi_output.xlsx
+++ b/writerConference/rssi_output.xlsx
@@ -2841,2410 +2841,2410 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>-33.7098503112793</v>
+        <v>-29.54437828063965</v>
       </c>
       <c r="B1" t="n">
-        <v>-29.36517333984375</v>
+        <v>-35.09778213500977</v>
       </c>
       <c r="C1" t="n">
-        <v>-44.56256484985352</v>
+        <v>-41.01274871826172</v>
       </c>
       <c r="D1" t="n">
-        <v>-41.69289398193359</v>
+        <v>-42.41579055786133</v>
       </c>
       <c r="E1" t="n">
-        <v>-46.05231857299805</v>
+        <v>-46.1126823425293</v>
       </c>
       <c r="F1" t="n">
-        <v>-44.3223762512207</v>
+        <v>-52.49204635620117</v>
       </c>
       <c r="G1" t="n">
-        <v>-53.7462158203125</v>
+        <v>-62.20493316650391</v>
       </c>
       <c r="H1" t="n">
-        <v>-56.12018585205078</v>
+        <v>-57.30550384521484</v>
       </c>
       <c r="I1" t="n">
-        <v>-55.15571212768555</v>
+        <v>-57.74993896484375</v>
       </c>
       <c r="J1" t="n">
-        <v>-63.62122344970703</v>
+        <v>-63.20989990234375</v>
       </c>
       <c r="K1" t="n">
-        <v>-57.8695182800293</v>
+        <v>-60.74666213989258</v>
       </c>
       <c r="L1" t="n">
-        <v>-63.17186737060547</v>
+        <v>-60.6839714050293</v>
       </c>
       <c r="M1" t="n">
-        <v>-67.51364135742188</v>
+        <v>-60.12469482421875</v>
       </c>
       <c r="N1" t="n">
-        <v>-65.44786834716797</v>
+        <v>-63.78755950927734</v>
       </c>
       <c r="O1" t="n">
-        <v>-68.09762573242188</v>
+        <v>-63.51335525512695</v>
       </c>
       <c r="P1" t="n">
-        <v>-64.08045196533203</v>
+        <v>-68.05302429199219</v>
       </c>
       <c r="Q1" t="n">
-        <v>-71.36520385742188</v>
+        <v>-69.68775939941406</v>
       </c>
       <c r="R1" t="n">
-        <v>-67.76979064941406</v>
+        <v>-77.74272155761719</v>
       </c>
       <c r="S1" t="n">
-        <v>-66.32881927490234</v>
+        <v>-68.48191070556641</v>
       </c>
       <c r="T1" t="n">
-        <v>-65.18865966796875</v>
+        <v>-68.33390808105469</v>
       </c>
       <c r="U1" t="n">
-        <v>-63.65459060668945</v>
+        <v>-73.78950500488281</v>
       </c>
       <c r="V1" t="n">
-        <v>-66.86631011962891</v>
+        <v>-77.72330474853516</v>
       </c>
       <c r="W1" t="n">
-        <v>-69.75447082519531</v>
+        <v>-69.94468688964844</v>
       </c>
       <c r="X1" t="n">
-        <v>-70.02456665039062</v>
+        <v>-75.05682373046875</v>
       </c>
       <c r="Y1" t="n">
-        <v>-68.05355072021484</v>
+        <v>-76.90386199951172</v>
       </c>
       <c r="Z1" t="n">
-        <v>-67.30155944824219</v>
+        <v>-75.89933776855469</v>
       </c>
       <c r="AA1" t="n">
-        <v>-71.46757507324219</v>
+        <v>-75.65846252441406</v>
       </c>
       <c r="AB1" t="n">
-        <v>-75.35781860351562</v>
+        <v>-75.3387451171875</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-30.85965919494629</v>
+        <v>-36.37484359741211</v>
       </c>
       <c r="B2" t="n">
-        <v>-36.96942520141602</v>
+        <v>-38.46696090698242</v>
       </c>
       <c r="C2" t="n">
-        <v>-41.33854293823242</v>
+        <v>-44.7988166809082</v>
       </c>
       <c r="D2" t="n">
-        <v>-41.73123931884766</v>
+        <v>-50.35476303100586</v>
       </c>
       <c r="E2" t="n">
-        <v>-51.06521606445312</v>
+        <v>-48.74587249755859</v>
       </c>
       <c r="F2" t="n">
-        <v>-51.75798797607422</v>
+        <v>-53.66500091552734</v>
       </c>
       <c r="G2" t="n">
-        <v>-59.0772819519043</v>
+        <v>-53.6481819152832</v>
       </c>
       <c r="H2" t="n">
-        <v>-57.61019897460938</v>
+        <v>-59.8607177734375</v>
       </c>
       <c r="I2" t="n">
-        <v>-55.0056266784668</v>
+        <v>-51.56760406494141</v>
       </c>
       <c r="J2" t="n">
-        <v>-58.08489990234375</v>
+        <v>-55.54486083984375</v>
       </c>
       <c r="K2" t="n">
-        <v>-63.36257171630859</v>
+        <v>-58.60979461669922</v>
       </c>
       <c r="L2" t="n">
-        <v>-59.57459259033203</v>
+        <v>-63.21550750732422</v>
       </c>
       <c r="M2" t="n">
-        <v>-65.30979156494141</v>
+        <v>-65.6240234375</v>
       </c>
       <c r="N2" t="n">
-        <v>-64.82060241699219</v>
+        <v>-64.44802093505859</v>
       </c>
       <c r="O2" t="n">
-        <v>-62.64388275146484</v>
+        <v>-70.02189636230469</v>
       </c>
       <c r="P2" t="n">
-        <v>-62.96048736572266</v>
+        <v>-68.05671691894531</v>
       </c>
       <c r="Q2" t="n">
-        <v>-66.68401336669922</v>
+        <v>-71.44490051269531</v>
       </c>
       <c r="R2" t="n">
-        <v>-63.84293365478516</v>
+        <v>-64.06539154052734</v>
       </c>
       <c r="S2" t="n">
-        <v>-62.73199462890625</v>
+        <v>-71.24034118652344</v>
       </c>
       <c r="T2" t="n">
-        <v>-73.34713745117188</v>
+        <v>-72.27819061279297</v>
       </c>
       <c r="U2" t="n">
-        <v>-67.17170715332031</v>
+        <v>-75.3365478515625</v>
       </c>
       <c r="V2" t="n">
-        <v>-68.99310302734375</v>
+        <v>-73.19606018066406</v>
       </c>
       <c r="W2" t="n">
-        <v>-70.39007568359375</v>
+        <v>-75.32147216796875</v>
       </c>
       <c r="X2" t="n">
-        <v>-70.7625732421875</v>
+        <v>-74.86286926269531</v>
       </c>
       <c r="Y2" t="n">
-        <v>-76.14750671386719</v>
+        <v>-78.84580993652344</v>
       </c>
       <c r="Z2" t="n">
-        <v>-75.00096130371094</v>
+        <v>-77.59410858154297</v>
       </c>
       <c r="AA2" t="n">
-        <v>-70.79287719726562</v>
+        <v>-75.27999114990234</v>
       </c>
       <c r="AB2" t="n">
-        <v>-75.02851104736328</v>
+        <v>-72.82197570800781</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-38.23548126220703</v>
+        <v>-43.41970062255859</v>
       </c>
       <c r="B3" t="n">
-        <v>-39.13436126708984</v>
+        <v>-41.01880645751953</v>
       </c>
       <c r="C3" t="n">
-        <v>-37.41079330444336</v>
+        <v>-42.00269317626953</v>
       </c>
       <c r="D3" t="n">
-        <v>-52.24956512451172</v>
+        <v>-48.01739883422852</v>
       </c>
       <c r="E3" t="n">
-        <v>-52.27462768554688</v>
+        <v>-50.64441680908203</v>
       </c>
       <c r="F3" t="n">
-        <v>-55.68167877197266</v>
+        <v>-53.39120483398438</v>
       </c>
       <c r="G3" t="n">
-        <v>-52.0781135559082</v>
+        <v>-58.32489776611328</v>
       </c>
       <c r="H3" t="n">
-        <v>-57.10161209106445</v>
+        <v>-52.07361602783203</v>
       </c>
       <c r="I3" t="n">
-        <v>-51.69345855712891</v>
+        <v>-55.20713043212891</v>
       </c>
       <c r="J3" t="n">
-        <v>-61.1893196105957</v>
+        <v>-57.81122970581055</v>
       </c>
       <c r="K3" t="n">
-        <v>-55.89912033081055</v>
+        <v>-59.76673126220703</v>
       </c>
       <c r="L3" t="n">
-        <v>-64.31955718994141</v>
+        <v>-67.95746612548828</v>
       </c>
       <c r="M3" t="n">
-        <v>-60.7296257019043</v>
+        <v>-59.70587158203125</v>
       </c>
       <c r="N3" t="n">
-        <v>-62.29038619995117</v>
+        <v>-68.75422668457031</v>
       </c>
       <c r="O3" t="n">
-        <v>-59.91478729248047</v>
+        <v>-72.50413513183594</v>
       </c>
       <c r="P3" t="n">
-        <v>-65.24606323242188</v>
+        <v>-68.45909881591797</v>
       </c>
       <c r="Q3" t="n">
-        <v>-62.96253204345703</v>
+        <v>-63.7124137878418</v>
       </c>
       <c r="R3" t="n">
-        <v>-67.14942932128906</v>
+        <v>-73.39876556396484</v>
       </c>
       <c r="S3" t="n">
-        <v>-60.48241424560547</v>
+        <v>-67.73902893066406</v>
       </c>
       <c r="T3" t="n">
-        <v>-72.95016479492188</v>
+        <v>-69.25592041015625</v>
       </c>
       <c r="U3" t="n">
-        <v>-68.528076171875</v>
+        <v>-74.91688537597656</v>
       </c>
       <c r="V3" t="n">
-        <v>-72.83042907714844</v>
+        <v>-73.96766662597656</v>
       </c>
       <c r="W3" t="n">
-        <v>-68.66171264648438</v>
+        <v>-75.2691650390625</v>
       </c>
       <c r="X3" t="n">
-        <v>-67.11366271972656</v>
+        <v>-74.10276794433594</v>
       </c>
       <c r="Y3" t="n">
-        <v>-67.27769470214844</v>
+        <v>-76.21791839599609</v>
       </c>
       <c r="Z3" t="n">
-        <v>-67.19422912597656</v>
+        <v>-77.51340484619141</v>
       </c>
       <c r="AA3" t="n">
-        <v>-71.64076232910156</v>
+        <v>-75.91716766357422</v>
       </c>
       <c r="AB3" t="n">
-        <v>-77.34688568115234</v>
+        <v>-81.95646667480469</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-35.23579788208008</v>
+        <v>-42.06691741943359</v>
       </c>
       <c r="B4" t="n">
-        <v>-44.68349456787109</v>
+        <v>-45.3929328918457</v>
       </c>
       <c r="C4" t="n">
-        <v>-46.83379745483398</v>
+        <v>-47.88335418701172</v>
       </c>
       <c r="D4" t="n">
-        <v>-47.07064056396484</v>
+        <v>-48.65499114990234</v>
       </c>
       <c r="E4" t="n">
-        <v>-45.09615325927734</v>
+        <v>-51.37503814697266</v>
       </c>
       <c r="F4" t="n">
-        <v>-48.94282531738281</v>
+        <v>-55.06383514404297</v>
       </c>
       <c r="G4" t="n">
-        <v>-59.63515472412109</v>
+        <v>-53.37709808349609</v>
       </c>
       <c r="H4" t="n">
-        <v>-65.88605499267578</v>
+        <v>-56.39413452148438</v>
       </c>
       <c r="I4" t="n">
-        <v>-53.63178634643555</v>
+        <v>-54.93974685668945</v>
       </c>
       <c r="J4" t="n">
-        <v>-61.3350715637207</v>
+        <v>-58.98735427856445</v>
       </c>
       <c r="K4" t="n">
-        <v>-62.65914916992188</v>
+        <v>-62.66041946411133</v>
       </c>
       <c r="L4" t="n">
-        <v>-56.07980346679688</v>
+        <v>-59.360107421875</v>
       </c>
       <c r="M4" t="n">
-        <v>-66.48919677734375</v>
+        <v>-58.74775314331055</v>
       </c>
       <c r="N4" t="n">
-        <v>-65.94012451171875</v>
+        <v>-69.63628387451172</v>
       </c>
       <c r="O4" t="n">
-        <v>-62.69511795043945</v>
+        <v>-68.71076965332031</v>
       </c>
       <c r="P4" t="n">
-        <v>-69.62189483642578</v>
+        <v>-66.30245208740234</v>
       </c>
       <c r="Q4" t="n">
-        <v>-63.83585739135742</v>
+        <v>-74.60622406005859</v>
       </c>
       <c r="R4" t="n">
-        <v>-63.78070068359375</v>
+        <v>-65.97151184082031</v>
       </c>
       <c r="S4" t="n">
-        <v>-69.29508209228516</v>
+        <v>-71.87339782714844</v>
       </c>
       <c r="T4" t="n">
-        <v>-71.72329711914062</v>
+        <v>-71.088134765625</v>
       </c>
       <c r="U4" t="n">
-        <v>-63.38232421875</v>
+        <v>-76.19334411621094</v>
       </c>
       <c r="V4" t="n">
-        <v>-72.17885589599609</v>
+        <v>-76.51402282714844</v>
       </c>
       <c r="W4" t="n">
-        <v>-63.01203155517578</v>
+        <v>-77.23451232910156</v>
       </c>
       <c r="X4" t="n">
-        <v>-66.27363586425781</v>
+        <v>-77.13478088378906</v>
       </c>
       <c r="Y4" t="n">
-        <v>-71.26071929931641</v>
+        <v>-75.2021484375</v>
       </c>
       <c r="Z4" t="n">
-        <v>-76.22398376464844</v>
+        <v>-74.92509460449219</v>
       </c>
       <c r="AA4" t="n">
-        <v>-68.18739318847656</v>
+        <v>-76.43038177490234</v>
       </c>
       <c r="AB4" t="n">
-        <v>-74.59661102294922</v>
+        <v>-75.56085968017578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-47.60088729858398</v>
+        <v>-50.16460418701172</v>
       </c>
       <c r="B5" t="n">
-        <v>-47.15861129760742</v>
+        <v>-46.64916610717773</v>
       </c>
       <c r="C5" t="n">
-        <v>-45.10218048095703</v>
+        <v>-55.9818229675293</v>
       </c>
       <c r="D5" t="n">
-        <v>-47.25439071655273</v>
+        <v>-58.77095413208008</v>
       </c>
       <c r="E5" t="n">
-        <v>-48.21390914916992</v>
+        <v>-53.42831420898438</v>
       </c>
       <c r="F5" t="n">
-        <v>-51.10880279541016</v>
+        <v>-57.83133697509766</v>
       </c>
       <c r="G5" t="n">
-        <v>-56.2523307800293</v>
+        <v>-60.41475296020508</v>
       </c>
       <c r="H5" t="n">
-        <v>-60.5600700378418</v>
+        <v>-58.34879684448242</v>
       </c>
       <c r="I5" t="n">
-        <v>-66.45044708251953</v>
+        <v>-58.86350250244141</v>
       </c>
       <c r="J5" t="n">
-        <v>-66.66381072998047</v>
+        <v>-68.05470275878906</v>
       </c>
       <c r="K5" t="n">
-        <v>-64.53769683837891</v>
+        <v>-62.17134475708008</v>
       </c>
       <c r="L5" t="n">
-        <v>-66.48809814453125</v>
+        <v>-65.17490386962891</v>
       </c>
       <c r="M5" t="n">
-        <v>-66.71400451660156</v>
+        <v>-64.36906433105469</v>
       </c>
       <c r="N5" t="n">
-        <v>-64.395751953125</v>
+        <v>-69.65180206298828</v>
       </c>
       <c r="O5" t="n">
-        <v>-70.25916290283203</v>
+        <v>-64.45137023925781</v>
       </c>
       <c r="P5" t="n">
-        <v>-66.51358795166016</v>
+        <v>-69.39357757568359</v>
       </c>
       <c r="Q5" t="n">
-        <v>-69.20713806152344</v>
+        <v>-66.52571868896484</v>
       </c>
       <c r="R5" t="n">
-        <v>-73.30071258544922</v>
+        <v>-71.69207000732422</v>
       </c>
       <c r="S5" t="n">
-        <v>-68.76321411132812</v>
+        <v>-74.69950103759766</v>
       </c>
       <c r="T5" t="n">
-        <v>-64.04213714599609</v>
+        <v>-73.35207366943359</v>
       </c>
       <c r="U5" t="n">
-        <v>-67.09999847412109</v>
+        <v>-67.23939514160156</v>
       </c>
       <c r="V5" t="n">
-        <v>-69.40083312988281</v>
+        <v>-72.7122802734375</v>
       </c>
       <c r="W5" t="n">
-        <v>-74.05891418457031</v>
+        <v>-74.28065490722656</v>
       </c>
       <c r="X5" t="n">
-        <v>-69.41868591308594</v>
+        <v>-77.54673004150391</v>
       </c>
       <c r="Y5" t="n">
-        <v>-69.32427978515625</v>
+        <v>-72.62503814697266</v>
       </c>
       <c r="Z5" t="n">
-        <v>-73.94447326660156</v>
+        <v>-74.48170471191406</v>
       </c>
       <c r="AA5" t="n">
-        <v>-68.78302001953125</v>
+        <v>-78.1944580078125</v>
       </c>
       <c r="AB5" t="n">
-        <v>-66.93858337402344</v>
+        <v>-81.85810089111328</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-52.53848266601562</v>
+        <v>-51.39049530029297</v>
       </c>
       <c r="B6" t="n">
-        <v>-46.83024215698242</v>
+        <v>-52.04323196411133</v>
       </c>
       <c r="C6" t="n">
-        <v>-53.2105712890625</v>
+        <v>-52.97794723510742</v>
       </c>
       <c r="D6" t="n">
-        <v>-49.6555061340332</v>
+        <v>-50.86052703857422</v>
       </c>
       <c r="E6" t="n">
-        <v>-54.37044143676758</v>
+        <v>-55.48836517333984</v>
       </c>
       <c r="F6" t="n">
-        <v>-58.95313262939453</v>
+        <v>-59.66237258911133</v>
       </c>
       <c r="G6" t="n">
-        <v>-63.35646820068359</v>
+        <v>-57.68551635742188</v>
       </c>
       <c r="H6" t="n">
-        <v>-56.32136154174805</v>
+        <v>-59.84402465820312</v>
       </c>
       <c r="I6" t="n">
-        <v>-59.92595672607422</v>
+        <v>-58.93107986450195</v>
       </c>
       <c r="J6" t="n">
-        <v>-59.96498870849609</v>
+        <v>-62.17662811279297</v>
       </c>
       <c r="K6" t="n">
-        <v>-59.31481170654297</v>
+        <v>-65.41178131103516</v>
       </c>
       <c r="L6" t="n">
-        <v>-66.0804443359375</v>
+        <v>-64.20021057128906</v>
       </c>
       <c r="M6" t="n">
-        <v>-59.77975463867188</v>
+        <v>-66.98896789550781</v>
       </c>
       <c r="N6" t="n">
-        <v>-65.30616760253906</v>
+        <v>-66.24797821044922</v>
       </c>
       <c r="O6" t="n">
-        <v>-76.65522766113281</v>
+        <v>-74.86843109130859</v>
       </c>
       <c r="P6" t="n">
-        <v>-69.71105194091797</v>
+        <v>-65.75113677978516</v>
       </c>
       <c r="Q6" t="n">
-        <v>-66.25959777832031</v>
+        <v>-69.96537017822266</v>
       </c>
       <c r="R6" t="n">
-        <v>-68.55277252197266</v>
+        <v>-75.50553894042969</v>
       </c>
       <c r="S6" t="n">
-        <v>-64.92787170410156</v>
+        <v>-66.23889923095703</v>
       </c>
       <c r="T6" t="n">
-        <v>-70.91484832763672</v>
+        <v>-71.11891937255859</v>
       </c>
       <c r="U6" t="n">
-        <v>-75.66230010986328</v>
+        <v>-71.88450622558594</v>
       </c>
       <c r="V6" t="n">
-        <v>-70.07126617431641</v>
+        <v>-79.20449829101562</v>
       </c>
       <c r="W6" t="n">
-        <v>-74.82609558105469</v>
+        <v>-80.64820098876953</v>
       </c>
       <c r="X6" t="n">
-        <v>-69.87010192871094</v>
+        <v>-77.52734375</v>
       </c>
       <c r="Y6" t="n">
-        <v>-76.08921813964844</v>
+        <v>-80.67929840087891</v>
       </c>
       <c r="Z6" t="n">
-        <v>-75.25812530517578</v>
+        <v>-72.54777526855469</v>
       </c>
       <c r="AA6" t="n">
-        <v>-77.64463806152344</v>
+        <v>-80.16984558105469</v>
       </c>
       <c r="AB6" t="n">
-        <v>-72.55345153808594</v>
+        <v>-85.80372619628906</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-57.21350860595703</v>
+        <v>-52.26765060424805</v>
       </c>
       <c r="B7" t="n">
-        <v>-53.22647857666016</v>
+        <v>-57.50865936279297</v>
       </c>
       <c r="C7" t="n">
-        <v>-58.71112060546875</v>
+        <v>-53.4208984375</v>
       </c>
       <c r="D7" t="n">
-        <v>-62.22270584106445</v>
+        <v>-54.9112434387207</v>
       </c>
       <c r="E7" t="n">
-        <v>-56.24955368041992</v>
+        <v>-61.71776580810547</v>
       </c>
       <c r="F7" t="n">
-        <v>-58.65511322021484</v>
+        <v>-54.57615280151367</v>
       </c>
       <c r="G7" t="n">
-        <v>-55.0084114074707</v>
+        <v>-54.30014801025391</v>
       </c>
       <c r="H7" t="n">
-        <v>-62.55127716064453</v>
+        <v>-60.76111602783203</v>
       </c>
       <c r="I7" t="n">
-        <v>-61.8798942565918</v>
+        <v>-62.1512565612793</v>
       </c>
       <c r="J7" t="n">
-        <v>-68.58695220947266</v>
+        <v>-61.00127410888672</v>
       </c>
       <c r="K7" t="n">
-        <v>-65.03408813476562</v>
+        <v>-68.68573760986328</v>
       </c>
       <c r="L7" t="n">
-        <v>-65.45881652832031</v>
+        <v>-65.96830749511719</v>
       </c>
       <c r="M7" t="n">
-        <v>-66.61933898925781</v>
+        <v>-70.43133544921875</v>
       </c>
       <c r="N7" t="n">
-        <v>-62.39210891723633</v>
+        <v>-64.98367309570312</v>
       </c>
       <c r="O7" t="n">
-        <v>-66.84602355957031</v>
+        <v>-73.48676300048828</v>
       </c>
       <c r="P7" t="n">
-        <v>-64.4493408203125</v>
+        <v>-68.98549652099609</v>
       </c>
       <c r="Q7" t="n">
-        <v>-68.92696380615234</v>
+        <v>-70.99674987792969</v>
       </c>
       <c r="R7" t="n">
-        <v>-68.36653137207031</v>
+        <v>-69.40586853027344</v>
       </c>
       <c r="S7" t="n">
-        <v>-70.42939758300781</v>
+        <v>-71.67861938476562</v>
       </c>
       <c r="T7" t="n">
-        <v>-71.85982513427734</v>
+        <v>-74.22937774658203</v>
       </c>
       <c r="U7" t="n">
-        <v>-72.999755859375</v>
+        <v>-72.90596008300781</v>
       </c>
       <c r="V7" t="n">
-        <v>-74.6788330078125</v>
+        <v>-70.73823547363281</v>
       </c>
       <c r="W7" t="n">
-        <v>-70.94622039794922</v>
+        <v>-71.40110778808594</v>
       </c>
       <c r="X7" t="n">
-        <v>-69.48048400878906</v>
+        <v>-77.80155181884766</v>
       </c>
       <c r="Y7" t="n">
-        <v>-74.71916198730469</v>
+        <v>-76.63549041748047</v>
       </c>
       <c r="Z7" t="n">
-        <v>-68.60203552246094</v>
+        <v>-79.18204498291016</v>
       </c>
       <c r="AA7" t="n">
-        <v>-70.87339782714844</v>
+        <v>-80.08013153076172</v>
       </c>
       <c r="AB7" t="n">
-        <v>-74.88841247558594</v>
+        <v>-83.80258941650391</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-48.55022430419922</v>
+        <v>-51.17599487304688</v>
       </c>
       <c r="B8" t="n">
-        <v>-54.42799758911133</v>
+        <v>-53.59403610229492</v>
       </c>
       <c r="C8" t="n">
-        <v>-58.26270294189453</v>
+        <v>-58.62064361572266</v>
       </c>
       <c r="D8" t="n">
-        <v>-49.16904830932617</v>
+        <v>-60.28693389892578</v>
       </c>
       <c r="E8" t="n">
-        <v>-50.63866424560547</v>
+        <v>-59.97678756713867</v>
       </c>
       <c r="F8" t="n">
-        <v>-63.39951705932617</v>
+        <v>-54.9075813293457</v>
       </c>
       <c r="G8" t="n">
-        <v>-56.6962890625</v>
+        <v>-60.8218994140625</v>
       </c>
       <c r="H8" t="n">
-        <v>-59.72841644287109</v>
+        <v>-59.519287109375</v>
       </c>
       <c r="I8" t="n">
-        <v>-61.46995162963867</v>
+        <v>-62.35908889770508</v>
       </c>
       <c r="J8" t="n">
-        <v>-59.7047004699707</v>
+        <v>-64.10920715332031</v>
       </c>
       <c r="K8" t="n">
-        <v>-65.81206512451172</v>
+        <v>-66.239013671875</v>
       </c>
       <c r="L8" t="n">
-        <v>-59.70590209960938</v>
+        <v>-66.88768005371094</v>
       </c>
       <c r="M8" t="n">
-        <v>-63.42805099487305</v>
+        <v>-68.73649597167969</v>
       </c>
       <c r="N8" t="n">
-        <v>-66.50537109375</v>
+        <v>-65.59660339355469</v>
       </c>
       <c r="O8" t="n">
-        <v>-67.37957000732422</v>
+        <v>-70.37828063964844</v>
       </c>
       <c r="P8" t="n">
-        <v>-65.24763488769531</v>
+        <v>-68.01747131347656</v>
       </c>
       <c r="Q8" t="n">
-        <v>-62.12561798095703</v>
+        <v>-67.61648559570312</v>
       </c>
       <c r="R8" t="n">
-        <v>-76.23993682861328</v>
+        <v>-71.669677734375</v>
       </c>
       <c r="S8" t="n">
-        <v>-66.34772491455078</v>
+        <v>-71.67903137207031</v>
       </c>
       <c r="T8" t="n">
-        <v>-70.30400848388672</v>
+        <v>-73.30935668945312</v>
       </c>
       <c r="U8" t="n">
-        <v>-66.37361907958984</v>
+        <v>-69.37790679931641</v>
       </c>
       <c r="V8" t="n">
-        <v>-73.42734527587891</v>
+        <v>-75.74718475341797</v>
       </c>
       <c r="W8" t="n">
-        <v>-69.79655456542969</v>
+        <v>-71.088623046875</v>
       </c>
       <c r="X8" t="n">
-        <v>-69.18862915039062</v>
+        <v>-72.48165130615234</v>
       </c>
       <c r="Y8" t="n">
-        <v>-68.59488677978516</v>
+        <v>-76.87666320800781</v>
       </c>
       <c r="Z8" t="n">
-        <v>-69.53178405761719</v>
+        <v>-76.08159637451172</v>
       </c>
       <c r="AA8" t="n">
-        <v>-69.28857421875</v>
+        <v>-77.36408233642578</v>
       </c>
       <c r="AB8" t="n">
-        <v>-73.88970184326172</v>
+        <v>-82.48197937011719</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-63.00504302978516</v>
+        <v>-59.0591926574707</v>
       </c>
       <c r="B9" t="n">
-        <v>-57.28912353515625</v>
+        <v>-61.37171173095703</v>
       </c>
       <c r="C9" t="n">
-        <v>-61.62161254882812</v>
+        <v>-58.87860107421875</v>
       </c>
       <c r="D9" t="n">
-        <v>-54.08329391479492</v>
+        <v>-60.83354949951172</v>
       </c>
       <c r="E9" t="n">
-        <v>-57.02082443237305</v>
+        <v>-63.73352813720703</v>
       </c>
       <c r="F9" t="n">
-        <v>-57.80374908447266</v>
+        <v>-61.41115570068359</v>
       </c>
       <c r="G9" t="n">
-        <v>-61.42966461181641</v>
+        <v>-61.0620002746582</v>
       </c>
       <c r="H9" t="n">
-        <v>-63.73186111450195</v>
+        <v>-65.3858642578125</v>
       </c>
       <c r="I9" t="n">
-        <v>-63.91861724853516</v>
+        <v>-59.90016555786133</v>
       </c>
       <c r="J9" t="n">
-        <v>-67.47383117675781</v>
+        <v>-63.9287109375</v>
       </c>
       <c r="K9" t="n">
-        <v>-65.56980895996094</v>
+        <v>-66.41543579101562</v>
       </c>
       <c r="L9" t="n">
-        <v>-70.36894989013672</v>
+        <v>-64.75648498535156</v>
       </c>
       <c r="M9" t="n">
-        <v>-64.564697265625</v>
+        <v>-67.22151947021484</v>
       </c>
       <c r="N9" t="n">
-        <v>-64.54884338378906</v>
+        <v>-64.55165100097656</v>
       </c>
       <c r="O9" t="n">
-        <v>-66.99611663818359</v>
+        <v>-72.41883087158203</v>
       </c>
       <c r="P9" t="n">
-        <v>-69.41072082519531</v>
+        <v>-69.34128570556641</v>
       </c>
       <c r="Q9" t="n">
-        <v>-68.36259460449219</v>
+        <v>-68.46666717529297</v>
       </c>
       <c r="R9" t="n">
-        <v>-66.38052368164062</v>
+        <v>-68.18747711181641</v>
       </c>
       <c r="S9" t="n">
-        <v>-63.96812057495117</v>
+        <v>-71.89634704589844</v>
       </c>
       <c r="T9" t="n">
-        <v>-66.18257141113281</v>
+        <v>-72.26173400878906</v>
       </c>
       <c r="U9" t="n">
-        <v>-69.54689025878906</v>
+        <v>-73.2772216796875</v>
       </c>
       <c r="V9" t="n">
-        <v>-69.84243774414062</v>
+        <v>-72.62757873535156</v>
       </c>
       <c r="W9" t="n">
-        <v>-70.81964111328125</v>
+        <v>-75.14509582519531</v>
       </c>
       <c r="X9" t="n">
-        <v>-70.88092041015625</v>
+        <v>-72.71028900146484</v>
       </c>
       <c r="Y9" t="n">
-        <v>-74.70520782470703</v>
+        <v>-70.92545318603516</v>
       </c>
       <c r="Z9" t="n">
-        <v>-66.07594299316406</v>
+        <v>-78.7479248046875</v>
       </c>
       <c r="AA9" t="n">
-        <v>-66.48365020751953</v>
+        <v>-73.73227691650391</v>
       </c>
       <c r="AB9" t="n">
-        <v>-73.66236114501953</v>
+        <v>-80.90633392333984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-66.05857849121094</v>
+        <v>-55.5160026550293</v>
       </c>
       <c r="B10" t="n">
-        <v>-60.38192749023438</v>
+        <v>-59.32087326049805</v>
       </c>
       <c r="C10" t="n">
-        <v>-64.10606384277344</v>
+        <v>-55.69062042236328</v>
       </c>
       <c r="D10" t="n">
-        <v>-58.36000442504883</v>
+        <v>-59.43877029418945</v>
       </c>
       <c r="E10" t="n">
-        <v>-60.08909225463867</v>
+        <v>-59.63532257080078</v>
       </c>
       <c r="F10" t="n">
-        <v>-63.63720703125</v>
+        <v>-60.69965744018555</v>
       </c>
       <c r="G10" t="n">
-        <v>-64.06038665771484</v>
+        <v>-63.22006225585938</v>
       </c>
       <c r="H10" t="n">
-        <v>-66.1959228515625</v>
+        <v>-61.77261352539062</v>
       </c>
       <c r="I10" t="n">
-        <v>-66.69162750244141</v>
+        <v>-65.58724975585938</v>
       </c>
       <c r="J10" t="n">
-        <v>-61.68937301635742</v>
+        <v>-59.88871002197266</v>
       </c>
       <c r="K10" t="n">
-        <v>-60.19041061401367</v>
+        <v>-67.08258819580078</v>
       </c>
       <c r="L10" t="n">
-        <v>-67.71107482910156</v>
+        <v>-69.80506134033203</v>
       </c>
       <c r="M10" t="n">
-        <v>-68.14168548583984</v>
+        <v>-68.08821105957031</v>
       </c>
       <c r="N10" t="n">
-        <v>-68.77070617675781</v>
+        <v>-66.73162841796875</v>
       </c>
       <c r="O10" t="n">
-        <v>-65.34156036376953</v>
+        <v>-67.13804626464844</v>
       </c>
       <c r="P10" t="n">
-        <v>-68.22176361083984</v>
+        <v>-72.51000213623047</v>
       </c>
       <c r="Q10" t="n">
-        <v>-64.98366546630859</v>
+        <v>-72.82742309570312</v>
       </c>
       <c r="R10" t="n">
-        <v>-68.83249664306641</v>
+        <v>-71.77513122558594</v>
       </c>
       <c r="S10" t="n">
-        <v>-64.36537170410156</v>
+        <v>-77.37395477294922</v>
       </c>
       <c r="T10" t="n">
-        <v>-71.63359069824219</v>
+        <v>-75.65969848632812</v>
       </c>
       <c r="U10" t="n">
-        <v>-71.57039642333984</v>
+        <v>-66.03615570068359</v>
       </c>
       <c r="V10" t="n">
-        <v>-62.81288909912109</v>
+        <v>-68.30891418457031</v>
       </c>
       <c r="W10" t="n">
-        <v>-70.41670989990234</v>
+        <v>-79.10562896728516</v>
       </c>
       <c r="X10" t="n">
-        <v>-69.42076873779297</v>
+        <v>-70.11925506591797</v>
       </c>
       <c r="Y10" t="n">
-        <v>-71.97993469238281</v>
+        <v>-77.05744934082031</v>
       </c>
       <c r="Z10" t="n">
-        <v>-68.46501159667969</v>
+        <v>-77.67154693603516</v>
       </c>
       <c r="AA10" t="n">
-        <v>-66.9295654296875</v>
+        <v>-82.02568054199219</v>
       </c>
       <c r="AB10" t="n">
-        <v>-69.55608367919922</v>
+        <v>-74.91375732421875</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-61.63851928710938</v>
+        <v>-56.92237091064453</v>
       </c>
       <c r="B11" t="n">
-        <v>-62.16160202026367</v>
+        <v>-57.29691696166992</v>
       </c>
       <c r="C11" t="n">
-        <v>-60.33963012695312</v>
+        <v>-58.68312835693359</v>
       </c>
       <c r="D11" t="n">
-        <v>-62.09901809692383</v>
+        <v>-60.45308685302734</v>
       </c>
       <c r="E11" t="n">
-        <v>-61.06621551513672</v>
+        <v>-60.08655548095703</v>
       </c>
       <c r="F11" t="n">
-        <v>-64.29229736328125</v>
+        <v>-62.45539474487305</v>
       </c>
       <c r="G11" t="n">
-        <v>-66.19809722900391</v>
+        <v>-60.26737213134766</v>
       </c>
       <c r="H11" t="n">
-        <v>-62.49774932861328</v>
+        <v>-65.65399169921875</v>
       </c>
       <c r="I11" t="n">
-        <v>-65.69528961181641</v>
+        <v>-63.89289474487305</v>
       </c>
       <c r="J11" t="n">
-        <v>-67.13438415527344</v>
+        <v>-59.71577072143555</v>
       </c>
       <c r="K11" t="n">
-        <v>-68.74611663818359</v>
+        <v>-65.20128631591797</v>
       </c>
       <c r="L11" t="n">
-        <v>-66.99912261962891</v>
+        <v>-63.75847244262695</v>
       </c>
       <c r="M11" t="n">
-        <v>-72.17703247070312</v>
+        <v>-70.11396789550781</v>
       </c>
       <c r="N11" t="n">
-        <v>-67.05782318115234</v>
+        <v>-69.86952209472656</v>
       </c>
       <c r="O11" t="n">
-        <v>-64.50007629394531</v>
+        <v>-73.65669250488281</v>
       </c>
       <c r="P11" t="n">
-        <v>-65.7720947265625</v>
+        <v>-68.37461853027344</v>
       </c>
       <c r="Q11" t="n">
-        <v>-76.02210998535156</v>
+        <v>-75.03041839599609</v>
       </c>
       <c r="R11" t="n">
-        <v>-68.63703918457031</v>
+        <v>-74.12325286865234</v>
       </c>
       <c r="S11" t="n">
-        <v>-68.88960266113281</v>
+        <v>-73.54981994628906</v>
       </c>
       <c r="T11" t="n">
-        <v>-72.38954162597656</v>
+        <v>-74.35606384277344</v>
       </c>
       <c r="U11" t="n">
-        <v>-60.68074798583984</v>
+        <v>-77.24849700927734</v>
       </c>
       <c r="V11" t="n">
-        <v>-68.55519104003906</v>
+        <v>-74.12379455566406</v>
       </c>
       <c r="W11" t="n">
-        <v>-66.04866790771484</v>
+        <v>-78.06961059570312</v>
       </c>
       <c r="X11" t="n">
-        <v>-73.74510192871094</v>
+        <v>-76.83967590332031</v>
       </c>
       <c r="Y11" t="n">
-        <v>-74.21844482421875</v>
+        <v>-78.64238739013672</v>
       </c>
       <c r="Z11" t="n">
-        <v>-67.74082946777344</v>
+        <v>-80.68653106689453</v>
       </c>
       <c r="AA11" t="n">
-        <v>-73.87210845947266</v>
+        <v>-79.21458435058594</v>
       </c>
       <c r="AB11" t="n">
-        <v>-75.00733947753906</v>
+        <v>-78.15306091308594</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-61.02529907226562</v>
+        <v>-58.48909378051758</v>
       </c>
       <c r="B12" t="n">
-        <v>-51.60551071166992</v>
+        <v>-61.9114990234375</v>
       </c>
       <c r="C12" t="n">
-        <v>-67.40309906005859</v>
+        <v>-63.41082763671875</v>
       </c>
       <c r="D12" t="n">
-        <v>-67.27445220947266</v>
+        <v>-64.53886413574219</v>
       </c>
       <c r="E12" t="n">
-        <v>-64.01358795166016</v>
+        <v>-62.73616790771484</v>
       </c>
       <c r="F12" t="n">
-        <v>-66.53683471679688</v>
+        <v>-63.28441619873047</v>
       </c>
       <c r="G12" t="n">
-        <v>-64.985107421875</v>
+        <v>-66.86582946777344</v>
       </c>
       <c r="H12" t="n">
-        <v>-65.36081695556641</v>
+        <v>-66.29201507568359</v>
       </c>
       <c r="I12" t="n">
-        <v>-66.04640960693359</v>
+        <v>-66.02408599853516</v>
       </c>
       <c r="J12" t="n">
-        <v>-68.80641174316406</v>
+        <v>-67.37745666503906</v>
       </c>
       <c r="K12" t="n">
-        <v>-66.21196746826172</v>
+        <v>-61.57733917236328</v>
       </c>
       <c r="L12" t="n">
-        <v>-66.38868713378906</v>
+        <v>-68.89759063720703</v>
       </c>
       <c r="M12" t="n">
-        <v>-65.52293395996094</v>
+        <v>-69.02716827392578</v>
       </c>
       <c r="N12" t="n">
-        <v>-72.50365447998047</v>
+        <v>-69.49871826171875</v>
       </c>
       <c r="O12" t="n">
-        <v>-59.7730827331543</v>
+        <v>-67.45500183105469</v>
       </c>
       <c r="P12" t="n">
-        <v>-68.51149749755859</v>
+        <v>-69.52811431884766</v>
       </c>
       <c r="Q12" t="n">
-        <v>-64.38053131103516</v>
+        <v>-71.65644836425781</v>
       </c>
       <c r="R12" t="n">
-        <v>-72.40220642089844</v>
+        <v>-74.47679138183594</v>
       </c>
       <c r="S12" t="n">
-        <v>-68.75942993164062</v>
+        <v>-73.16814422607422</v>
       </c>
       <c r="T12" t="n">
-        <v>-67.91849517822266</v>
+        <v>-75.67391967773438</v>
       </c>
       <c r="U12" t="n">
-        <v>-70.07183074951172</v>
+        <v>-73.53524780273438</v>
       </c>
       <c r="V12" t="n">
-        <v>-70.09879302978516</v>
+        <v>-76.57199859619141</v>
       </c>
       <c r="W12" t="n">
-        <v>-71.95429229736328</v>
+        <v>-75.16112518310547</v>
       </c>
       <c r="X12" t="n">
-        <v>-70.65775299072266</v>
+        <v>-79.30699157714844</v>
       </c>
       <c r="Y12" t="n">
-        <v>-70.68893432617188</v>
+        <v>-82.85700225830078</v>
       </c>
       <c r="Z12" t="n">
-        <v>-73.84772491455078</v>
+        <v>-75.32565307617188</v>
       </c>
       <c r="AA12" t="n">
-        <v>-71.39455413818359</v>
+        <v>-79.69426727294922</v>
       </c>
       <c r="AB12" t="n">
-        <v>-78.66481018066406</v>
+        <v>-85.23415374755859</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-68.71748352050781</v>
+        <v>-65.90314483642578</v>
       </c>
       <c r="B13" t="n">
-        <v>-64.83194732666016</v>
+        <v>-62.50186920166016</v>
       </c>
       <c r="C13" t="n">
-        <v>-61.96004104614258</v>
+        <v>-61.190673828125</v>
       </c>
       <c r="D13" t="n">
-        <v>-69.94150543212891</v>
+        <v>-62.36211013793945</v>
       </c>
       <c r="E13" t="n">
-        <v>-62.87835693359375</v>
+        <v>-65.27644348144531</v>
       </c>
       <c r="F13" t="n">
-        <v>-70.60520935058594</v>
+        <v>-64.73695373535156</v>
       </c>
       <c r="G13" t="n">
-        <v>-66.21601867675781</v>
+        <v>-64.28559112548828</v>
       </c>
       <c r="H13" t="n">
-        <v>-65.4014892578125</v>
+        <v>-71.27503967285156</v>
       </c>
       <c r="I13" t="n">
-        <v>-70.00236511230469</v>
+        <v>-67.71778869628906</v>
       </c>
       <c r="J13" t="n">
-        <v>-65.30608367919922</v>
+        <v>-61.37406158447266</v>
       </c>
       <c r="K13" t="n">
-        <v>-67.26004791259766</v>
+        <v>-65.10200500488281</v>
       </c>
       <c r="L13" t="n">
-        <v>-71.17364501953125</v>
+        <v>-65.44467926025391</v>
       </c>
       <c r="M13" t="n">
-        <v>-67.02207183837891</v>
+        <v>-67.18739318847656</v>
       </c>
       <c r="N13" t="n">
-        <v>-65.50791931152344</v>
+        <v>-68.36161041259766</v>
       </c>
       <c r="O13" t="n">
-        <v>-62.08211135864258</v>
+        <v>-72.70252227783203</v>
       </c>
       <c r="P13" t="n">
-        <v>-68.62937164306641</v>
+        <v>-72.49720764160156</v>
       </c>
       <c r="Q13" t="n">
-        <v>-67.79485321044922</v>
+        <v>-73.34010314941406</v>
       </c>
       <c r="R13" t="n">
-        <v>-69.60890197753906</v>
+        <v>-79.05167388916016</v>
       </c>
       <c r="S13" t="n">
-        <v>-68.55556488037109</v>
+        <v>-70.13699340820312</v>
       </c>
       <c r="T13" t="n">
-        <v>-71.31977081298828</v>
+        <v>-77.02048492431641</v>
       </c>
       <c r="U13" t="n">
-        <v>-71.38316345214844</v>
+        <v>-84.16352844238281</v>
       </c>
       <c r="V13" t="n">
-        <v>-68.16362762451172</v>
+        <v>-74.85790252685547</v>
       </c>
       <c r="W13" t="n">
-        <v>-69.68831634521484</v>
+        <v>-77.129150390625</v>
       </c>
       <c r="X13" t="n">
-        <v>-71.29336547851562</v>
+        <v>-82.65171051025391</v>
       </c>
       <c r="Y13" t="n">
-        <v>-71.71079254150391</v>
+        <v>-81.35713195800781</v>
       </c>
       <c r="Z13" t="n">
-        <v>-73.06523895263672</v>
+        <v>-79.83195495605469</v>
       </c>
       <c r="AA13" t="n">
-        <v>-73.63838958740234</v>
+        <v>-82.56890869140625</v>
       </c>
       <c r="AB13" t="n">
-        <v>-71.04493713378906</v>
+        <v>-82.90206146240234</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-60.71237182617188</v>
+        <v>-63.49418258666992</v>
       </c>
       <c r="B14" t="n">
-        <v>-67.46517944335938</v>
+        <v>-60.4561653137207</v>
       </c>
       <c r="C14" t="n">
-        <v>-66.25839996337891</v>
+        <v>-64.21138763427734</v>
       </c>
       <c r="D14" t="n">
-        <v>-56.92254638671875</v>
+        <v>-64.13167572021484</v>
       </c>
       <c r="E14" t="n">
-        <v>-65.44233703613281</v>
+        <v>-70.83878326416016</v>
       </c>
       <c r="F14" t="n">
-        <v>-65.80440521240234</v>
+        <v>-65.23210144042969</v>
       </c>
       <c r="G14" t="n">
-        <v>-67.04121398925781</v>
+        <v>-65.20094299316406</v>
       </c>
       <c r="H14" t="n">
-        <v>-63.65402221679688</v>
+        <v>-67.5638427734375</v>
       </c>
       <c r="I14" t="n">
-        <v>-64.78574371337891</v>
+        <v>-65.57559967041016</v>
       </c>
       <c r="J14" t="n">
-        <v>-72.35047149658203</v>
+        <v>-66.86076354980469</v>
       </c>
       <c r="K14" t="n">
-        <v>-70.4326171875</v>
+        <v>-68.82637023925781</v>
       </c>
       <c r="L14" t="n">
-        <v>-66.74758911132812</v>
+        <v>-69.60560607910156</v>
       </c>
       <c r="M14" t="n">
-        <v>-69.83165740966797</v>
+        <v>-70.2008056640625</v>
       </c>
       <c r="N14" t="n">
-        <v>-68.89837646484375</v>
+        <v>-71.16615295410156</v>
       </c>
       <c r="O14" t="n">
-        <v>-68.84629821777344</v>
+        <v>-70.60492706298828</v>
       </c>
       <c r="P14" t="n">
-        <v>-61.61391067504883</v>
+        <v>-74.49031066894531</v>
       </c>
       <c r="Q14" t="n">
-        <v>-67.90733337402344</v>
+        <v>-73.19929504394531</v>
       </c>
       <c r="R14" t="n">
-        <v>-66.76154327392578</v>
+        <v>-77.54786682128906</v>
       </c>
       <c r="S14" t="n">
-        <v>-67.06711578369141</v>
+        <v>-71.67961120605469</v>
       </c>
       <c r="T14" t="n">
-        <v>-71.03845977783203</v>
+        <v>-75.67070007324219</v>
       </c>
       <c r="U14" t="n">
-        <v>-67.90599060058594</v>
+        <v>-74.53125</v>
       </c>
       <c r="V14" t="n">
-        <v>-65.19773864746094</v>
+        <v>-70.00687408447266</v>
       </c>
       <c r="W14" t="n">
-        <v>-65.52643585205078</v>
+        <v>-77.55565643310547</v>
       </c>
       <c r="X14" t="n">
-        <v>-73.27798461914062</v>
+        <v>-79.15355682373047</v>
       </c>
       <c r="Y14" t="n">
-        <v>-68.60185241699219</v>
+        <v>-76.74304962158203</v>
       </c>
       <c r="Z14" t="n">
-        <v>-67.3868408203125</v>
+        <v>-79.60240173339844</v>
       </c>
       <c r="AA14" t="n">
-        <v>-70.34724426269531</v>
+        <v>-78.29042053222656</v>
       </c>
       <c r="AB14" t="n">
-        <v>-74.90477752685547</v>
+        <v>-84.55947113037109</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-70.56026458740234</v>
+        <v>-62.30966949462891</v>
       </c>
       <c r="B15" t="n">
-        <v>-71.41136169433594</v>
+        <v>-65.96763610839844</v>
       </c>
       <c r="C15" t="n">
-        <v>-71.40203094482422</v>
+        <v>-68.57225036621094</v>
       </c>
       <c r="D15" t="n">
-        <v>-65.76118469238281</v>
+        <v>-70.42918395996094</v>
       </c>
       <c r="E15" t="n">
-        <v>-73.48091125488281</v>
+        <v>-66.82102966308594</v>
       </c>
       <c r="F15" t="n">
-        <v>-69.43849182128906</v>
+        <v>-67.17020416259766</v>
       </c>
       <c r="G15" t="n">
-        <v>-70.3570556640625</v>
+        <v>-67.83538055419922</v>
       </c>
       <c r="H15" t="n">
-        <v>-69.59553527832031</v>
+        <v>-69.94715118408203</v>
       </c>
       <c r="I15" t="n">
-        <v>-68.26966857910156</v>
+        <v>-63.53704833984375</v>
       </c>
       <c r="J15" t="n">
-        <v>-71.98405456542969</v>
+        <v>-71.72233581542969</v>
       </c>
       <c r="K15" t="n">
-        <v>-75.46871185302734</v>
+        <v>-67.69179534912109</v>
       </c>
       <c r="L15" t="n">
-        <v>-73.31890106201172</v>
+        <v>-72.63126373291016</v>
       </c>
       <c r="M15" t="n">
-        <v>-71.85759735107422</v>
+        <v>-75.83063507080078</v>
       </c>
       <c r="N15" t="n">
-        <v>-71.94322967529297</v>
+        <v>-73.91346740722656</v>
       </c>
       <c r="O15" t="n">
-        <v>-73.79487609863281</v>
+        <v>-71.29120635986328</v>
       </c>
       <c r="P15" t="n">
-        <v>-74.73420715332031</v>
+        <v>-73.90985107421875</v>
       </c>
       <c r="Q15" t="n">
-        <v>-69.60689544677734</v>
+        <v>-72.51887512207031</v>
       </c>
       <c r="R15" t="n">
-        <v>-69.30638885498047</v>
+        <v>-73.01859283447266</v>
       </c>
       <c r="S15" t="n">
-        <v>-69.95090484619141</v>
+        <v>-73.77928161621094</v>
       </c>
       <c r="T15" t="n">
-        <v>-74.24980926513672</v>
+        <v>-77.18952178955078</v>
       </c>
       <c r="U15" t="n">
-        <v>-71.64653015136719</v>
+        <v>-77.90135192871094</v>
       </c>
       <c r="V15" t="n">
-        <v>-69.10652160644531</v>
+        <v>-81.75455474853516</v>
       </c>
       <c r="W15" t="n">
-        <v>-73.43485260009766</v>
+        <v>-78.28952789306641</v>
       </c>
       <c r="X15" t="n">
-        <v>-69.68348693847656</v>
+        <v>-72.85260772705078</v>
       </c>
       <c r="Y15" t="n">
-        <v>-78.33647155761719</v>
+        <v>-76.62331390380859</v>
       </c>
       <c r="Z15" t="n">
-        <v>-71.61546325683594</v>
+        <v>-79.37429809570312</v>
       </c>
       <c r="AA15" t="n">
-        <v>-68.41701507568359</v>
+        <v>-79.42280578613281</v>
       </c>
       <c r="AB15" t="n">
-        <v>-73.32344818115234</v>
+        <v>-86.00511169433594</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-65.66287231445312</v>
+        <v>-67.877685546875</v>
       </c>
       <c r="B16" t="n">
-        <v>-74.1400146484375</v>
+        <v>-66.19985198974609</v>
       </c>
       <c r="C16" t="n">
-        <v>-73.08901977539062</v>
+        <v>-67.40251159667969</v>
       </c>
       <c r="D16" t="n">
-        <v>-76.04224395751953</v>
+        <v>-74.11466217041016</v>
       </c>
       <c r="E16" t="n">
-        <v>-69.83625030517578</v>
+        <v>-69.12591552734375</v>
       </c>
       <c r="F16" t="n">
-        <v>-71.0516357421875</v>
+        <v>-69.30365753173828</v>
       </c>
       <c r="G16" t="n">
-        <v>-70.30686187744141</v>
+        <v>-68.29499816894531</v>
       </c>
       <c r="H16" t="n">
-        <v>-66.05747985839844</v>
+        <v>-73.26917266845703</v>
       </c>
       <c r="I16" t="n">
-        <v>-74.92098236083984</v>
+        <v>-73.71580505371094</v>
       </c>
       <c r="J16" t="n">
-        <v>-75.7718505859375</v>
+        <v>-75.24391174316406</v>
       </c>
       <c r="K16" t="n">
-        <v>-73.16789245605469</v>
+        <v>-68.81834411621094</v>
       </c>
       <c r="L16" t="n">
-        <v>-71.30830383300781</v>
+        <v>-73.67750549316406</v>
       </c>
       <c r="M16" t="n">
-        <v>-75.99625396728516</v>
+        <v>-72.39320373535156</v>
       </c>
       <c r="N16" t="n">
-        <v>-75.63008880615234</v>
+        <v>-73.14854431152344</v>
       </c>
       <c r="O16" t="n">
-        <v>-78.39583587646484</v>
+        <v>-73.93575286865234</v>
       </c>
       <c r="P16" t="n">
-        <v>-73.85528564453125</v>
+        <v>-74.23655700683594</v>
       </c>
       <c r="Q16" t="n">
-        <v>-69.53143310546875</v>
+        <v>-74.09754943847656</v>
       </c>
       <c r="R16" t="n">
-        <v>-69.4432373046875</v>
+        <v>-76.44931793212891</v>
       </c>
       <c r="S16" t="n">
-        <v>-70.66081237792969</v>
+        <v>-74.11637878417969</v>
       </c>
       <c r="T16" t="n">
-        <v>-73.33457946777344</v>
+        <v>-75.38789367675781</v>
       </c>
       <c r="U16" t="n">
-        <v>-70.26005554199219</v>
+        <v>-72.05419158935547</v>
       </c>
       <c r="V16" t="n">
-        <v>-73.38973999023438</v>
+        <v>-78.44207763671875</v>
       </c>
       <c r="W16" t="n">
-        <v>-71.27129364013672</v>
+        <v>-78.82579040527344</v>
       </c>
       <c r="X16" t="n">
-        <v>-69.18337249755859</v>
+        <v>-83.22924041748047</v>
       </c>
       <c r="Y16" t="n">
-        <v>-70.40149688720703</v>
+        <v>-77.67035675048828</v>
       </c>
       <c r="Z16" t="n">
-        <v>-80.86421203613281</v>
+        <v>-80.05003356933594</v>
       </c>
       <c r="AA16" t="n">
-        <v>-72.11105346679688</v>
+        <v>-80.2943115234375</v>
       </c>
       <c r="AB16" t="n">
-        <v>-72.83988952636719</v>
+        <v>-77.62066650390625</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-67.95009613037109</v>
+        <v>-66.38054656982422</v>
       </c>
       <c r="B17" t="n">
-        <v>-75.29545593261719</v>
+        <v>-72.57728576660156</v>
       </c>
       <c r="C17" t="n">
-        <v>-71.95643615722656</v>
+        <v>-72.18824768066406</v>
       </c>
       <c r="D17" t="n">
-        <v>-75.17889404296875</v>
+        <v>-61.44972610473633</v>
       </c>
       <c r="E17" t="n">
-        <v>-76.40382385253906</v>
+        <v>-70.53150177001953</v>
       </c>
       <c r="F17" t="n">
-        <v>-65.51237487792969</v>
+        <v>-64.85343933105469</v>
       </c>
       <c r="G17" t="n">
-        <v>-70.25747680664062</v>
+        <v>-71.25227355957031</v>
       </c>
       <c r="H17" t="n">
-        <v>-63.54871368408203</v>
+        <v>-69.70243072509766</v>
       </c>
       <c r="I17" t="n">
-        <v>-79.65044403076172</v>
+        <v>-74.94989013671875</v>
       </c>
       <c r="J17" t="n">
-        <v>-78.04311370849609</v>
+        <v>-74.6292724609375</v>
       </c>
       <c r="K17" t="n">
-        <v>-73.05531311035156</v>
+        <v>-69.29833221435547</v>
       </c>
       <c r="L17" t="n">
-        <v>-78.42352294921875</v>
+        <v>-72.13933563232422</v>
       </c>
       <c r="M17" t="n">
-        <v>-79.16069793701172</v>
+        <v>-70.00481414794922</v>
       </c>
       <c r="N17" t="n">
-        <v>-80.88692474365234</v>
+        <v>-73.87464904785156</v>
       </c>
       <c r="O17" t="n">
-        <v>-80.92038726806641</v>
+        <v>-69.13288879394531</v>
       </c>
       <c r="P17" t="n">
-        <v>-78.53007507324219</v>
+        <v>-74.51416015625</v>
       </c>
       <c r="Q17" t="n">
-        <v>-76.06574249267578</v>
+        <v>-73.34513092041016</v>
       </c>
       <c r="R17" t="n">
-        <v>-72.85861206054688</v>
+        <v>-74.68004608154297</v>
       </c>
       <c r="S17" t="n">
-        <v>-74.84043121337891</v>
+        <v>-75.2607421875</v>
       </c>
       <c r="T17" t="n">
-        <v>-66.95240020751953</v>
+        <v>-79.81011962890625</v>
       </c>
       <c r="U17" t="n">
-        <v>-72.87763214111328</v>
+        <v>-74.71172332763672</v>
       </c>
       <c r="V17" t="n">
-        <v>-73.02011108398438</v>
+        <v>-80.33384704589844</v>
       </c>
       <c r="W17" t="n">
-        <v>-74.58713531494141</v>
+        <v>-77.35687255859375</v>
       </c>
       <c r="X17" t="n">
-        <v>-73.24288940429688</v>
+        <v>-78.65464019775391</v>
       </c>
       <c r="Y17" t="n">
-        <v>-72.89736938476562</v>
+        <v>-76.00363159179688</v>
       </c>
       <c r="Z17" t="n">
-        <v>-71.64860534667969</v>
+        <v>-79.52149963378906</v>
       </c>
       <c r="AA17" t="n">
-        <v>-75.35336303710938</v>
+        <v>-80.35894012451172</v>
       </c>
       <c r="AB17" t="n">
-        <v>-73.84610748291016</v>
+        <v>-79.83903503417969</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-82.56191253662109</v>
+        <v>-66.69111633300781</v>
       </c>
       <c r="B18" t="n">
-        <v>-72.20119476318359</v>
+        <v>-72.02314758300781</v>
       </c>
       <c r="C18" t="n">
-        <v>-74.60499572753906</v>
+        <v>-71.76013946533203</v>
       </c>
       <c r="D18" t="n">
-        <v>-73.46527099609375</v>
+        <v>-72.25702667236328</v>
       </c>
       <c r="E18" t="n">
-        <v>-80.53417205810547</v>
+        <v>-75.75534057617188</v>
       </c>
       <c r="F18" t="n">
-        <v>-77.35057067871094</v>
+        <v>-72.15212249755859</v>
       </c>
       <c r="G18" t="n">
-        <v>-71.52903747558594</v>
+        <v>-70.07462310791016</v>
       </c>
       <c r="H18" t="n">
-        <v>-77.147216796875</v>
+        <v>-66.1748046875</v>
       </c>
       <c r="I18" t="n">
-        <v>-72.57780456542969</v>
+        <v>-73.90046691894531</v>
       </c>
       <c r="J18" t="n">
-        <v>-69.85655212402344</v>
+        <v>-69.79678344726562</v>
       </c>
       <c r="K18" t="n">
-        <v>-69.05537414550781</v>
+        <v>-69.36789703369141</v>
       </c>
       <c r="L18" t="n">
-        <v>-82.39275360107422</v>
+        <v>-77.43444061279297</v>
       </c>
       <c r="M18" t="n">
-        <v>-72.28077697753906</v>
+        <v>-70.47522735595703</v>
       </c>
       <c r="N18" t="n">
-        <v>-76.44526672363281</v>
+        <v>-79.07201385498047</v>
       </c>
       <c r="O18" t="n">
-        <v>-81.57005310058594</v>
+        <v>-73.74082183837891</v>
       </c>
       <c r="P18" t="n">
-        <v>-79.78741455078125</v>
+        <v>-74.91039276123047</v>
       </c>
       <c r="Q18" t="n">
-        <v>-82.02322387695312</v>
+        <v>-74.53038024902344</v>
       </c>
       <c r="R18" t="n">
-        <v>-70.65764617919922</v>
+        <v>-72.55752563476562</v>
       </c>
       <c r="S18" t="n">
-        <v>-66.58204650878906</v>
+        <v>-72.59864807128906</v>
       </c>
       <c r="T18" t="n">
-        <v>-67.19918823242188</v>
+        <v>-72.41017150878906</v>
       </c>
       <c r="U18" t="n">
-        <v>-72.55812072753906</v>
+        <v>-77.51871490478516</v>
       </c>
       <c r="V18" t="n">
-        <v>-71.01139068603516</v>
+        <v>-76.79765319824219</v>
       </c>
       <c r="W18" t="n">
-        <v>-68.61624908447266</v>
+        <v>-78.60032653808594</v>
       </c>
       <c r="X18" t="n">
-        <v>-74.5089111328125</v>
+        <v>-70.48684692382812</v>
       </c>
       <c r="Y18" t="n">
-        <v>-74.5421142578125</v>
+        <v>-76.809326171875</v>
       </c>
       <c r="Z18" t="n">
-        <v>-77.44527435302734</v>
+        <v>-80.16561126708984</v>
       </c>
       <c r="AA18" t="n">
-        <v>-78.48726654052734</v>
+        <v>-80.76869201660156</v>
       </c>
       <c r="AB18" t="n">
-        <v>-71.149658203125</v>
+        <v>-77.27940368652344</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-74.41789245605469</v>
+        <v>-65.66892242431641</v>
       </c>
       <c r="B19" t="n">
-        <v>-73.47636413574219</v>
+        <v>-75.6976318359375</v>
       </c>
       <c r="C19" t="n">
-        <v>-68.04264068603516</v>
+        <v>-71.51641082763672</v>
       </c>
       <c r="D19" t="n">
-        <v>-73.44758605957031</v>
+        <v>-68.6466064453125</v>
       </c>
       <c r="E19" t="n">
-        <v>-69.08865356445312</v>
+        <v>-73.03321075439453</v>
       </c>
       <c r="F19" t="n">
-        <v>-78.30683135986328</v>
+        <v>-66.02442932128906</v>
       </c>
       <c r="G19" t="n">
-        <v>-72.84080505371094</v>
+        <v>-71.10191345214844</v>
       </c>
       <c r="H19" t="n">
-        <v>-70.41705322265625</v>
+        <v>-69.96049499511719</v>
       </c>
       <c r="I19" t="n">
-        <v>-77.15754699707031</v>
+        <v>-71.16014862060547</v>
       </c>
       <c r="J19" t="n">
-        <v>-75.369873046875</v>
+        <v>-73.12614440917969</v>
       </c>
       <c r="K19" t="n">
-        <v>-80.79496765136719</v>
+        <v>-71.51950073242188</v>
       </c>
       <c r="L19" t="n">
-        <v>-75.77071380615234</v>
+        <v>-77.70277404785156</v>
       </c>
       <c r="M19" t="n">
-        <v>-73.40704345703125</v>
+        <v>-72.07955932617188</v>
       </c>
       <c r="N19" t="n">
-        <v>-72.61399841308594</v>
+        <v>-76.76769256591797</v>
       </c>
       <c r="O19" t="n">
-        <v>-76.84849548339844</v>
+        <v>-75.69742584228516</v>
       </c>
       <c r="P19" t="n">
-        <v>-81.23288726806641</v>
+        <v>-78.07212829589844</v>
       </c>
       <c r="Q19" t="n">
-        <v>-86.36928558349609</v>
+        <v>-74.37855529785156</v>
       </c>
       <c r="R19" t="n">
-        <v>-78.02260589599609</v>
+        <v>-74.05214691162109</v>
       </c>
       <c r="S19" t="n">
-        <v>-80.96835327148438</v>
+        <v>-77.59681701660156</v>
       </c>
       <c r="T19" t="n">
-        <v>-71.13746643066406</v>
+        <v>-79.11094665527344</v>
       </c>
       <c r="U19" t="n">
-        <v>-69.37747955322266</v>
+        <v>-79.68849945068359</v>
       </c>
       <c r="V19" t="n">
-        <v>-66.08702087402344</v>
+        <v>-78.59841918945312</v>
       </c>
       <c r="W19" t="n">
-        <v>-70.67255401611328</v>
+        <v>-79.71012878417969</v>
       </c>
       <c r="X19" t="n">
-        <v>-72.57991027832031</v>
+        <v>-82.61798858642578</v>
       </c>
       <c r="Y19" t="n">
-        <v>-74.16518402099609</v>
+        <v>-79.61064910888672</v>
       </c>
       <c r="Z19" t="n">
-        <v>-71.53642272949219</v>
+        <v>-81.41543579101562</v>
       </c>
       <c r="AA19" t="n">
-        <v>-76.15592956542969</v>
+        <v>-81.00087738037109</v>
       </c>
       <c r="AB19" t="n">
-        <v>-77.76552581787109</v>
+        <v>-78.55274963378906</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-78.13078308105469</v>
+        <v>-70.51654815673828</v>
       </c>
       <c r="B20" t="n">
-        <v>-74.48893737792969</v>
+        <v>-70.49613189697266</v>
       </c>
       <c r="C20" t="n">
-        <v>-75.18788146972656</v>
+        <v>-71.48475646972656</v>
       </c>
       <c r="D20" t="n">
-        <v>-76.584716796875</v>
+        <v>-74.35157012939453</v>
       </c>
       <c r="E20" t="n">
-        <v>-73.81916046142578</v>
+        <v>-72.06267547607422</v>
       </c>
       <c r="F20" t="n">
-        <v>-73.4073486328125</v>
+        <v>-68.75949096679688</v>
       </c>
       <c r="G20" t="n">
-        <v>-76.08621978759766</v>
+        <v>-71.75226593017578</v>
       </c>
       <c r="H20" t="n">
-        <v>-63.05192947387695</v>
+        <v>-75.00750732421875</v>
       </c>
       <c r="I20" t="n">
-        <v>-75.05297088623047</v>
+        <v>-74.40789794921875</v>
       </c>
       <c r="J20" t="n">
-        <v>-78.28858184814453</v>
+        <v>-69.00860595703125</v>
       </c>
       <c r="K20" t="n">
-        <v>-79.66801452636719</v>
+        <v>-71.31169891357422</v>
       </c>
       <c r="L20" t="n">
-        <v>-73.56180572509766</v>
+        <v>-73.45387268066406</v>
       </c>
       <c r="M20" t="n">
-        <v>-79.36619567871094</v>
+        <v>-79.33461761474609</v>
       </c>
       <c r="N20" t="n">
-        <v>-74.29719543457031</v>
+        <v>-74.49898529052734</v>
       </c>
       <c r="O20" t="n">
-        <v>-77.61293029785156</v>
+        <v>-77.26109313964844</v>
       </c>
       <c r="P20" t="n">
-        <v>-76.37906646728516</v>
+        <v>-73.34968566894531</v>
       </c>
       <c r="Q20" t="n">
-        <v>-81.30924987792969</v>
+        <v>-76.31936645507812</v>
       </c>
       <c r="R20" t="n">
-        <v>-75.63078308105469</v>
+        <v>-79.68821716308594</v>
       </c>
       <c r="S20" t="n">
-        <v>-83.06260681152344</v>
+        <v>-77.81813812255859</v>
       </c>
       <c r="T20" t="n">
-        <v>-75.07057952880859</v>
+        <v>-75.16345977783203</v>
       </c>
       <c r="U20" t="n">
-        <v>-66.76954650878906</v>
+        <v>-79.75334167480469</v>
       </c>
       <c r="V20" t="n">
-        <v>-70.70344543457031</v>
+        <v>-77.74275207519531</v>
       </c>
       <c r="W20" t="n">
-        <v>-68.56224060058594</v>
+        <v>-76.28648376464844</v>
       </c>
       <c r="X20" t="n">
-        <v>-69.66465759277344</v>
+        <v>-75.89604187011719</v>
       </c>
       <c r="Y20" t="n">
-        <v>-68.60409545898438</v>
+        <v>-81.85404968261719</v>
       </c>
       <c r="Z20" t="n">
-        <v>-78.17012023925781</v>
+        <v>-78.55402374267578</v>
       </c>
       <c r="AA20" t="n">
-        <v>-68.19345092773438</v>
+        <v>-79.07398986816406</v>
       </c>
       <c r="AB20" t="n">
-        <v>-82.45644378662109</v>
+        <v>-83.650634765625</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-81.25498962402344</v>
+        <v>-71.63816833496094</v>
       </c>
       <c r="B21" t="n">
-        <v>-76.91462707519531</v>
+        <v>-69.71632385253906</v>
       </c>
       <c r="C21" t="n">
-        <v>-71.46345520019531</v>
+        <v>-69.17899322509766</v>
       </c>
       <c r="D21" t="n">
-        <v>-72.30067443847656</v>
+        <v>-77.51766204833984</v>
       </c>
       <c r="E21" t="n">
-        <v>-75.72108459472656</v>
+        <v>-73.50392150878906</v>
       </c>
       <c r="F21" t="n">
-        <v>-75.314453125</v>
+        <v>-73.14151000976562</v>
       </c>
       <c r="G21" t="n">
-        <v>-75.16545104980469</v>
+        <v>-67.53705596923828</v>
       </c>
       <c r="H21" t="n">
-        <v>-75.27019500732422</v>
+        <v>-72.12450408935547</v>
       </c>
       <c r="I21" t="n">
-        <v>-75.78343200683594</v>
+        <v>-77.87306213378906</v>
       </c>
       <c r="J21" t="n">
-        <v>-74.12216186523438</v>
+        <v>-71.49028778076172</v>
       </c>
       <c r="K21" t="n">
-        <v>-77.87333679199219</v>
+        <v>-76.09183502197266</v>
       </c>
       <c r="L21" t="n">
-        <v>-79.26020050048828</v>
+        <v>-79.84092712402344</v>
       </c>
       <c r="M21" t="n">
-        <v>-69.97673797607422</v>
+        <v>-73.81364440917969</v>
       </c>
       <c r="N21" t="n">
-        <v>-71.88005065917969</v>
+        <v>-75.14064025878906</v>
       </c>
       <c r="O21" t="n">
-        <v>-76.9571533203125</v>
+        <v>-79.36132049560547</v>
       </c>
       <c r="P21" t="n">
-        <v>-80.57804870605469</v>
+        <v>-74.70512390136719</v>
       </c>
       <c r="Q21" t="n">
-        <v>-79.56877899169922</v>
+        <v>-71.05899047851562</v>
       </c>
       <c r="R21" t="n">
-        <v>-80.63559722900391</v>
+        <v>-75.71920776367188</v>
       </c>
       <c r="S21" t="n">
-        <v>-77.79786682128906</v>
+        <v>-77.61579895019531</v>
       </c>
       <c r="T21" t="n">
-        <v>-74.81257629394531</v>
+        <v>-76.25758361816406</v>
       </c>
       <c r="U21" t="n">
-        <v>-81.29903411865234</v>
+        <v>-79.8961181640625</v>
       </c>
       <c r="V21" t="n">
-        <v>-72.70610046386719</v>
+        <v>-77.63011169433594</v>
       </c>
       <c r="W21" t="n">
-        <v>-69.62628936767578</v>
+        <v>-77.94265747070312</v>
       </c>
       <c r="X21" t="n">
-        <v>-72.96126556396484</v>
+        <v>-80.70580291748047</v>
       </c>
       <c r="Y21" t="n">
-        <v>-75.46872711181641</v>
+        <v>-79.0872802734375</v>
       </c>
       <c r="Z21" t="n">
-        <v>-71.05309295654297</v>
+        <v>-78.93019866943359</v>
       </c>
       <c r="AA21" t="n">
-        <v>-72.76422882080078</v>
+        <v>-80.25437927246094</v>
       </c>
       <c r="AB21" t="n">
-        <v>-75.57295227050781</v>
+        <v>-84.97608184814453</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-74.26811218261719</v>
+        <v>-73.16664123535156</v>
       </c>
       <c r="B22" t="n">
-        <v>-74.19389343261719</v>
+        <v>-76.08524322509766</v>
       </c>
       <c r="C22" t="n">
-        <v>-72.19647979736328</v>
+        <v>-74.96018981933594</v>
       </c>
       <c r="D22" t="n">
-        <v>-74.61298370361328</v>
+        <v>-72.6575927734375</v>
       </c>
       <c r="E22" t="n">
-        <v>-73.31517028808594</v>
+        <v>-73.88963317871094</v>
       </c>
       <c r="F22" t="n">
-        <v>-75.6357421875</v>
+        <v>-72.26884460449219</v>
       </c>
       <c r="G22" t="n">
-        <v>-78.01568603515625</v>
+        <v>-73.46075439453125</v>
       </c>
       <c r="H22" t="n">
-        <v>-76.47563171386719</v>
+        <v>-78.10478210449219</v>
       </c>
       <c r="I22" t="n">
-        <v>-77.82705688476562</v>
+        <v>-73.57621765136719</v>
       </c>
       <c r="J22" t="n">
-        <v>-79.25778961181641</v>
+        <v>-74.68040466308594</v>
       </c>
       <c r="K22" t="n">
-        <v>-73.12360382080078</v>
+        <v>-70.11716461181641</v>
       </c>
       <c r="L22" t="n">
-        <v>-79.40827941894531</v>
+        <v>-75.81221771240234</v>
       </c>
       <c r="M22" t="n">
-        <v>-75.55934906005859</v>
+        <v>-76.89328002929688</v>
       </c>
       <c r="N22" t="n">
-        <v>-75.06697082519531</v>
+        <v>-74.36268615722656</v>
       </c>
       <c r="O22" t="n">
-        <v>-76.51625823974609</v>
+        <v>-83.58219909667969</v>
       </c>
       <c r="P22" t="n">
-        <v>-79.88783264160156</v>
+        <v>-77.94508361816406</v>
       </c>
       <c r="Q22" t="n">
-        <v>-79.71443939208984</v>
+        <v>-70.45671081542969</v>
       </c>
       <c r="R22" t="n">
-        <v>-80.95819091796875</v>
+        <v>-73.67375946044922</v>
       </c>
       <c r="S22" t="n">
-        <v>-87.47231292724609</v>
+        <v>-80.00267028808594</v>
       </c>
       <c r="T22" t="n">
-        <v>-77.90341949462891</v>
+        <v>-77.2354736328125</v>
       </c>
       <c r="U22" t="n">
-        <v>-84.17408752441406</v>
+        <v>-69.99967193603516</v>
       </c>
       <c r="V22" t="n">
-        <v>-87.38719177246094</v>
+        <v>-76.76461029052734</v>
       </c>
       <c r="W22" t="n">
-        <v>-68.70097351074219</v>
+        <v>-79.16471862792969</v>
       </c>
       <c r="X22" t="n">
-        <v>-71.67454528808594</v>
+        <v>-79.52717590332031</v>
       </c>
       <c r="Y22" t="n">
-        <v>-70.12554168701172</v>
+        <v>-79.43270874023438</v>
       </c>
       <c r="Z22" t="n">
-        <v>-70.05418395996094</v>
+        <v>-79.33701324462891</v>
       </c>
       <c r="AA22" t="n">
-        <v>-74.94514465332031</v>
+        <v>-73.364013671875</v>
       </c>
       <c r="AB22" t="n">
-        <v>-82.58702850341797</v>
+        <v>-81.99134063720703</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-77.39276123046875</v>
+        <v>-75.80809783935547</v>
       </c>
       <c r="B23" t="n">
-        <v>-83.15900421142578</v>
+        <v>-76.65592956542969</v>
       </c>
       <c r="C23" t="n">
-        <v>-74.92586517333984</v>
+        <v>-80.40056610107422</v>
       </c>
       <c r="D23" t="n">
-        <v>-73.15699768066406</v>
+        <v>-77.46632385253906</v>
       </c>
       <c r="E23" t="n">
-        <v>-75.27000427246094</v>
+        <v>-71.95722961425781</v>
       </c>
       <c r="F23" t="n">
-        <v>-79.62995910644531</v>
+        <v>-74.95726776123047</v>
       </c>
       <c r="G23" t="n">
-        <v>-74.59681701660156</v>
+        <v>-74.93435668945312</v>
       </c>
       <c r="H23" t="n">
-        <v>-73.40852355957031</v>
+        <v>-75.90707397460938</v>
       </c>
       <c r="I23" t="n">
-        <v>-80.91252899169922</v>
+        <v>-78.75736236572266</v>
       </c>
       <c r="J23" t="n">
-        <v>-81.32289123535156</v>
+        <v>-76.49394989013672</v>
       </c>
       <c r="K23" t="n">
-        <v>-77.43226623535156</v>
+        <v>-70.66416168212891</v>
       </c>
       <c r="L23" t="n">
-        <v>-74.85385131835938</v>
+        <v>-76.57572174072266</v>
       </c>
       <c r="M23" t="n">
-        <v>-74.42857360839844</v>
+        <v>-76.74633026123047</v>
       </c>
       <c r="N23" t="n">
-        <v>-77.00340270996094</v>
+        <v>-73.70371246337891</v>
       </c>
       <c r="O23" t="n">
-        <v>-77.91706085205078</v>
+        <v>-73.87977600097656</v>
       </c>
       <c r="P23" t="n">
-        <v>-81.96080017089844</v>
+        <v>-74.77850341796875</v>
       </c>
       <c r="Q23" t="n">
-        <v>-86.45185852050781</v>
+        <v>-76.74845886230469</v>
       </c>
       <c r="R23" t="n">
-        <v>-84.11820220947266</v>
+        <v>-79.56447601318359</v>
       </c>
       <c r="S23" t="n">
-        <v>-82.88856506347656</v>
+        <v>-82.03951263427734</v>
       </c>
       <c r="T23" t="n">
-        <v>-84.94425964355469</v>
+        <v>-83.19242095947266</v>
       </c>
       <c r="U23" t="n">
-        <v>-85.67079162597656</v>
+        <v>-80.4356689453125</v>
       </c>
       <c r="V23" t="n">
-        <v>-87.08745574951172</v>
+        <v>-81.15925598144531</v>
       </c>
       <c r="W23" t="n">
-        <v>-86.90181732177734</v>
+        <v>-74.35964965820312</v>
       </c>
       <c r="X23" t="n">
-        <v>-73.81581115722656</v>
+        <v>-72.58455657958984</v>
       </c>
       <c r="Y23" t="n">
-        <v>-78.70712280273438</v>
+        <v>-77.21080017089844</v>
       </c>
       <c r="Z23" t="n">
-        <v>-70.16224670410156</v>
+        <v>-80.00856018066406</v>
       </c>
       <c r="AA23" t="n">
-        <v>-77.04498291015625</v>
+        <v>-79.32548522949219</v>
       </c>
       <c r="AB23" t="n">
-        <v>-76.87382507324219</v>
+        <v>-75.54943084716797</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-76.67024230957031</v>
+        <v>-74.07028198242188</v>
       </c>
       <c r="B24" t="n">
-        <v>-79.9002685546875</v>
+        <v>-75.88597106933594</v>
       </c>
       <c r="C24" t="n">
-        <v>-74.27772521972656</v>
+        <v>-81.87270355224609</v>
       </c>
       <c r="D24" t="n">
-        <v>-74.14283752441406</v>
+        <v>-75.53866577148438</v>
       </c>
       <c r="E24" t="n">
-        <v>-76.52529144287109</v>
+        <v>-76.55022430419922</v>
       </c>
       <c r="F24" t="n">
-        <v>-74.91453552246094</v>
+        <v>-73.89364624023438</v>
       </c>
       <c r="G24" t="n">
-        <v>-83.20436096191406</v>
+        <v>-73.91054534912109</v>
       </c>
       <c r="H24" t="n">
-        <v>-81.90430450439453</v>
+        <v>-75.98516082763672</v>
       </c>
       <c r="I24" t="n">
-        <v>-82.64316558837891</v>
+        <v>-73.47712707519531</v>
       </c>
       <c r="J24" t="n">
-        <v>-72.14088439941406</v>
+        <v>-72.49539947509766</v>
       </c>
       <c r="K24" t="n">
-        <v>-76.89967346191406</v>
+        <v>-74.52955627441406</v>
       </c>
       <c r="L24" t="n">
-        <v>-75.26759338378906</v>
+        <v>-76.05091094970703</v>
       </c>
       <c r="M24" t="n">
-        <v>-77.96434783935547</v>
+        <v>-79.46646881103516</v>
       </c>
       <c r="N24" t="n">
-        <v>-76.67836761474609</v>
+        <v>-76.15562438964844</v>
       </c>
       <c r="O24" t="n">
-        <v>-82.77848052978516</v>
+        <v>-77.7506103515625</v>
       </c>
       <c r="P24" t="n">
-        <v>-80.51214599609375</v>
+        <v>-76.57834625244141</v>
       </c>
       <c r="Q24" t="n">
-        <v>-81.54441070556641</v>
+        <v>-80.03543853759766</v>
       </c>
       <c r="R24" t="n">
-        <v>-76.419677734375</v>
+        <v>-72.43936157226562</v>
       </c>
       <c r="S24" t="n">
-        <v>-87.37319946289062</v>
+        <v>-80.81486511230469</v>
       </c>
       <c r="T24" t="n">
-        <v>-87.19925689697266</v>
+        <v>-80.46818542480469</v>
       </c>
       <c r="U24" t="n">
-        <v>-79.72039031982422</v>
+        <v>-72.40145111083984</v>
       </c>
       <c r="V24" t="n">
-        <v>-86.14324951171875</v>
+        <v>-81.62532043457031</v>
       </c>
       <c r="W24" t="n">
-        <v>-81.86113739013672</v>
+        <v>-82.2410888671875</v>
       </c>
       <c r="X24" t="n">
-        <v>-81.09801483154297</v>
+        <v>-74.94746398925781</v>
       </c>
       <c r="Y24" t="n">
-        <v>-73.15705108642578</v>
+        <v>-81.07450103759766</v>
       </c>
       <c r="Z24" t="n">
-        <v>-75.04213714599609</v>
+        <v>-76.77145385742188</v>
       </c>
       <c r="AA24" t="n">
-        <v>-75.37068176269531</v>
+        <v>-79.66426849365234</v>
       </c>
       <c r="AB24" t="n">
-        <v>-78.66026306152344</v>
+        <v>-78.9097900390625</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-76.23153686523438</v>
+        <v>-76.6339111328125</v>
       </c>
       <c r="B25" t="n">
-        <v>-72.52291107177734</v>
+        <v>-76.89310455322266</v>
       </c>
       <c r="C25" t="n">
-        <v>-74.42781066894531</v>
+        <v>-73.57195281982422</v>
       </c>
       <c r="D25" t="n">
-        <v>-82.74723815917969</v>
+        <v>-78.45179748535156</v>
       </c>
       <c r="E25" t="n">
-        <v>-76.66915893554688</v>
+        <v>-74.48390197753906</v>
       </c>
       <c r="F25" t="n">
-        <v>-76.73323059082031</v>
+        <v>-72.8756103515625</v>
       </c>
       <c r="G25" t="n">
-        <v>-81.51185607910156</v>
+        <v>-76.81378173828125</v>
       </c>
       <c r="H25" t="n">
-        <v>-76.85637664794922</v>
+        <v>-71.61107635498047</v>
       </c>
       <c r="I25" t="n">
-        <v>-76.03464508056641</v>
+        <v>-75.9609375</v>
       </c>
       <c r="J25" t="n">
-        <v>-79.20720672607422</v>
+        <v>-69.08363342285156</v>
       </c>
       <c r="K25" t="n">
-        <v>-79.09215545654297</v>
+        <v>-78.69931030273438</v>
       </c>
       <c r="L25" t="n">
-        <v>-79.52674102783203</v>
+        <v>-79.52665710449219</v>
       </c>
       <c r="M25" t="n">
-        <v>-77.28958892822266</v>
+        <v>-76.26544952392578</v>
       </c>
       <c r="N25" t="n">
-        <v>-78.24336242675781</v>
+        <v>-76.05919647216797</v>
       </c>
       <c r="O25" t="n">
-        <v>-84.74198150634766</v>
+        <v>-81.21054840087891</v>
       </c>
       <c r="P25" t="n">
-        <v>-79.45770263671875</v>
+        <v>-79.39593505859375</v>
       </c>
       <c r="Q25" t="n">
-        <v>-87.35588836669922</v>
+        <v>-82.25514221191406</v>
       </c>
       <c r="R25" t="n">
-        <v>-82.26923370361328</v>
+        <v>-72.0318603515625</v>
       </c>
       <c r="S25" t="n">
-        <v>-87.75522613525391</v>
+        <v>-81.05567932128906</v>
       </c>
       <c r="T25" t="n">
-        <v>-85.86707305908203</v>
+        <v>-81.41032409667969</v>
       </c>
       <c r="U25" t="n">
-        <v>-85.23875427246094</v>
+        <v>-77.55890655517578</v>
       </c>
       <c r="V25" t="n">
-        <v>-85.22197723388672</v>
+        <v>-79.62325286865234</v>
       </c>
       <c r="W25" t="n">
-        <v>-87.51824951171875</v>
+        <v>-79.58866119384766</v>
       </c>
       <c r="X25" t="n">
-        <v>-81.37672424316406</v>
+        <v>-77.59519195556641</v>
       </c>
       <c r="Y25" t="n">
-        <v>-90.94090270996094</v>
+        <v>-81.99845123291016</v>
       </c>
       <c r="Z25" t="n">
-        <v>-77.40787506103516</v>
+        <v>-76.82286834716797</v>
       </c>
       <c r="AA25" t="n">
-        <v>-75.83223724365234</v>
+        <v>-79.83009338378906</v>
       </c>
       <c r="AB25" t="n">
-        <v>-75.01430511474609</v>
+        <v>-84.60743713378906</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-74.29132843017578</v>
+        <v>-79.56044006347656</v>
       </c>
       <c r="B26" t="n">
-        <v>-80.24071502685547</v>
+        <v>-78.52989959716797</v>
       </c>
       <c r="C26" t="n">
-        <v>-77.15879821777344</v>
+        <v>-76.45951843261719</v>
       </c>
       <c r="D26" t="n">
-        <v>-76.77176666259766</v>
+        <v>-76.89188385009766</v>
       </c>
       <c r="E26" t="n">
-        <v>-78.02944946289062</v>
+        <v>-79.49822235107422</v>
       </c>
       <c r="F26" t="n">
-        <v>-81.79370880126953</v>
+        <v>-74.42856597900391</v>
       </c>
       <c r="G26" t="n">
-        <v>-78.412841796875</v>
+        <v>-79.55971527099609</v>
       </c>
       <c r="H26" t="n">
-        <v>-80.414306640625</v>
+        <v>-81.63719940185547</v>
       </c>
       <c r="I26" t="n">
-        <v>-77.97597503662109</v>
+        <v>-76.69266510009766</v>
       </c>
       <c r="J26" t="n">
-        <v>-78.37715911865234</v>
+        <v>-79.14131927490234</v>
       </c>
       <c r="K26" t="n">
-        <v>-81.33338928222656</v>
+        <v>-81.19374847412109</v>
       </c>
       <c r="L26" t="n">
-        <v>-66.50273132324219</v>
+        <v>-77.92402648925781</v>
       </c>
       <c r="M26" t="n">
-        <v>-77.17381286621094</v>
+        <v>-79.77883911132812</v>
       </c>
       <c r="N26" t="n">
-        <v>-76.94549560546875</v>
+        <v>-79.90240478515625</v>
       </c>
       <c r="O26" t="n">
-        <v>-88.76499938964844</v>
+        <v>-74.62898254394531</v>
       </c>
       <c r="P26" t="n">
-        <v>-82.71668243408203</v>
+        <v>-79.30819702148438</v>
       </c>
       <c r="Q26" t="n">
-        <v>-83.26509857177734</v>
+        <v>-82.02508544921875</v>
       </c>
       <c r="R26" t="n">
-        <v>-86.57534790039062</v>
+        <v>-82.02677917480469</v>
       </c>
       <c r="S26" t="n">
-        <v>-85.53096771240234</v>
+        <v>-75.99477386474609</v>
       </c>
       <c r="T26" t="n">
-        <v>-85.93826293945312</v>
+        <v>-78.98751068115234</v>
       </c>
       <c r="U26" t="n">
-        <v>-82.84851837158203</v>
+        <v>-73.92124938964844</v>
       </c>
       <c r="V26" t="n">
-        <v>-86.25467681884766</v>
+        <v>-78.29605865478516</v>
       </c>
       <c r="W26" t="n">
-        <v>-87.52857971191406</v>
+        <v>-78.02203369140625</v>
       </c>
       <c r="X26" t="n">
-        <v>-89.84626007080078</v>
+        <v>-78.61019134521484</v>
       </c>
       <c r="Y26" t="n">
-        <v>-88.46855926513672</v>
+        <v>-81.18259429931641</v>
       </c>
       <c r="Z26" t="n">
-        <v>-88.92632293701172</v>
+        <v>-78.49226379394531</v>
       </c>
       <c r="AA26" t="n">
-        <v>-72.06128692626953</v>
+        <v>-79.79507446289062</v>
       </c>
       <c r="AB26" t="n">
-        <v>-79.03414154052734</v>
+        <v>-81.22373962402344</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-80.49584197998047</v>
+        <v>-73.36844635009766</v>
       </c>
       <c r="B27" t="n">
-        <v>-78.48761749267578</v>
+        <v>-77.19682312011719</v>
       </c>
       <c r="C27" t="n">
-        <v>-76.74382019042969</v>
+        <v>-78.82787322998047</v>
       </c>
       <c r="D27" t="n">
-        <v>-73.02796936035156</v>
+        <v>-79.00032043457031</v>
       </c>
       <c r="E27" t="n">
-        <v>-77.58210754394531</v>
+        <v>-76.50749969482422</v>
       </c>
       <c r="F27" t="n">
-        <v>-80.16930389404297</v>
+        <v>-82.56536865234375</v>
       </c>
       <c r="G27" t="n">
-        <v>-86.05076599121094</v>
+        <v>-78.51487731933594</v>
       </c>
       <c r="H27" t="n">
-        <v>-75.11082458496094</v>
+        <v>-78.30803680419922</v>
       </c>
       <c r="I27" t="n">
-        <v>-78.75054168701172</v>
+        <v>-76.65489196777344</v>
       </c>
       <c r="J27" t="n">
-        <v>-78.99031829833984</v>
+        <v>-75.03974914550781</v>
       </c>
       <c r="K27" t="n">
-        <v>-78.73844909667969</v>
+        <v>-74.1781005859375</v>
       </c>
       <c r="L27" t="n">
-        <v>-78.65528106689453</v>
+        <v>-79.88047027587891</v>
       </c>
       <c r="M27" t="n">
-        <v>-75.02451324462891</v>
+        <v>-74.26854705810547</v>
       </c>
       <c r="N27" t="n">
-        <v>-74.71725463867188</v>
+        <v>-75.88855743408203</v>
       </c>
       <c r="O27" t="n">
-        <v>-84.08021545410156</v>
+        <v>-84.16246032714844</v>
       </c>
       <c r="P27" t="n">
-        <v>-83.62667083740234</v>
+        <v>-83.58545684814453</v>
       </c>
       <c r="Q27" t="n">
-        <v>-84.29795837402344</v>
+        <v>-79.28048706054688</v>
       </c>
       <c r="R27" t="n">
-        <v>-83.70762634277344</v>
+        <v>-78.08992767333984</v>
       </c>
       <c r="S27" t="n">
-        <v>-83.39666748046875</v>
+        <v>-80.3148193359375</v>
       </c>
       <c r="T27" t="n">
-        <v>-87.91719818115234</v>
+        <v>-82.04225158691406</v>
       </c>
       <c r="U27" t="n">
-        <v>-81.22193145751953</v>
+        <v>-77.35020446777344</v>
       </c>
       <c r="V27" t="n">
-        <v>-88.93115234375</v>
+        <v>-77.93212890625</v>
       </c>
       <c r="W27" t="n">
-        <v>-88.05735778808594</v>
+        <v>-82.75068664550781</v>
       </c>
       <c r="X27" t="n">
-        <v>-82.34342956542969</v>
+        <v>-80.12519836425781</v>
       </c>
       <c r="Y27" t="n">
-        <v>-84.57770538330078</v>
+        <v>-79.90282440185547</v>
       </c>
       <c r="Z27" t="n">
-        <v>-85.90391540527344</v>
+        <v>-80.65210723876953</v>
       </c>
       <c r="AA27" t="n">
-        <v>-85.10020446777344</v>
+        <v>-82.09708404541016</v>
       </c>
       <c r="AB27" t="n">
-        <v>-79.46134185791016</v>
+        <v>-82.69106292724609</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-76.22833251953125</v>
+        <v>-77.12129211425781</v>
       </c>
       <c r="B28" t="n">
-        <v>-72.55656433105469</v>
+        <v>-81.33280944824219</v>
       </c>
       <c r="C28" t="n">
-        <v>-77.59907531738281</v>
+        <v>-77.17927551269531</v>
       </c>
       <c r="D28" t="n">
-        <v>-79.01795959472656</v>
+        <v>-76.99478912353516</v>
       </c>
       <c r="E28" t="n">
-        <v>-78.68472290039062</v>
+        <v>-79.74996948242188</v>
       </c>
       <c r="F28" t="n">
-        <v>-80.22959899902344</v>
+        <v>-77.31790924072266</v>
       </c>
       <c r="G28" t="n">
-        <v>-76.28404235839844</v>
+        <v>-77.37118530273438</v>
       </c>
       <c r="H28" t="n">
-        <v>-78.40287780761719</v>
+        <v>-76.58278656005859</v>
       </c>
       <c r="I28" t="n">
-        <v>-81.43287658691406</v>
+        <v>-81.98173522949219</v>
       </c>
       <c r="J28" t="n">
-        <v>-74.13648986816406</v>
+        <v>-78.80445098876953</v>
       </c>
       <c r="K28" t="n">
-        <v>-79.97368621826172</v>
+        <v>-76.84877014160156</v>
       </c>
       <c r="L28" t="n">
-        <v>-81.86325836181641</v>
+        <v>-75.07277679443359</v>
       </c>
       <c r="M28" t="n">
-        <v>-84.93480682373047</v>
+        <v>-79.77114868164062</v>
       </c>
       <c r="N28" t="n">
-        <v>-77.77055358886719</v>
+        <v>-78.32823181152344</v>
       </c>
       <c r="O28" t="n">
-        <v>-74.91010284423828</v>
+        <v>-82.10035705566406</v>
       </c>
       <c r="P28" t="n">
-        <v>-86.13667297363281</v>
+        <v>-78.5245361328125</v>
       </c>
       <c r="Q28" t="n">
-        <v>-84.73651123046875</v>
+        <v>-76.74819946289062</v>
       </c>
       <c r="R28" t="n">
-        <v>-81.89016723632812</v>
+        <v>-81.63816833496094</v>
       </c>
       <c r="S28" t="n">
-        <v>-86.90323638916016</v>
+        <v>-78.95393371582031</v>
       </c>
       <c r="T28" t="n">
-        <v>-89.05724334716797</v>
+        <v>-77.98097229003906</v>
       </c>
       <c r="U28" t="n">
-        <v>-80.47806549072266</v>
+        <v>-78.92832946777344</v>
       </c>
       <c r="V28" t="n">
-        <v>-83.67282867431641</v>
+        <v>-87.82027435302734</v>
       </c>
       <c r="W28" t="n">
-        <v>-82.46327209472656</v>
+        <v>-79.27070617675781</v>
       </c>
       <c r="X28" t="n">
-        <v>-80.32495880126953</v>
+        <v>-79.71662902832031</v>
       </c>
       <c r="Y28" t="n">
-        <v>-89.03594970703125</v>
+        <v>-82.62809753417969</v>
       </c>
       <c r="Z28" t="n">
-        <v>-83.90570831298828</v>
+        <v>-75.72476959228516</v>
       </c>
       <c r="AA28" t="n">
-        <v>-89.82203674316406</v>
+        <v>-84.89713287353516</v>
       </c>
       <c r="AB28" t="n">
-        <v>-82.16972351074219</v>
+        <v>-83.12837219238281</v>
       </c>
     </row>
   </sheetData>

--- a/writerConference/rssi_output.xlsx
+++ b/writerConference/rssi_output.xlsx
@@ -2841,2410 +2841,2410 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="n">
-        <v>-29.54437828063965</v>
+        <v>-31.73988914489746</v>
       </c>
       <c r="B1" t="n">
-        <v>-35.09778213500977</v>
+        <v>-32.42946243286133</v>
       </c>
       <c r="C1" t="n">
-        <v>-41.01274871826172</v>
+        <v>-35.58815383911133</v>
       </c>
       <c r="D1" t="n">
-        <v>-42.41579055786133</v>
+        <v>-36.15460968017578</v>
       </c>
       <c r="E1" t="n">
-        <v>-46.1126823425293</v>
+        <v>-40.74419403076172</v>
       </c>
       <c r="F1" t="n">
-        <v>-52.49204635620117</v>
+        <v>-39.8609733581543</v>
       </c>
       <c r="G1" t="n">
-        <v>-62.20493316650391</v>
+        <v>-42.57514190673828</v>
       </c>
       <c r="H1" t="n">
-        <v>-57.30550384521484</v>
+        <v>-46.60338592529297</v>
       </c>
       <c r="I1" t="n">
-        <v>-57.74993896484375</v>
+        <v>-48.25447463989258</v>
       </c>
       <c r="J1" t="n">
-        <v>-63.20989990234375</v>
+        <v>-44.60097503662109</v>
       </c>
       <c r="K1" t="n">
-        <v>-60.74666213989258</v>
+        <v>-44.7952995300293</v>
       </c>
       <c r="L1" t="n">
-        <v>-60.6839714050293</v>
+        <v>-45.5946044921875</v>
       </c>
       <c r="M1" t="n">
-        <v>-60.12469482421875</v>
+        <v>-50.12831878662109</v>
       </c>
       <c r="N1" t="n">
-        <v>-63.78755950927734</v>
+        <v>-50.54061126708984</v>
       </c>
       <c r="O1" t="n">
-        <v>-63.51335525512695</v>
+        <v>-50.35604858398438</v>
       </c>
       <c r="P1" t="n">
-        <v>-68.05302429199219</v>
+        <v>-51.69874954223633</v>
       </c>
       <c r="Q1" t="n">
-        <v>-69.68775939941406</v>
+        <v>-50.63460159301758</v>
       </c>
       <c r="R1" t="n">
-        <v>-77.74272155761719</v>
+        <v>-52.20363616943359</v>
       </c>
       <c r="S1" t="n">
-        <v>-68.48191070556641</v>
+        <v>-54.53389739990234</v>
       </c>
       <c r="T1" t="n">
-        <v>-68.33390808105469</v>
+        <v>-52.3571662902832</v>
       </c>
       <c r="U1" t="n">
-        <v>-73.78950500488281</v>
+        <v>-51.42533111572266</v>
       </c>
       <c r="V1" t="n">
-        <v>-77.72330474853516</v>
+        <v>-52.77375411987305</v>
       </c>
       <c r="W1" t="n">
-        <v>-69.94468688964844</v>
+        <v>-52.99045562744141</v>
       </c>
       <c r="X1" t="n">
-        <v>-75.05682373046875</v>
+        <v>-56.56414031982422</v>
       </c>
       <c r="Y1" t="n">
-        <v>-76.90386199951172</v>
+        <v>-57.21269989013672</v>
       </c>
       <c r="Z1" t="n">
-        <v>-75.89933776855469</v>
+        <v>-57.63677978515625</v>
       </c>
       <c r="AA1" t="n">
-        <v>-75.65846252441406</v>
+        <v>-57.56461715698242</v>
       </c>
       <c r="AB1" t="n">
-        <v>-75.3387451171875</v>
+        <v>-60.49135589599609</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>-36.37484359741211</v>
+        <v>-36.81267929077148</v>
       </c>
       <c r="B2" t="n">
-        <v>-38.46696090698242</v>
+        <v>-34.91189575195312</v>
       </c>
       <c r="C2" t="n">
-        <v>-44.7988166809082</v>
+        <v>-38.66301727294922</v>
       </c>
       <c r="D2" t="n">
-        <v>-50.35476303100586</v>
+        <v>-40.37996292114258</v>
       </c>
       <c r="E2" t="n">
-        <v>-48.74587249755859</v>
+        <v>-42.16316986083984</v>
       </c>
       <c r="F2" t="n">
-        <v>-53.66500091552734</v>
+        <v>-41.91585922241211</v>
       </c>
       <c r="G2" t="n">
-        <v>-53.6481819152832</v>
+        <v>-40.94680023193359</v>
       </c>
       <c r="H2" t="n">
-        <v>-59.8607177734375</v>
+        <v>-46.98404693603516</v>
       </c>
       <c r="I2" t="n">
-        <v>-51.56760406494141</v>
+        <v>-45.71127700805664</v>
       </c>
       <c r="J2" t="n">
-        <v>-55.54486083984375</v>
+        <v>-44.61403656005859</v>
       </c>
       <c r="K2" t="n">
-        <v>-58.60979461669922</v>
+        <v>-48.67433929443359</v>
       </c>
       <c r="L2" t="n">
-        <v>-63.21550750732422</v>
+        <v>-51.93740844726562</v>
       </c>
       <c r="M2" t="n">
-        <v>-65.6240234375</v>
+        <v>-49.50347137451172</v>
       </c>
       <c r="N2" t="n">
-        <v>-64.44802093505859</v>
+        <v>-48.62194442749023</v>
       </c>
       <c r="O2" t="n">
-        <v>-70.02189636230469</v>
+        <v>-51.27848052978516</v>
       </c>
       <c r="P2" t="n">
-        <v>-68.05671691894531</v>
+        <v>-49.85099411010742</v>
       </c>
       <c r="Q2" t="n">
-        <v>-71.44490051269531</v>
+        <v>-50.41632843017578</v>
       </c>
       <c r="R2" t="n">
-        <v>-64.06539154052734</v>
+        <v>-51.35309600830078</v>
       </c>
       <c r="S2" t="n">
-        <v>-71.24034118652344</v>
+        <v>-52.60859298706055</v>
       </c>
       <c r="T2" t="n">
-        <v>-72.27819061279297</v>
+        <v>-49.4244270324707</v>
       </c>
       <c r="U2" t="n">
-        <v>-75.3365478515625</v>
+        <v>-51.58549880981445</v>
       </c>
       <c r="V2" t="n">
-        <v>-73.19606018066406</v>
+        <v>-53.13056182861328</v>
       </c>
       <c r="W2" t="n">
-        <v>-75.32147216796875</v>
+        <v>-52.93049240112305</v>
       </c>
       <c r="X2" t="n">
-        <v>-74.86286926269531</v>
+        <v>-52.4065055847168</v>
       </c>
       <c r="Y2" t="n">
-        <v>-78.84580993652344</v>
+        <v>-54.28730392456055</v>
       </c>
       <c r="Z2" t="n">
-        <v>-77.59410858154297</v>
+        <v>-53.90579986572266</v>
       </c>
       <c r="AA2" t="n">
-        <v>-75.27999114990234</v>
+        <v>-53.74308395385742</v>
       </c>
       <c r="AB2" t="n">
-        <v>-72.82197570800781</v>
+        <v>-56.30080032348633</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-43.41970062255859</v>
+        <v>-38.54506683349609</v>
       </c>
       <c r="B3" t="n">
-        <v>-41.01880645751953</v>
+        <v>-37.9269905090332</v>
       </c>
       <c r="C3" t="n">
-        <v>-42.00269317626953</v>
+        <v>-38.3278923034668</v>
       </c>
       <c r="D3" t="n">
-        <v>-48.01739883422852</v>
+        <v>-42.82613754272461</v>
       </c>
       <c r="E3" t="n">
-        <v>-50.64441680908203</v>
+        <v>-44.05791091918945</v>
       </c>
       <c r="F3" t="n">
-        <v>-53.39120483398438</v>
+        <v>-42.48711013793945</v>
       </c>
       <c r="G3" t="n">
-        <v>-58.32489776611328</v>
+        <v>-47.54775619506836</v>
       </c>
       <c r="H3" t="n">
-        <v>-52.07361602783203</v>
+        <v>-42.41589736938477</v>
       </c>
       <c r="I3" t="n">
-        <v>-55.20713043212891</v>
+        <v>-46.82323455810547</v>
       </c>
       <c r="J3" t="n">
-        <v>-57.81122970581055</v>
+        <v>-43.73761749267578</v>
       </c>
       <c r="K3" t="n">
-        <v>-59.76673126220703</v>
+        <v>-46.90348434448242</v>
       </c>
       <c r="L3" t="n">
-        <v>-67.95746612548828</v>
+        <v>-48.34639739990234</v>
       </c>
       <c r="M3" t="n">
-        <v>-59.70587158203125</v>
+        <v>-50.9393196105957</v>
       </c>
       <c r="N3" t="n">
-        <v>-68.75422668457031</v>
+        <v>-48.37625885009766</v>
       </c>
       <c r="O3" t="n">
-        <v>-72.50413513183594</v>
+        <v>-49.11184310913086</v>
       </c>
       <c r="P3" t="n">
-        <v>-68.45909881591797</v>
+        <v>-50.50649261474609</v>
       </c>
       <c r="Q3" t="n">
-        <v>-63.7124137878418</v>
+        <v>-52.43607330322266</v>
       </c>
       <c r="R3" t="n">
-        <v>-73.39876556396484</v>
+        <v>-51.2906608581543</v>
       </c>
       <c r="S3" t="n">
-        <v>-67.73902893066406</v>
+        <v>-55.76071166992188</v>
       </c>
       <c r="T3" t="n">
-        <v>-69.25592041015625</v>
+        <v>-50.20852661132812</v>
       </c>
       <c r="U3" t="n">
-        <v>-74.91688537597656</v>
+        <v>-55.50812530517578</v>
       </c>
       <c r="V3" t="n">
-        <v>-73.96766662597656</v>
+        <v>-51.6044807434082</v>
       </c>
       <c r="W3" t="n">
-        <v>-75.2691650390625</v>
+        <v>-53.99892044067383</v>
       </c>
       <c r="X3" t="n">
-        <v>-74.10276794433594</v>
+        <v>-53.87089920043945</v>
       </c>
       <c r="Y3" t="n">
-        <v>-76.21791839599609</v>
+        <v>-56.74726104736328</v>
       </c>
       <c r="Z3" t="n">
-        <v>-77.51340484619141</v>
+        <v>-54.44118118286133</v>
       </c>
       <c r="AA3" t="n">
-        <v>-75.91716766357422</v>
+        <v>-57.31298828125</v>
       </c>
       <c r="AB3" t="n">
-        <v>-81.95646667480469</v>
+        <v>-55.3466682434082</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>-42.06691741943359</v>
+        <v>-38.04422760009766</v>
       </c>
       <c r="B4" t="n">
-        <v>-45.3929328918457</v>
+        <v>-37.18502044677734</v>
       </c>
       <c r="C4" t="n">
-        <v>-47.88335418701172</v>
+        <v>-38.63078689575195</v>
       </c>
       <c r="D4" t="n">
-        <v>-48.65499114990234</v>
+        <v>-41.09058380126953</v>
       </c>
       <c r="E4" t="n">
-        <v>-51.37503814697266</v>
+        <v>-41.83008575439453</v>
       </c>
       <c r="F4" t="n">
-        <v>-55.06383514404297</v>
+        <v>-43.35531234741211</v>
       </c>
       <c r="G4" t="n">
-        <v>-53.37709808349609</v>
+        <v>-45.87278747558594</v>
       </c>
       <c r="H4" t="n">
-        <v>-56.39413452148438</v>
+        <v>-45.20355606079102</v>
       </c>
       <c r="I4" t="n">
-        <v>-54.93974685668945</v>
+        <v>-47.27805328369141</v>
       </c>
       <c r="J4" t="n">
-        <v>-58.98735427856445</v>
+        <v>-48.25748825073242</v>
       </c>
       <c r="K4" t="n">
-        <v>-62.66041946411133</v>
+        <v>-51.39498138427734</v>
       </c>
       <c r="L4" t="n">
-        <v>-59.360107421875</v>
+        <v>-48.55614471435547</v>
       </c>
       <c r="M4" t="n">
-        <v>-58.74775314331055</v>
+        <v>-48.38710403442383</v>
       </c>
       <c r="N4" t="n">
-        <v>-69.63628387451172</v>
+        <v>-47.0711669921875</v>
       </c>
       <c r="O4" t="n">
-        <v>-68.71076965332031</v>
+        <v>-50.01717376708984</v>
       </c>
       <c r="P4" t="n">
-        <v>-66.30245208740234</v>
+        <v>-51.92952728271484</v>
       </c>
       <c r="Q4" t="n">
-        <v>-74.60622406005859</v>
+        <v>-53.86928176879883</v>
       </c>
       <c r="R4" t="n">
-        <v>-65.97151184082031</v>
+        <v>-55.63983154296875</v>
       </c>
       <c r="S4" t="n">
-        <v>-71.87339782714844</v>
+        <v>-53.69623565673828</v>
       </c>
       <c r="T4" t="n">
-        <v>-71.088134765625</v>
+        <v>-52.71157073974609</v>
       </c>
       <c r="U4" t="n">
-        <v>-76.19334411621094</v>
+        <v>-50.58631134033203</v>
       </c>
       <c r="V4" t="n">
-        <v>-76.51402282714844</v>
+        <v>-54.9727897644043</v>
       </c>
       <c r="W4" t="n">
-        <v>-77.23451232910156</v>
+        <v>-54.3115348815918</v>
       </c>
       <c r="X4" t="n">
-        <v>-77.13478088378906</v>
+        <v>-56.59212112426758</v>
       </c>
       <c r="Y4" t="n">
-        <v>-75.2021484375</v>
+        <v>-54.1353874206543</v>
       </c>
       <c r="Z4" t="n">
-        <v>-74.92509460449219</v>
+        <v>-51.92157745361328</v>
       </c>
       <c r="AA4" t="n">
-        <v>-76.43038177490234</v>
+        <v>-55.03647613525391</v>
       </c>
       <c r="AB4" t="n">
-        <v>-75.56085968017578</v>
+        <v>-51.60871124267578</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-50.16460418701172</v>
+        <v>-41.05666351318359</v>
       </c>
       <c r="B5" t="n">
-        <v>-46.64916610717773</v>
+        <v>-39.52852630615234</v>
       </c>
       <c r="C5" t="n">
-        <v>-55.9818229675293</v>
+        <v>-45.05177307128906</v>
       </c>
       <c r="D5" t="n">
-        <v>-58.77095413208008</v>
+        <v>-43.23124313354492</v>
       </c>
       <c r="E5" t="n">
-        <v>-53.42831420898438</v>
+        <v>-45.6072998046875</v>
       </c>
       <c r="F5" t="n">
-        <v>-57.83133697509766</v>
+        <v>-43.97835922241211</v>
       </c>
       <c r="G5" t="n">
-        <v>-60.41475296020508</v>
+        <v>-44.34788131713867</v>
       </c>
       <c r="H5" t="n">
-        <v>-58.34879684448242</v>
+        <v>-42.22414016723633</v>
       </c>
       <c r="I5" t="n">
-        <v>-58.86350250244141</v>
+        <v>-46.35562133789062</v>
       </c>
       <c r="J5" t="n">
-        <v>-68.05470275878906</v>
+        <v>-45.75962448120117</v>
       </c>
       <c r="K5" t="n">
-        <v>-62.17134475708008</v>
+        <v>-47.91632843017578</v>
       </c>
       <c r="L5" t="n">
-        <v>-65.17490386962891</v>
+        <v>-48.83633804321289</v>
       </c>
       <c r="M5" t="n">
-        <v>-64.36906433105469</v>
+        <v>-48.36687850952148</v>
       </c>
       <c r="N5" t="n">
-        <v>-69.65180206298828</v>
+        <v>-50.75573348999023</v>
       </c>
       <c r="O5" t="n">
-        <v>-64.45137023925781</v>
+        <v>-50.21101379394531</v>
       </c>
       <c r="P5" t="n">
-        <v>-69.39357757568359</v>
+        <v>-49.68480682373047</v>
       </c>
       <c r="Q5" t="n">
-        <v>-66.52571868896484</v>
+        <v>-50.76472473144531</v>
       </c>
       <c r="R5" t="n">
-        <v>-71.69207000732422</v>
+        <v>-53.2379264831543</v>
       </c>
       <c r="S5" t="n">
-        <v>-74.69950103759766</v>
+        <v>-54.4400520324707</v>
       </c>
       <c r="T5" t="n">
-        <v>-73.35207366943359</v>
+        <v>-52.08837127685547</v>
       </c>
       <c r="U5" t="n">
-        <v>-67.23939514160156</v>
+        <v>-52.79519653320312</v>
       </c>
       <c r="V5" t="n">
-        <v>-72.7122802734375</v>
+        <v>-54.89124298095703</v>
       </c>
       <c r="W5" t="n">
-        <v>-74.28065490722656</v>
+        <v>-52.30797576904297</v>
       </c>
       <c r="X5" t="n">
-        <v>-77.54673004150391</v>
+        <v>-53.9687385559082</v>
       </c>
       <c r="Y5" t="n">
-        <v>-72.62503814697266</v>
+        <v>-54.96966552734375</v>
       </c>
       <c r="Z5" t="n">
-        <v>-74.48170471191406</v>
+        <v>-59.09485626220703</v>
       </c>
       <c r="AA5" t="n">
-        <v>-78.1944580078125</v>
+        <v>-55.8912353515625</v>
       </c>
       <c r="AB5" t="n">
-        <v>-81.85810089111328</v>
+        <v>-52.83844757080078</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-51.39049530029297</v>
+        <v>-40.99485015869141</v>
       </c>
       <c r="B6" t="n">
-        <v>-52.04323196411133</v>
+        <v>-44.61943054199219</v>
       </c>
       <c r="C6" t="n">
-        <v>-52.97794723510742</v>
+        <v>-40.77645111083984</v>
       </c>
       <c r="D6" t="n">
-        <v>-50.86052703857422</v>
+        <v>-44.27646636962891</v>
       </c>
       <c r="E6" t="n">
-        <v>-55.48836517333984</v>
+        <v>-43.09598922729492</v>
       </c>
       <c r="F6" t="n">
-        <v>-59.66237258911133</v>
+        <v>-43.15429306030273</v>
       </c>
       <c r="G6" t="n">
-        <v>-57.68551635742188</v>
+        <v>-45.61401748657227</v>
       </c>
       <c r="H6" t="n">
-        <v>-59.84402465820312</v>
+        <v>-46.14541244506836</v>
       </c>
       <c r="I6" t="n">
-        <v>-58.93107986450195</v>
+        <v>-44.73264312744141</v>
       </c>
       <c r="J6" t="n">
-        <v>-62.17662811279297</v>
+        <v>-50.25421905517578</v>
       </c>
       <c r="K6" t="n">
-        <v>-65.41178131103516</v>
+        <v>-45.63645172119141</v>
       </c>
       <c r="L6" t="n">
-        <v>-64.20021057128906</v>
+        <v>-48.66823959350586</v>
       </c>
       <c r="M6" t="n">
-        <v>-66.98896789550781</v>
+        <v>-52.6375732421875</v>
       </c>
       <c r="N6" t="n">
-        <v>-66.24797821044922</v>
+        <v>-52.8624267578125</v>
       </c>
       <c r="O6" t="n">
-        <v>-74.86843109130859</v>
+        <v>-50.93155288696289</v>
       </c>
       <c r="P6" t="n">
-        <v>-65.75113677978516</v>
+        <v>-49.86342620849609</v>
       </c>
       <c r="Q6" t="n">
-        <v>-69.96537017822266</v>
+        <v>-52.34780883789062</v>
       </c>
       <c r="R6" t="n">
-        <v>-75.50553894042969</v>
+        <v>-53.71743011474609</v>
       </c>
       <c r="S6" t="n">
-        <v>-66.23889923095703</v>
+        <v>-55.62947845458984</v>
       </c>
       <c r="T6" t="n">
-        <v>-71.11891937255859</v>
+        <v>-58.31301879882812</v>
       </c>
       <c r="U6" t="n">
-        <v>-71.88450622558594</v>
+        <v>-53.8682746887207</v>
       </c>
       <c r="V6" t="n">
-        <v>-79.20449829101562</v>
+        <v>-55.5026741027832</v>
       </c>
       <c r="W6" t="n">
-        <v>-80.64820098876953</v>
+        <v>-54.87021636962891</v>
       </c>
       <c r="X6" t="n">
-        <v>-77.52734375</v>
+        <v>-54.19746017456055</v>
       </c>
       <c r="Y6" t="n">
-        <v>-80.67929840087891</v>
+        <v>-51.78805541992188</v>
       </c>
       <c r="Z6" t="n">
-        <v>-72.54777526855469</v>
+        <v>-53.21662521362305</v>
       </c>
       <c r="AA6" t="n">
-        <v>-80.16984558105469</v>
+        <v>-54.3794059753418</v>
       </c>
       <c r="AB6" t="n">
-        <v>-85.80372619628906</v>
+        <v>-58.3748664855957</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-52.26765060424805</v>
+        <v>-42.25920104980469</v>
       </c>
       <c r="B7" t="n">
-        <v>-57.50865936279297</v>
+        <v>-38.40400314331055</v>
       </c>
       <c r="C7" t="n">
-        <v>-53.4208984375</v>
+        <v>-40.46535873413086</v>
       </c>
       <c r="D7" t="n">
-        <v>-54.9112434387207</v>
+        <v>-46.57241821289062</v>
       </c>
       <c r="E7" t="n">
-        <v>-61.71776580810547</v>
+        <v>-42.15779876708984</v>
       </c>
       <c r="F7" t="n">
-        <v>-54.57615280151367</v>
+        <v>-44.89062881469727</v>
       </c>
       <c r="G7" t="n">
-        <v>-54.30014801025391</v>
+        <v>-47.35093307495117</v>
       </c>
       <c r="H7" t="n">
-        <v>-60.76111602783203</v>
+        <v>-46.50449752807617</v>
       </c>
       <c r="I7" t="n">
-        <v>-62.1512565612793</v>
+        <v>-45.70908737182617</v>
       </c>
       <c r="J7" t="n">
-        <v>-61.00127410888672</v>
+        <v>-47.87649154663086</v>
       </c>
       <c r="K7" t="n">
-        <v>-68.68573760986328</v>
+        <v>-48.74477767944336</v>
       </c>
       <c r="L7" t="n">
-        <v>-65.96830749511719</v>
+        <v>-45.71120452880859</v>
       </c>
       <c r="M7" t="n">
-        <v>-70.43133544921875</v>
+        <v>-54.4282341003418</v>
       </c>
       <c r="N7" t="n">
-        <v>-64.98367309570312</v>
+        <v>-46.24619674682617</v>
       </c>
       <c r="O7" t="n">
-        <v>-73.48676300048828</v>
+        <v>-50.92034149169922</v>
       </c>
       <c r="P7" t="n">
-        <v>-68.98549652099609</v>
+        <v>-48.57260513305664</v>
       </c>
       <c r="Q7" t="n">
-        <v>-70.99674987792969</v>
+        <v>-49.75765228271484</v>
       </c>
       <c r="R7" t="n">
-        <v>-69.40586853027344</v>
+        <v>-51.11204528808594</v>
       </c>
       <c r="S7" t="n">
-        <v>-71.67861938476562</v>
+        <v>-52.55612182617188</v>
       </c>
       <c r="T7" t="n">
-        <v>-74.22937774658203</v>
+        <v>-52.98968505859375</v>
       </c>
       <c r="U7" t="n">
-        <v>-72.90596008300781</v>
+        <v>-54.19139862060547</v>
       </c>
       <c r="V7" t="n">
-        <v>-70.73823547363281</v>
+        <v>-52.23403167724609</v>
       </c>
       <c r="W7" t="n">
-        <v>-71.40110778808594</v>
+        <v>-54.4010124206543</v>
       </c>
       <c r="X7" t="n">
-        <v>-77.80155181884766</v>
+        <v>-49.26727294921875</v>
       </c>
       <c r="Y7" t="n">
-        <v>-76.63549041748047</v>
+        <v>-53.65781784057617</v>
       </c>
       <c r="Z7" t="n">
-        <v>-79.18204498291016</v>
+        <v>-58.41410064697266</v>
       </c>
       <c r="AA7" t="n">
-        <v>-80.08013153076172</v>
+        <v>-55.72740936279297</v>
       </c>
       <c r="AB7" t="n">
-        <v>-83.80258941650391</v>
+        <v>-55.60271453857422</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>-51.17599487304688</v>
+        <v>-44.45858764648438</v>
       </c>
       <c r="B8" t="n">
-        <v>-53.59403610229492</v>
+        <v>-44.25540924072266</v>
       </c>
       <c r="C8" t="n">
-        <v>-58.62064361572266</v>
+        <v>-43.74545288085938</v>
       </c>
       <c r="D8" t="n">
-        <v>-60.28693389892578</v>
+        <v>-45.87172698974609</v>
       </c>
       <c r="E8" t="n">
-        <v>-59.97678756713867</v>
+        <v>-43.96171188354492</v>
       </c>
       <c r="F8" t="n">
-        <v>-54.9075813293457</v>
+        <v>-45.97286605834961</v>
       </c>
       <c r="G8" t="n">
-        <v>-60.8218994140625</v>
+        <v>-47.42250442504883</v>
       </c>
       <c r="H8" t="n">
-        <v>-59.519287109375</v>
+        <v>-45.85314178466797</v>
       </c>
       <c r="I8" t="n">
-        <v>-62.35908889770508</v>
+        <v>-48.96924209594727</v>
       </c>
       <c r="J8" t="n">
-        <v>-64.10920715332031</v>
+        <v>-46.9132080078125</v>
       </c>
       <c r="K8" t="n">
-        <v>-66.239013671875</v>
+        <v>-51.83929443359375</v>
       </c>
       <c r="L8" t="n">
-        <v>-66.88768005371094</v>
+        <v>-48.4498291015625</v>
       </c>
       <c r="M8" t="n">
-        <v>-68.73649597167969</v>
+        <v>-50.18611907958984</v>
       </c>
       <c r="N8" t="n">
-        <v>-65.59660339355469</v>
+        <v>-48.47720718383789</v>
       </c>
       <c r="O8" t="n">
-        <v>-70.37828063964844</v>
+        <v>-53.0195198059082</v>
       </c>
       <c r="P8" t="n">
-        <v>-68.01747131347656</v>
+        <v>-53.72293853759766</v>
       </c>
       <c r="Q8" t="n">
-        <v>-67.61648559570312</v>
+        <v>-52.75686645507812</v>
       </c>
       <c r="R8" t="n">
-        <v>-71.669677734375</v>
+        <v>-52.73811721801758</v>
       </c>
       <c r="S8" t="n">
-        <v>-71.67903137207031</v>
+        <v>-51.50477981567383</v>
       </c>
       <c r="T8" t="n">
-        <v>-73.30935668945312</v>
+        <v>-54.09079742431641</v>
       </c>
       <c r="U8" t="n">
-        <v>-69.37790679931641</v>
+        <v>-52.62389373779297</v>
       </c>
       <c r="V8" t="n">
-        <v>-75.74718475341797</v>
+        <v>-53.69901657104492</v>
       </c>
       <c r="W8" t="n">
-        <v>-71.088623046875</v>
+        <v>-54.2218017578125</v>
       </c>
       <c r="X8" t="n">
-        <v>-72.48165130615234</v>
+        <v>-56.57583618164062</v>
       </c>
       <c r="Y8" t="n">
-        <v>-76.87666320800781</v>
+        <v>-53.90227127075195</v>
       </c>
       <c r="Z8" t="n">
-        <v>-76.08159637451172</v>
+        <v>-51.38205718994141</v>
       </c>
       <c r="AA8" t="n">
-        <v>-77.36408233642578</v>
+        <v>-54.3906135559082</v>
       </c>
       <c r="AB8" t="n">
-        <v>-82.48197937011719</v>
+        <v>-51.83428192138672</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>-59.0591926574707</v>
+        <v>-44.66403198242188</v>
       </c>
       <c r="B9" t="n">
-        <v>-61.37171173095703</v>
+        <v>-45.29808807373047</v>
       </c>
       <c r="C9" t="n">
-        <v>-58.87860107421875</v>
+        <v>-45.10898971557617</v>
       </c>
       <c r="D9" t="n">
-        <v>-60.83354949951172</v>
+        <v>-47.71498107910156</v>
       </c>
       <c r="E9" t="n">
-        <v>-63.73352813720703</v>
+        <v>-45.70597839355469</v>
       </c>
       <c r="F9" t="n">
-        <v>-61.41115570068359</v>
+        <v>-47.09680938720703</v>
       </c>
       <c r="G9" t="n">
-        <v>-61.0620002746582</v>
+        <v>-47.5026969909668</v>
       </c>
       <c r="H9" t="n">
-        <v>-65.3858642578125</v>
+        <v>-48.38098907470703</v>
       </c>
       <c r="I9" t="n">
-        <v>-59.90016555786133</v>
+        <v>-46.61978149414062</v>
       </c>
       <c r="J9" t="n">
-        <v>-63.9287109375</v>
+        <v>-51.20893478393555</v>
       </c>
       <c r="K9" t="n">
-        <v>-66.41543579101562</v>
+        <v>-49.2418327331543</v>
       </c>
       <c r="L9" t="n">
-        <v>-64.75648498535156</v>
+        <v>-47.6416015625</v>
       </c>
       <c r="M9" t="n">
-        <v>-67.22151947021484</v>
+        <v>-52.03745651245117</v>
       </c>
       <c r="N9" t="n">
-        <v>-64.55165100097656</v>
+        <v>-52.97294998168945</v>
       </c>
       <c r="O9" t="n">
-        <v>-72.41883087158203</v>
+        <v>-54.36359405517578</v>
       </c>
       <c r="P9" t="n">
-        <v>-69.34128570556641</v>
+        <v>-52.6606330871582</v>
       </c>
       <c r="Q9" t="n">
-        <v>-68.46666717529297</v>
+        <v>-55.86273193359375</v>
       </c>
       <c r="R9" t="n">
-        <v>-68.18747711181641</v>
+        <v>-53.16482543945312</v>
       </c>
       <c r="S9" t="n">
-        <v>-71.89634704589844</v>
+        <v>-53.9349479675293</v>
       </c>
       <c r="T9" t="n">
-        <v>-72.26173400878906</v>
+        <v>-54.6314697265625</v>
       </c>
       <c r="U9" t="n">
-        <v>-73.2772216796875</v>
+        <v>-51.4801025390625</v>
       </c>
       <c r="V9" t="n">
-        <v>-72.62757873535156</v>
+        <v>-52.78258514404297</v>
       </c>
       <c r="W9" t="n">
-        <v>-75.14509582519531</v>
+        <v>-52.32088088989258</v>
       </c>
       <c r="X9" t="n">
-        <v>-72.71028900146484</v>
+        <v>-53.01553344726562</v>
       </c>
       <c r="Y9" t="n">
-        <v>-70.92545318603516</v>
+        <v>-53.86494827270508</v>
       </c>
       <c r="Z9" t="n">
-        <v>-78.7479248046875</v>
+        <v>-53.30454254150391</v>
       </c>
       <c r="AA9" t="n">
-        <v>-73.73227691650391</v>
+        <v>-55.30101776123047</v>
       </c>
       <c r="AB9" t="n">
-        <v>-80.90633392333984</v>
+        <v>-57.9416389465332</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-55.5160026550293</v>
+        <v>-39.12181091308594</v>
       </c>
       <c r="B10" t="n">
-        <v>-59.32087326049805</v>
+        <v>-46.64934921264648</v>
       </c>
       <c r="C10" t="n">
-        <v>-55.69062042236328</v>
+        <v>-45.1938591003418</v>
       </c>
       <c r="D10" t="n">
-        <v>-59.43877029418945</v>
+        <v>-48.27265167236328</v>
       </c>
       <c r="E10" t="n">
-        <v>-59.63532257080078</v>
+        <v>-50.68456268310547</v>
       </c>
       <c r="F10" t="n">
-        <v>-60.69965744018555</v>
+        <v>-45.89110946655273</v>
       </c>
       <c r="G10" t="n">
-        <v>-63.22006225585938</v>
+        <v>-46.09725952148438</v>
       </c>
       <c r="H10" t="n">
-        <v>-61.77261352539062</v>
+        <v>-48.12667465209961</v>
       </c>
       <c r="I10" t="n">
-        <v>-65.58724975585938</v>
+        <v>-47.01843643188477</v>
       </c>
       <c r="J10" t="n">
-        <v>-59.88871002197266</v>
+        <v>-50.17618560791016</v>
       </c>
       <c r="K10" t="n">
-        <v>-67.08258819580078</v>
+        <v>-48.57525634765625</v>
       </c>
       <c r="L10" t="n">
-        <v>-69.80506134033203</v>
+        <v>-53.5469856262207</v>
       </c>
       <c r="M10" t="n">
-        <v>-68.08821105957031</v>
+        <v>-50.12737274169922</v>
       </c>
       <c r="N10" t="n">
-        <v>-66.73162841796875</v>
+        <v>-54.78336334228516</v>
       </c>
       <c r="O10" t="n">
-        <v>-67.13804626464844</v>
+        <v>-53.8497314453125</v>
       </c>
       <c r="P10" t="n">
-        <v>-72.51000213623047</v>
+        <v>-52.02029418945312</v>
       </c>
       <c r="Q10" t="n">
-        <v>-72.82742309570312</v>
+        <v>-50.90266799926758</v>
       </c>
       <c r="R10" t="n">
-        <v>-71.77513122558594</v>
+        <v>-50.06453704833984</v>
       </c>
       <c r="S10" t="n">
-        <v>-77.37395477294922</v>
+        <v>-53.68118286132812</v>
       </c>
       <c r="T10" t="n">
-        <v>-75.65969848632812</v>
+        <v>-54.89473724365234</v>
       </c>
       <c r="U10" t="n">
-        <v>-66.03615570068359</v>
+        <v>-56.57947540283203</v>
       </c>
       <c r="V10" t="n">
-        <v>-68.30891418457031</v>
+        <v>-55.93012619018555</v>
       </c>
       <c r="W10" t="n">
-        <v>-79.10562896728516</v>
+        <v>-54.77272796630859</v>
       </c>
       <c r="X10" t="n">
-        <v>-70.11925506591797</v>
+        <v>-54.05218505859375</v>
       </c>
       <c r="Y10" t="n">
-        <v>-77.05744934082031</v>
+        <v>-54.90413284301758</v>
       </c>
       <c r="Z10" t="n">
-        <v>-77.67154693603516</v>
+        <v>-55.8582878112793</v>
       </c>
       <c r="AA10" t="n">
-        <v>-82.02568054199219</v>
+        <v>-58.16130447387695</v>
       </c>
       <c r="AB10" t="n">
-        <v>-74.91375732421875</v>
+        <v>-53.4565315246582</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>-56.92237091064453</v>
+        <v>-47.02125549316406</v>
       </c>
       <c r="B11" t="n">
-        <v>-57.29691696166992</v>
+        <v>-46.58137893676758</v>
       </c>
       <c r="C11" t="n">
-        <v>-58.68312835693359</v>
+        <v>-47.22534942626953</v>
       </c>
       <c r="D11" t="n">
-        <v>-60.45308685302734</v>
+        <v>-46.60981750488281</v>
       </c>
       <c r="E11" t="n">
-        <v>-60.08655548095703</v>
+        <v>-49.63618087768555</v>
       </c>
       <c r="F11" t="n">
-        <v>-62.45539474487305</v>
+        <v>-47.89403533935547</v>
       </c>
       <c r="G11" t="n">
-        <v>-60.26737213134766</v>
+        <v>-49.24105072021484</v>
       </c>
       <c r="H11" t="n">
-        <v>-65.65399169921875</v>
+        <v>-52.19019317626953</v>
       </c>
       <c r="I11" t="n">
-        <v>-63.89289474487305</v>
+        <v>-46.71459197998047</v>
       </c>
       <c r="J11" t="n">
-        <v>-59.71577072143555</v>
+        <v>-50.47639846801758</v>
       </c>
       <c r="K11" t="n">
-        <v>-65.20128631591797</v>
+        <v>-47.24239730834961</v>
       </c>
       <c r="L11" t="n">
-        <v>-63.75847244262695</v>
+        <v>-53.22939300537109</v>
       </c>
       <c r="M11" t="n">
-        <v>-70.11396789550781</v>
+        <v>-50.3544921875</v>
       </c>
       <c r="N11" t="n">
-        <v>-69.86952209472656</v>
+        <v>-48.27704620361328</v>
       </c>
       <c r="O11" t="n">
-        <v>-73.65669250488281</v>
+        <v>-52.2994270324707</v>
       </c>
       <c r="P11" t="n">
-        <v>-68.37461853027344</v>
+        <v>-51.86870574951172</v>
       </c>
       <c r="Q11" t="n">
-        <v>-75.03041839599609</v>
+        <v>-52.95248413085938</v>
       </c>
       <c r="R11" t="n">
-        <v>-74.12325286865234</v>
+        <v>-52.68215179443359</v>
       </c>
       <c r="S11" t="n">
-        <v>-73.54981994628906</v>
+        <v>-54.14744186401367</v>
       </c>
       <c r="T11" t="n">
-        <v>-74.35606384277344</v>
+        <v>-54.42976760864258</v>
       </c>
       <c r="U11" t="n">
-        <v>-77.24849700927734</v>
+        <v>-52.95650482177734</v>
       </c>
       <c r="V11" t="n">
-        <v>-74.12379455566406</v>
+        <v>-55.82483673095703</v>
       </c>
       <c r="W11" t="n">
-        <v>-78.06961059570312</v>
+        <v>-54.35262298583984</v>
       </c>
       <c r="X11" t="n">
-        <v>-76.83967590332031</v>
+        <v>-55.69370269775391</v>
       </c>
       <c r="Y11" t="n">
-        <v>-78.64238739013672</v>
+        <v>-55.3239631652832</v>
       </c>
       <c r="Z11" t="n">
-        <v>-80.68653106689453</v>
+        <v>-56.95648956298828</v>
       </c>
       <c r="AA11" t="n">
-        <v>-79.21458435058594</v>
+        <v>-56.28501510620117</v>
       </c>
       <c r="AB11" t="n">
-        <v>-78.15306091308594</v>
+        <v>-57.09693145751953</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>-58.48909378051758</v>
+        <v>-47.32057952880859</v>
       </c>
       <c r="B12" t="n">
-        <v>-61.9114990234375</v>
+        <v>-48.1151123046875</v>
       </c>
       <c r="C12" t="n">
-        <v>-63.41082763671875</v>
+        <v>-45.90510559082031</v>
       </c>
       <c r="D12" t="n">
-        <v>-64.53886413574219</v>
+        <v>-49.08084869384766</v>
       </c>
       <c r="E12" t="n">
-        <v>-62.73616790771484</v>
+        <v>-49.94729995727539</v>
       </c>
       <c r="F12" t="n">
-        <v>-63.28441619873047</v>
+        <v>-50.68285369873047</v>
       </c>
       <c r="G12" t="n">
-        <v>-66.86582946777344</v>
+        <v>-50.95113372802734</v>
       </c>
       <c r="H12" t="n">
-        <v>-66.29201507568359</v>
+        <v>-52.38076782226562</v>
       </c>
       <c r="I12" t="n">
-        <v>-66.02408599853516</v>
+        <v>-47.47702026367188</v>
       </c>
       <c r="J12" t="n">
-        <v>-67.37745666503906</v>
+        <v>-48.8932991027832</v>
       </c>
       <c r="K12" t="n">
-        <v>-61.57733917236328</v>
+        <v>-48.71118545532227</v>
       </c>
       <c r="L12" t="n">
-        <v>-68.89759063720703</v>
+        <v>-51.22174072265625</v>
       </c>
       <c r="M12" t="n">
-        <v>-69.02716827392578</v>
+        <v>-49.00471878051758</v>
       </c>
       <c r="N12" t="n">
-        <v>-69.49871826171875</v>
+        <v>-52.05788040161133</v>
       </c>
       <c r="O12" t="n">
-        <v>-67.45500183105469</v>
+        <v>-51.26788330078125</v>
       </c>
       <c r="P12" t="n">
-        <v>-69.52811431884766</v>
+        <v>-51.9616813659668</v>
       </c>
       <c r="Q12" t="n">
-        <v>-71.65644836425781</v>
+        <v>-54.03864669799805</v>
       </c>
       <c r="R12" t="n">
-        <v>-74.47679138183594</v>
+        <v>-53.4595947265625</v>
       </c>
       <c r="S12" t="n">
-        <v>-73.16814422607422</v>
+        <v>-55.94376373291016</v>
       </c>
       <c r="T12" t="n">
-        <v>-75.67391967773438</v>
+        <v>-56.25168991088867</v>
       </c>
       <c r="U12" t="n">
-        <v>-73.53524780273438</v>
+        <v>-53.57329559326172</v>
       </c>
       <c r="V12" t="n">
-        <v>-76.57199859619141</v>
+        <v>-56.7467155456543</v>
       </c>
       <c r="W12" t="n">
-        <v>-75.16112518310547</v>
+        <v>-52.3035774230957</v>
       </c>
       <c r="X12" t="n">
-        <v>-79.30699157714844</v>
+        <v>-53.90332794189453</v>
       </c>
       <c r="Y12" t="n">
-        <v>-82.85700225830078</v>
+        <v>-54.30168533325195</v>
       </c>
       <c r="Z12" t="n">
-        <v>-75.32565307617188</v>
+        <v>-54.806884765625</v>
       </c>
       <c r="AA12" t="n">
-        <v>-79.69426727294922</v>
+        <v>-55.5299072265625</v>
       </c>
       <c r="AB12" t="n">
-        <v>-85.23415374755859</v>
+        <v>-57.26963043212891</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>-65.90314483642578</v>
+        <v>-47.22951889038086</v>
       </c>
       <c r="B13" t="n">
-        <v>-62.50186920166016</v>
+        <v>-46.4117546081543</v>
       </c>
       <c r="C13" t="n">
-        <v>-61.190673828125</v>
+        <v>-44.74771499633789</v>
       </c>
       <c r="D13" t="n">
-        <v>-62.36211013793945</v>
+        <v>-48.97022247314453</v>
       </c>
       <c r="E13" t="n">
-        <v>-65.27644348144531</v>
+        <v>-49.82147216796875</v>
       </c>
       <c r="F13" t="n">
-        <v>-64.73695373535156</v>
+        <v>-46.24026107788086</v>
       </c>
       <c r="G13" t="n">
-        <v>-64.28559112548828</v>
+        <v>-48.67017364501953</v>
       </c>
       <c r="H13" t="n">
-        <v>-71.27503967285156</v>
+        <v>-52.14723587036133</v>
       </c>
       <c r="I13" t="n">
-        <v>-67.71778869628906</v>
+        <v>-50.37056350708008</v>
       </c>
       <c r="J13" t="n">
-        <v>-61.37406158447266</v>
+        <v>-52.03292083740234</v>
       </c>
       <c r="K13" t="n">
-        <v>-65.10200500488281</v>
+        <v>-48.5875358581543</v>
       </c>
       <c r="L13" t="n">
-        <v>-65.44467926025391</v>
+        <v>-49.95302581787109</v>
       </c>
       <c r="M13" t="n">
-        <v>-67.18739318847656</v>
+        <v>-50.90197372436523</v>
       </c>
       <c r="N13" t="n">
-        <v>-68.36161041259766</v>
+        <v>-54.14835739135742</v>
       </c>
       <c r="O13" t="n">
-        <v>-72.70252227783203</v>
+        <v>-52.00418090820312</v>
       </c>
       <c r="P13" t="n">
-        <v>-72.49720764160156</v>
+        <v>-47.94605255126953</v>
       </c>
       <c r="Q13" t="n">
-        <v>-73.34010314941406</v>
+        <v>-52.76544952392578</v>
       </c>
       <c r="R13" t="n">
-        <v>-79.05167388916016</v>
+        <v>-49.96628570556641</v>
       </c>
       <c r="S13" t="n">
-        <v>-70.13699340820312</v>
+        <v>-52.44472503662109</v>
       </c>
       <c r="T13" t="n">
-        <v>-77.02048492431641</v>
+        <v>-55.5615119934082</v>
       </c>
       <c r="U13" t="n">
-        <v>-84.16352844238281</v>
+        <v>-56.65592575073242</v>
       </c>
       <c r="V13" t="n">
-        <v>-74.85790252685547</v>
+        <v>-55.6765251159668</v>
       </c>
       <c r="W13" t="n">
-        <v>-77.129150390625</v>
+        <v>-53.3101921081543</v>
       </c>
       <c r="X13" t="n">
-        <v>-82.65171051025391</v>
+        <v>-53.7601203918457</v>
       </c>
       <c r="Y13" t="n">
-        <v>-81.35713195800781</v>
+        <v>-55.26053619384766</v>
       </c>
       <c r="Z13" t="n">
-        <v>-79.83195495605469</v>
+        <v>-58.28661346435547</v>
       </c>
       <c r="AA13" t="n">
-        <v>-82.56890869140625</v>
+        <v>-57.93131637573242</v>
       </c>
       <c r="AB13" t="n">
-        <v>-82.90206146240234</v>
+        <v>-55.39469146728516</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>-63.49418258666992</v>
+        <v>-47.49927520751953</v>
       </c>
       <c r="B14" t="n">
-        <v>-60.4561653137207</v>
+        <v>-45.82749557495117</v>
       </c>
       <c r="C14" t="n">
-        <v>-64.21138763427734</v>
+        <v>-50.25790405273438</v>
       </c>
       <c r="D14" t="n">
-        <v>-64.13167572021484</v>
+        <v>-50.47902297973633</v>
       </c>
       <c r="E14" t="n">
-        <v>-70.83878326416016</v>
+        <v>-49.31134033203125</v>
       </c>
       <c r="F14" t="n">
-        <v>-65.23210144042969</v>
+        <v>-49.67377471923828</v>
       </c>
       <c r="G14" t="n">
-        <v>-65.20094299316406</v>
+        <v>-51.81311798095703</v>
       </c>
       <c r="H14" t="n">
-        <v>-67.5638427734375</v>
+        <v>-51.02509689331055</v>
       </c>
       <c r="I14" t="n">
-        <v>-65.57559967041016</v>
+        <v>-54.84840774536133</v>
       </c>
       <c r="J14" t="n">
-        <v>-66.86076354980469</v>
+        <v>-51.90558624267578</v>
       </c>
       <c r="K14" t="n">
-        <v>-68.82637023925781</v>
+        <v>-49.55432510375977</v>
       </c>
       <c r="L14" t="n">
-        <v>-69.60560607910156</v>
+        <v>-53.67982864379883</v>
       </c>
       <c r="M14" t="n">
-        <v>-70.2008056640625</v>
+        <v>-50.16133880615234</v>
       </c>
       <c r="N14" t="n">
-        <v>-71.16615295410156</v>
+        <v>-49.76430892944336</v>
       </c>
       <c r="O14" t="n">
-        <v>-70.60492706298828</v>
+        <v>-53.96170806884766</v>
       </c>
       <c r="P14" t="n">
-        <v>-74.49031066894531</v>
+        <v>-54.1585807800293</v>
       </c>
       <c r="Q14" t="n">
-        <v>-73.19929504394531</v>
+        <v>-54.64727783203125</v>
       </c>
       <c r="R14" t="n">
-        <v>-77.54786682128906</v>
+        <v>-54.147705078125</v>
       </c>
       <c r="S14" t="n">
-        <v>-71.67961120605469</v>
+        <v>-52.84505462646484</v>
       </c>
       <c r="T14" t="n">
-        <v>-75.67070007324219</v>
+        <v>-51.99172210693359</v>
       </c>
       <c r="U14" t="n">
-        <v>-74.53125</v>
+        <v>-53.20928955078125</v>
       </c>
       <c r="V14" t="n">
-        <v>-70.00687408447266</v>
+        <v>-55.54476165771484</v>
       </c>
       <c r="W14" t="n">
-        <v>-77.55565643310547</v>
+        <v>-50.70330047607422</v>
       </c>
       <c r="X14" t="n">
-        <v>-79.15355682373047</v>
+        <v>-53.22603607177734</v>
       </c>
       <c r="Y14" t="n">
-        <v>-76.74304962158203</v>
+        <v>-56.68585968017578</v>
       </c>
       <c r="Z14" t="n">
-        <v>-79.60240173339844</v>
+        <v>-58.62018585205078</v>
       </c>
       <c r="AA14" t="n">
-        <v>-78.29042053222656</v>
+        <v>-55.93502044677734</v>
       </c>
       <c r="AB14" t="n">
-        <v>-84.55947113037109</v>
+        <v>-55.12460327148438</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-62.30966949462891</v>
+        <v>-50.28752136230469</v>
       </c>
       <c r="B15" t="n">
-        <v>-65.96763610839844</v>
+        <v>-48.19797515869141</v>
       </c>
       <c r="C15" t="n">
-        <v>-68.57225036621094</v>
+        <v>-50.74509811401367</v>
       </c>
       <c r="D15" t="n">
-        <v>-70.42918395996094</v>
+        <v>-49.95989227294922</v>
       </c>
       <c r="E15" t="n">
-        <v>-66.82102966308594</v>
+        <v>-50.29404449462891</v>
       </c>
       <c r="F15" t="n">
-        <v>-67.17020416259766</v>
+        <v>-51.78090286254883</v>
       </c>
       <c r="G15" t="n">
-        <v>-67.83538055419922</v>
+        <v>-52.7792854309082</v>
       </c>
       <c r="H15" t="n">
-        <v>-69.94715118408203</v>
+        <v>-51.85343551635742</v>
       </c>
       <c r="I15" t="n">
-        <v>-63.53704833984375</v>
+        <v>-46.35147094726562</v>
       </c>
       <c r="J15" t="n">
-        <v>-71.72233581542969</v>
+        <v>-53.22740936279297</v>
       </c>
       <c r="K15" t="n">
-        <v>-67.69179534912109</v>
+        <v>-50.39856719970703</v>
       </c>
       <c r="L15" t="n">
-        <v>-72.63126373291016</v>
+        <v>-53.3067512512207</v>
       </c>
       <c r="M15" t="n">
-        <v>-75.83063507080078</v>
+        <v>-50.5528450012207</v>
       </c>
       <c r="N15" t="n">
-        <v>-73.91346740722656</v>
+        <v>-54.63793182373047</v>
       </c>
       <c r="O15" t="n">
-        <v>-71.29120635986328</v>
+        <v>-51.31819534301758</v>
       </c>
       <c r="P15" t="n">
-        <v>-73.90985107421875</v>
+        <v>-64.55559539794922</v>
       </c>
       <c r="Q15" t="n">
-        <v>-72.51887512207031</v>
+        <v>-68.69786071777344</v>
       </c>
       <c r="R15" t="n">
-        <v>-73.01859283447266</v>
+        <v>-64.40249633789062</v>
       </c>
       <c r="S15" t="n">
-        <v>-73.77928161621094</v>
+        <v>-68.73667907714844</v>
       </c>
       <c r="T15" t="n">
-        <v>-77.18952178955078</v>
+        <v>-64.65493011474609</v>
       </c>
       <c r="U15" t="n">
-        <v>-77.90135192871094</v>
+        <v>-66.87474060058594</v>
       </c>
       <c r="V15" t="n">
-        <v>-81.75455474853516</v>
+        <v>-66.82463073730469</v>
       </c>
       <c r="W15" t="n">
-        <v>-78.28952789306641</v>
+        <v>-71.66188049316406</v>
       </c>
       <c r="X15" t="n">
-        <v>-72.85260772705078</v>
+        <v>-70.35524749755859</v>
       </c>
       <c r="Y15" t="n">
-        <v>-76.62331390380859</v>
+        <v>-69.22618103027344</v>
       </c>
       <c r="Z15" t="n">
-        <v>-79.37429809570312</v>
+        <v>-69.90742492675781</v>
       </c>
       <c r="AA15" t="n">
-        <v>-79.42280578613281</v>
+        <v>-69.34880828857422</v>
       </c>
       <c r="AB15" t="n">
-        <v>-86.00511169433594</v>
+        <v>-71.47173309326172</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>-67.877685546875</v>
+        <v>-47.89324188232422</v>
       </c>
       <c r="B16" t="n">
-        <v>-66.19985198974609</v>
+        <v>-48.77280426025391</v>
       </c>
       <c r="C16" t="n">
-        <v>-67.40251159667969</v>
+        <v>-47.33703994750977</v>
       </c>
       <c r="D16" t="n">
-        <v>-74.11466217041016</v>
+        <v>-48.29613494873047</v>
       </c>
       <c r="E16" t="n">
-        <v>-69.12591552734375</v>
+        <v>-49.33088302612305</v>
       </c>
       <c r="F16" t="n">
-        <v>-69.30365753173828</v>
+        <v>-50.8424186706543</v>
       </c>
       <c r="G16" t="n">
-        <v>-68.29499816894531</v>
+        <v>-51.62396240234375</v>
       </c>
       <c r="H16" t="n">
-        <v>-73.26917266845703</v>
+        <v>-55.71799850463867</v>
       </c>
       <c r="I16" t="n">
-        <v>-73.71580505371094</v>
+        <v>-52.55010223388672</v>
       </c>
       <c r="J16" t="n">
-        <v>-75.24391174316406</v>
+        <v>-51.89943695068359</v>
       </c>
       <c r="K16" t="n">
-        <v>-68.81834411621094</v>
+        <v>-51.68509674072266</v>
       </c>
       <c r="L16" t="n">
-        <v>-73.67750549316406</v>
+        <v>-52.66959381103516</v>
       </c>
       <c r="M16" t="n">
-        <v>-72.39320373535156</v>
+        <v>-56.301025390625</v>
       </c>
       <c r="N16" t="n">
-        <v>-73.14854431152344</v>
+        <v>-55.11457061767578</v>
       </c>
       <c r="O16" t="n">
-        <v>-73.93575286865234</v>
+        <v>-53.9765510559082</v>
       </c>
       <c r="P16" t="n">
-        <v>-74.23655700683594</v>
+        <v>-51.9483642578125</v>
       </c>
       <c r="Q16" t="n">
-        <v>-74.09754943847656</v>
+        <v>-67.92775726318359</v>
       </c>
       <c r="R16" t="n">
-        <v>-76.44931793212891</v>
+        <v>-66.52024841308594</v>
       </c>
       <c r="S16" t="n">
-        <v>-74.11637878417969</v>
+        <v>-69.79842376708984</v>
       </c>
       <c r="T16" t="n">
-        <v>-75.38789367675781</v>
+        <v>-70.58229064941406</v>
       </c>
       <c r="U16" t="n">
-        <v>-72.05419158935547</v>
+        <v>-66.39036560058594</v>
       </c>
       <c r="V16" t="n">
-        <v>-78.44207763671875</v>
+        <v>-70.05596160888672</v>
       </c>
       <c r="W16" t="n">
-        <v>-78.82579040527344</v>
+        <v>-68.60011291503906</v>
       </c>
       <c r="X16" t="n">
-        <v>-83.22924041748047</v>
+        <v>-69.43851470947266</v>
       </c>
       <c r="Y16" t="n">
-        <v>-77.67035675048828</v>
+        <v>-67.20568084716797</v>
       </c>
       <c r="Z16" t="n">
-        <v>-80.05003356933594</v>
+        <v>-67.77571868896484</v>
       </c>
       <c r="AA16" t="n">
-        <v>-80.2943115234375</v>
+        <v>-71.20092010498047</v>
       </c>
       <c r="AB16" t="n">
-        <v>-77.62066650390625</v>
+        <v>-68.03513336181641</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-66.38054656982422</v>
+        <v>-48.64846038818359</v>
       </c>
       <c r="B17" t="n">
-        <v>-72.57728576660156</v>
+        <v>-46.66537094116211</v>
       </c>
       <c r="C17" t="n">
-        <v>-72.18824768066406</v>
+        <v>-48.49109649658203</v>
       </c>
       <c r="D17" t="n">
-        <v>-61.44972610473633</v>
+        <v>-49.96242904663086</v>
       </c>
       <c r="E17" t="n">
-        <v>-70.53150177001953</v>
+        <v>-51.98567962646484</v>
       </c>
       <c r="F17" t="n">
-        <v>-64.85343933105469</v>
+        <v>-50.91937637329102</v>
       </c>
       <c r="G17" t="n">
-        <v>-71.25227355957031</v>
+        <v>-54.87287521362305</v>
       </c>
       <c r="H17" t="n">
-        <v>-69.70243072509766</v>
+        <v>-49.38460540771484</v>
       </c>
       <c r="I17" t="n">
-        <v>-74.94989013671875</v>
+        <v>-50.48985290527344</v>
       </c>
       <c r="J17" t="n">
-        <v>-74.6292724609375</v>
+        <v>-51.86396408081055</v>
       </c>
       <c r="K17" t="n">
-        <v>-69.29833221435547</v>
+        <v>-52.21939086914062</v>
       </c>
       <c r="L17" t="n">
-        <v>-72.13933563232422</v>
+        <v>-51.35604095458984</v>
       </c>
       <c r="M17" t="n">
-        <v>-70.00481414794922</v>
+        <v>-53.53836822509766</v>
       </c>
       <c r="N17" t="n">
-        <v>-73.87464904785156</v>
+        <v>-50.91620635986328</v>
       </c>
       <c r="O17" t="n">
-        <v>-69.13288879394531</v>
+        <v>-54.85881423950195</v>
       </c>
       <c r="P17" t="n">
-        <v>-74.51416015625</v>
+        <v>-53.30976104736328</v>
       </c>
       <c r="Q17" t="n">
-        <v>-73.34513092041016</v>
+        <v>-57.02696990966797</v>
       </c>
       <c r="R17" t="n">
-        <v>-74.68004608154297</v>
+        <v>-65.77300262451172</v>
       </c>
       <c r="S17" t="n">
-        <v>-75.2607421875</v>
+        <v>-65.89887237548828</v>
       </c>
       <c r="T17" t="n">
-        <v>-79.81011962890625</v>
+        <v>-70.76648712158203</v>
       </c>
       <c r="U17" t="n">
-        <v>-74.71172332763672</v>
+        <v>-67.61903381347656</v>
       </c>
       <c r="V17" t="n">
-        <v>-80.33384704589844</v>
+        <v>-69.65459442138672</v>
       </c>
       <c r="W17" t="n">
-        <v>-77.35687255859375</v>
+        <v>-70.40023803710938</v>
       </c>
       <c r="X17" t="n">
-        <v>-78.65464019775391</v>
+        <v>-67.80451965332031</v>
       </c>
       <c r="Y17" t="n">
-        <v>-76.00363159179688</v>
+        <v>-68.13453674316406</v>
       </c>
       <c r="Z17" t="n">
-        <v>-79.52149963378906</v>
+        <v>-71.50521087646484</v>
       </c>
       <c r="AA17" t="n">
-        <v>-80.35894012451172</v>
+        <v>-70.48492431640625</v>
       </c>
       <c r="AB17" t="n">
-        <v>-79.83903503417969</v>
+        <v>-71.12799072265625</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-66.69111633300781</v>
+        <v>-50.22522354125977</v>
       </c>
       <c r="B18" t="n">
-        <v>-72.02314758300781</v>
+        <v>-52.39974212646484</v>
       </c>
       <c r="C18" t="n">
-        <v>-71.76013946533203</v>
+        <v>-51.24489593505859</v>
       </c>
       <c r="D18" t="n">
-        <v>-72.25702667236328</v>
+        <v>-50.8704719543457</v>
       </c>
       <c r="E18" t="n">
-        <v>-75.75534057617188</v>
+        <v>-48.74613571166992</v>
       </c>
       <c r="F18" t="n">
-        <v>-72.15212249755859</v>
+        <v>-52.0855598449707</v>
       </c>
       <c r="G18" t="n">
-        <v>-70.07462310791016</v>
+        <v>-52.33549880981445</v>
       </c>
       <c r="H18" t="n">
-        <v>-66.1748046875</v>
+        <v>-51.09739303588867</v>
       </c>
       <c r="I18" t="n">
-        <v>-73.90046691894531</v>
+        <v>-53.92757034301758</v>
       </c>
       <c r="J18" t="n">
-        <v>-69.79678344726562</v>
+        <v>-53.32944488525391</v>
       </c>
       <c r="K18" t="n">
-        <v>-69.36789703369141</v>
+        <v>-54.2873420715332</v>
       </c>
       <c r="L18" t="n">
-        <v>-77.43444061279297</v>
+        <v>-54.10322189331055</v>
       </c>
       <c r="M18" t="n">
-        <v>-70.47522735595703</v>
+        <v>-54.9906005859375</v>
       </c>
       <c r="N18" t="n">
-        <v>-79.07201385498047</v>
+        <v>-52.40690994262695</v>
       </c>
       <c r="O18" t="n">
-        <v>-73.74082183837891</v>
+        <v>-56.05599975585938</v>
       </c>
       <c r="P18" t="n">
-        <v>-74.91039276123047</v>
+        <v>-56.90422439575195</v>
       </c>
       <c r="Q18" t="n">
-        <v>-74.53038024902344</v>
+        <v>-53.20668792724609</v>
       </c>
       <c r="R18" t="n">
-        <v>-72.55752563476562</v>
+        <v>-53.0686149597168</v>
       </c>
       <c r="S18" t="n">
-        <v>-72.59864807128906</v>
+        <v>-69.54255676269531</v>
       </c>
       <c r="T18" t="n">
-        <v>-72.41017150878906</v>
+        <v>-67.00211334228516</v>
       </c>
       <c r="U18" t="n">
-        <v>-77.51871490478516</v>
+        <v>-68.93470001220703</v>
       </c>
       <c r="V18" t="n">
-        <v>-76.79765319824219</v>
+        <v>-72.82270812988281</v>
       </c>
       <c r="W18" t="n">
-        <v>-78.60032653808594</v>
+        <v>-72.58129119873047</v>
       </c>
       <c r="X18" t="n">
-        <v>-70.48684692382812</v>
+        <v>-68.9930419921875</v>
       </c>
       <c r="Y18" t="n">
-        <v>-76.809326171875</v>
+        <v>-74.2125244140625</v>
       </c>
       <c r="Z18" t="n">
-        <v>-80.16561126708984</v>
+        <v>-71.84358215332031</v>
       </c>
       <c r="AA18" t="n">
-        <v>-80.76869201660156</v>
+        <v>-73.88484191894531</v>
       </c>
       <c r="AB18" t="n">
-        <v>-77.27940368652344</v>
+        <v>-69.86763000488281</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-65.66892242431641</v>
+        <v>-51.8220100402832</v>
       </c>
       <c r="B19" t="n">
-        <v>-75.6976318359375</v>
+        <v>-54.0688591003418</v>
       </c>
       <c r="C19" t="n">
-        <v>-71.51641082763672</v>
+        <v>-53.62754440307617</v>
       </c>
       <c r="D19" t="n">
-        <v>-68.6466064453125</v>
+        <v>-51.00857543945312</v>
       </c>
       <c r="E19" t="n">
-        <v>-73.03321075439453</v>
+        <v>-52.21724319458008</v>
       </c>
       <c r="F19" t="n">
-        <v>-66.02442932128906</v>
+        <v>-51.45005416870117</v>
       </c>
       <c r="G19" t="n">
-        <v>-71.10191345214844</v>
+        <v>-53.64345550537109</v>
       </c>
       <c r="H19" t="n">
-        <v>-69.96049499511719</v>
+        <v>-51.31417846679688</v>
       </c>
       <c r="I19" t="n">
-        <v>-71.16014862060547</v>
+        <v>-54.69671630859375</v>
       </c>
       <c r="J19" t="n">
-        <v>-73.12614440917969</v>
+        <v>-55.79241943359375</v>
       </c>
       <c r="K19" t="n">
-        <v>-71.51950073242188</v>
+        <v>-49.70817947387695</v>
       </c>
       <c r="L19" t="n">
-        <v>-77.70277404785156</v>
+        <v>-53.22660446166992</v>
       </c>
       <c r="M19" t="n">
-        <v>-72.07955932617188</v>
+        <v>-54.73433303833008</v>
       </c>
       <c r="N19" t="n">
-        <v>-76.76769256591797</v>
+        <v>-53.19573974609375</v>
       </c>
       <c r="O19" t="n">
-        <v>-75.69742584228516</v>
+        <v>-53.80254364013672</v>
       </c>
       <c r="P19" t="n">
-        <v>-78.07212829589844</v>
+        <v>-56.6111946105957</v>
       </c>
       <c r="Q19" t="n">
-        <v>-74.37855529785156</v>
+        <v>-53.1603889465332</v>
       </c>
       <c r="R19" t="n">
-        <v>-74.05214691162109</v>
+        <v>-54.00318145751953</v>
       </c>
       <c r="S19" t="n">
-        <v>-77.59681701660156</v>
+        <v>-52.40974044799805</v>
       </c>
       <c r="T19" t="n">
-        <v>-79.11094665527344</v>
+        <v>-67.6348876953125</v>
       </c>
       <c r="U19" t="n">
-        <v>-79.68849945068359</v>
+        <v>-69.45948791503906</v>
       </c>
       <c r="V19" t="n">
-        <v>-78.59841918945312</v>
+        <v>-71.43819427490234</v>
       </c>
       <c r="W19" t="n">
-        <v>-79.71012878417969</v>
+        <v>-70.95841979980469</v>
       </c>
       <c r="X19" t="n">
-        <v>-82.61798858642578</v>
+        <v>-68.02742767333984</v>
       </c>
       <c r="Y19" t="n">
-        <v>-79.61064910888672</v>
+        <v>-70.29704284667969</v>
       </c>
       <c r="Z19" t="n">
-        <v>-81.41543579101562</v>
+        <v>-70.28620910644531</v>
       </c>
       <c r="AA19" t="n">
-        <v>-81.00087738037109</v>
+        <v>-75.09870910644531</v>
       </c>
       <c r="AB19" t="n">
-        <v>-78.55274963378906</v>
+        <v>-72.26210784912109</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-70.51654815673828</v>
+        <v>-51.86007690429688</v>
       </c>
       <c r="B20" t="n">
-        <v>-70.49613189697266</v>
+        <v>-50.71985244750977</v>
       </c>
       <c r="C20" t="n">
-        <v>-71.48475646972656</v>
+        <v>-52.65346145629883</v>
       </c>
       <c r="D20" t="n">
-        <v>-74.35157012939453</v>
+        <v>-51.3021125793457</v>
       </c>
       <c r="E20" t="n">
-        <v>-72.06267547607422</v>
+        <v>-52.71793746948242</v>
       </c>
       <c r="F20" t="n">
-        <v>-68.75949096679688</v>
+        <v>-51.7596435546875</v>
       </c>
       <c r="G20" t="n">
-        <v>-71.75226593017578</v>
+        <v>-54.6197395324707</v>
       </c>
       <c r="H20" t="n">
-        <v>-75.00750732421875</v>
+        <v>-52.5129280090332</v>
       </c>
       <c r="I20" t="n">
-        <v>-74.40789794921875</v>
+        <v>-49.82367324829102</v>
       </c>
       <c r="J20" t="n">
-        <v>-69.00860595703125</v>
+        <v>-52.21096038818359</v>
       </c>
       <c r="K20" t="n">
-        <v>-71.31169891357422</v>
+        <v>-52.77191162109375</v>
       </c>
       <c r="L20" t="n">
-        <v>-73.45387268066406</v>
+        <v>-55.56705856323242</v>
       </c>
       <c r="M20" t="n">
-        <v>-79.33461761474609</v>
+        <v>-51.00131988525391</v>
       </c>
       <c r="N20" t="n">
-        <v>-74.49898529052734</v>
+        <v>-57.55972290039062</v>
       </c>
       <c r="O20" t="n">
-        <v>-77.26109313964844</v>
+        <v>-55.5323600769043</v>
       </c>
       <c r="P20" t="n">
-        <v>-73.34968566894531</v>
+        <v>-54.222412109375</v>
       </c>
       <c r="Q20" t="n">
-        <v>-76.31936645507812</v>
+        <v>-56.64765167236328</v>
       </c>
       <c r="R20" t="n">
-        <v>-79.68821716308594</v>
+        <v>-56.49523162841797</v>
       </c>
       <c r="S20" t="n">
-        <v>-77.81813812255859</v>
+        <v>-55.24657440185547</v>
       </c>
       <c r="T20" t="n">
-        <v>-75.16345977783203</v>
+        <v>-56.3955192565918</v>
       </c>
       <c r="U20" t="n">
-        <v>-79.75334167480469</v>
+        <v>-72.59904479980469</v>
       </c>
       <c r="V20" t="n">
-        <v>-77.74275207519531</v>
+        <v>-68.02433776855469</v>
       </c>
       <c r="W20" t="n">
-        <v>-76.28648376464844</v>
+        <v>-68.01971435546875</v>
       </c>
       <c r="X20" t="n">
-        <v>-75.89604187011719</v>
+        <v>-71.76333618164062</v>
       </c>
       <c r="Y20" t="n">
-        <v>-81.85404968261719</v>
+        <v>-72.33756256103516</v>
       </c>
       <c r="Z20" t="n">
-        <v>-78.55402374267578</v>
+        <v>-71.67333984375</v>
       </c>
       <c r="AA20" t="n">
-        <v>-79.07398986816406</v>
+        <v>-69.76461029052734</v>
       </c>
       <c r="AB20" t="n">
-        <v>-83.650634765625</v>
+        <v>-70.05943298339844</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-71.63816833496094</v>
+        <v>-52.76316452026367</v>
       </c>
       <c r="B21" t="n">
-        <v>-69.71632385253906</v>
+        <v>-52.73208618164062</v>
       </c>
       <c r="C21" t="n">
-        <v>-69.17899322509766</v>
+        <v>-49.40773773193359</v>
       </c>
       <c r="D21" t="n">
-        <v>-77.51766204833984</v>
+        <v>-52.82772064208984</v>
       </c>
       <c r="E21" t="n">
-        <v>-73.50392150878906</v>
+        <v>-52.23093795776367</v>
       </c>
       <c r="F21" t="n">
-        <v>-73.14151000976562</v>
+        <v>-49.32870483398438</v>
       </c>
       <c r="G21" t="n">
-        <v>-67.53705596923828</v>
+        <v>-53.15692901611328</v>
       </c>
       <c r="H21" t="n">
-        <v>-72.12450408935547</v>
+        <v>-52.86566925048828</v>
       </c>
       <c r="I21" t="n">
-        <v>-77.87306213378906</v>
+        <v>-51.0093994140625</v>
       </c>
       <c r="J21" t="n">
-        <v>-71.49028778076172</v>
+        <v>-55.31232833862305</v>
       </c>
       <c r="K21" t="n">
-        <v>-76.09183502197266</v>
+        <v>-52.95493316650391</v>
       </c>
       <c r="L21" t="n">
-        <v>-79.84092712402344</v>
+        <v>-52.73116302490234</v>
       </c>
       <c r="M21" t="n">
-        <v>-73.81364440917969</v>
+        <v>-53.58528900146484</v>
       </c>
       <c r="N21" t="n">
-        <v>-75.14064025878906</v>
+        <v>-52.65914154052734</v>
       </c>
       <c r="O21" t="n">
-        <v>-79.36132049560547</v>
+        <v>-51.91030120849609</v>
       </c>
       <c r="P21" t="n">
-        <v>-74.70512390136719</v>
+        <v>-57.43411254882812</v>
       </c>
       <c r="Q21" t="n">
-        <v>-71.05899047851562</v>
+        <v>-52.95670318603516</v>
       </c>
       <c r="R21" t="n">
-        <v>-75.71920776367188</v>
+        <v>-55.65864181518555</v>
       </c>
       <c r="S21" t="n">
-        <v>-77.61579895019531</v>
+        <v>-54.75880813598633</v>
       </c>
       <c r="T21" t="n">
-        <v>-76.25758361816406</v>
+        <v>-56.77223968505859</v>
       </c>
       <c r="U21" t="n">
-        <v>-79.8961181640625</v>
+        <v>-55.72560882568359</v>
       </c>
       <c r="V21" t="n">
-        <v>-77.63011169433594</v>
+        <v>-70.88741302490234</v>
       </c>
       <c r="W21" t="n">
-        <v>-77.94265747070312</v>
+        <v>-68.90652465820312</v>
       </c>
       <c r="X21" t="n">
-        <v>-80.70580291748047</v>
+        <v>-69.91450500488281</v>
       </c>
       <c r="Y21" t="n">
-        <v>-79.0872802734375</v>
+        <v>-72.42574310302734</v>
       </c>
       <c r="Z21" t="n">
-        <v>-78.93019866943359</v>
+        <v>-69.37944030761719</v>
       </c>
       <c r="AA21" t="n">
-        <v>-80.25437927246094</v>
+        <v>-70.20404052734375</v>
       </c>
       <c r="AB21" t="n">
-        <v>-84.97608184814453</v>
+        <v>-67.81252288818359</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-73.16664123535156</v>
+        <v>-51.86664962768555</v>
       </c>
       <c r="B22" t="n">
-        <v>-76.08524322509766</v>
+        <v>-52.3482666015625</v>
       </c>
       <c r="C22" t="n">
-        <v>-74.96018981933594</v>
+        <v>-51.4198112487793</v>
       </c>
       <c r="D22" t="n">
-        <v>-72.6575927734375</v>
+        <v>-50.91972351074219</v>
       </c>
       <c r="E22" t="n">
-        <v>-73.88963317871094</v>
+        <v>-50.85391616821289</v>
       </c>
       <c r="F22" t="n">
-        <v>-72.26884460449219</v>
+        <v>-54.93390655517578</v>
       </c>
       <c r="G22" t="n">
-        <v>-73.46075439453125</v>
+        <v>-51.68154144287109</v>
       </c>
       <c r="H22" t="n">
-        <v>-78.10478210449219</v>
+        <v>-48.83151626586914</v>
       </c>
       <c r="I22" t="n">
-        <v>-73.57621765136719</v>
+        <v>-55.34709548950195</v>
       </c>
       <c r="J22" t="n">
-        <v>-74.68040466308594</v>
+        <v>-54.06611251831055</v>
       </c>
       <c r="K22" t="n">
-        <v>-70.11716461181641</v>
+        <v>-53.40439605712891</v>
       </c>
       <c r="L22" t="n">
-        <v>-75.81221771240234</v>
+        <v>-54.25374221801758</v>
       </c>
       <c r="M22" t="n">
-        <v>-76.89328002929688</v>
+        <v>-53.3216667175293</v>
       </c>
       <c r="N22" t="n">
-        <v>-74.36268615722656</v>
+        <v>-54.32076263427734</v>
       </c>
       <c r="O22" t="n">
-        <v>-83.58219909667969</v>
+        <v>-57.45117950439453</v>
       </c>
       <c r="P22" t="n">
-        <v>-77.94508361816406</v>
+        <v>-55.34222412109375</v>
       </c>
       <c r="Q22" t="n">
-        <v>-70.45671081542969</v>
+        <v>-57.0357666015625</v>
       </c>
       <c r="R22" t="n">
-        <v>-73.67375946044922</v>
+        <v>-54.44559478759766</v>
       </c>
       <c r="S22" t="n">
-        <v>-80.00267028808594</v>
+        <v>-56.39290618896484</v>
       </c>
       <c r="T22" t="n">
-        <v>-77.2354736328125</v>
+        <v>-55.75325775146484</v>
       </c>
       <c r="U22" t="n">
-        <v>-69.99967193603516</v>
+        <v>-57.2446403503418</v>
       </c>
       <c r="V22" t="n">
-        <v>-76.76461029052734</v>
+        <v>-57.35049438476562</v>
       </c>
       <c r="W22" t="n">
-        <v>-79.16471862792969</v>
+        <v>-72.70272064208984</v>
       </c>
       <c r="X22" t="n">
-        <v>-79.52717590332031</v>
+        <v>-72.92958068847656</v>
       </c>
       <c r="Y22" t="n">
-        <v>-79.43270874023438</v>
+        <v>-69.69307708740234</v>
       </c>
       <c r="Z22" t="n">
-        <v>-79.33701324462891</v>
+        <v>-69.01883697509766</v>
       </c>
       <c r="AA22" t="n">
-        <v>-73.364013671875</v>
+        <v>-68.63764953613281</v>
       </c>
       <c r="AB22" t="n">
-        <v>-81.99134063720703</v>
+        <v>-73.05783843994141</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>-75.80809783935547</v>
+        <v>-54.61175537109375</v>
       </c>
       <c r="B23" t="n">
-        <v>-76.65592956542969</v>
+        <v>-51.81267166137695</v>
       </c>
       <c r="C23" t="n">
-        <v>-80.40056610107422</v>
+        <v>-52.98918533325195</v>
       </c>
       <c r="D23" t="n">
-        <v>-77.46632385253906</v>
+        <v>-55.14949798583984</v>
       </c>
       <c r="E23" t="n">
-        <v>-71.95722961425781</v>
+        <v>-53.17409133911133</v>
       </c>
       <c r="F23" t="n">
-        <v>-74.95726776123047</v>
+        <v>-53.35282135009766</v>
       </c>
       <c r="G23" t="n">
-        <v>-74.93435668945312</v>
+        <v>-51.93437576293945</v>
       </c>
       <c r="H23" t="n">
-        <v>-75.90707397460938</v>
+        <v>-55.8218879699707</v>
       </c>
       <c r="I23" t="n">
-        <v>-78.75736236572266</v>
+        <v>-56.22738647460938</v>
       </c>
       <c r="J23" t="n">
-        <v>-76.49394989013672</v>
+        <v>-56.48784255981445</v>
       </c>
       <c r="K23" t="n">
-        <v>-70.66416168212891</v>
+        <v>-55.13801956176758</v>
       </c>
       <c r="L23" t="n">
-        <v>-76.57572174072266</v>
+        <v>-55.8057746887207</v>
       </c>
       <c r="M23" t="n">
-        <v>-76.74633026123047</v>
+        <v>-55.57235717773438</v>
       </c>
       <c r="N23" t="n">
-        <v>-73.70371246337891</v>
+        <v>-59.55754852294922</v>
       </c>
       <c r="O23" t="n">
-        <v>-73.87977600097656</v>
+        <v>-57.44136810302734</v>
       </c>
       <c r="P23" t="n">
-        <v>-74.77850341796875</v>
+        <v>-57.64064407348633</v>
       </c>
       <c r="Q23" t="n">
-        <v>-76.74845886230469</v>
+        <v>-55.66021728515625</v>
       </c>
       <c r="R23" t="n">
-        <v>-79.56447601318359</v>
+        <v>-57.94157791137695</v>
       </c>
       <c r="S23" t="n">
-        <v>-82.03951263427734</v>
+        <v>-55.06809234619141</v>
       </c>
       <c r="T23" t="n">
-        <v>-83.19242095947266</v>
+        <v>-57.89089965820312</v>
       </c>
       <c r="U23" t="n">
-        <v>-80.4356689453125</v>
+        <v>-57.5999641418457</v>
       </c>
       <c r="V23" t="n">
-        <v>-81.15925598144531</v>
+        <v>-55.96894073486328</v>
       </c>
       <c r="W23" t="n">
-        <v>-74.35964965820312</v>
+        <v>-54.72615814208984</v>
       </c>
       <c r="X23" t="n">
-        <v>-72.58455657958984</v>
+        <v>-70.33320617675781</v>
       </c>
       <c r="Y23" t="n">
-        <v>-77.21080017089844</v>
+        <v>-68.95033264160156</v>
       </c>
       <c r="Z23" t="n">
-        <v>-80.00856018066406</v>
+        <v>-69.90549468994141</v>
       </c>
       <c r="AA23" t="n">
-        <v>-79.32548522949219</v>
+        <v>-70.53894805908203</v>
       </c>
       <c r="AB23" t="n">
-        <v>-75.54943084716797</v>
+        <v>-69.39640808105469</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>-74.07028198242188</v>
+        <v>-52.19430541992188</v>
       </c>
       <c r="B24" t="n">
-        <v>-75.88597106933594</v>
+        <v>-51.96906661987305</v>
       </c>
       <c r="C24" t="n">
-        <v>-81.87270355224609</v>
+        <v>-53.11777877807617</v>
       </c>
       <c r="D24" t="n">
-        <v>-75.53866577148438</v>
+        <v>-54.74143218994141</v>
       </c>
       <c r="E24" t="n">
-        <v>-76.55022430419922</v>
+        <v>-53.1979866027832</v>
       </c>
       <c r="F24" t="n">
-        <v>-73.89364624023438</v>
+        <v>-52.34109497070312</v>
       </c>
       <c r="G24" t="n">
-        <v>-73.91054534912109</v>
+        <v>-53.9310302734375</v>
       </c>
       <c r="H24" t="n">
-        <v>-75.98516082763672</v>
+        <v>-54.16803741455078</v>
       </c>
       <c r="I24" t="n">
-        <v>-73.47712707519531</v>
+        <v>-51.66147613525391</v>
       </c>
       <c r="J24" t="n">
-        <v>-72.49539947509766</v>
+        <v>-55.41135787963867</v>
       </c>
       <c r="K24" t="n">
-        <v>-74.52955627441406</v>
+        <v>-55.0040283203125</v>
       </c>
       <c r="L24" t="n">
-        <v>-76.05091094970703</v>
+        <v>-56.24602127075195</v>
       </c>
       <c r="M24" t="n">
-        <v>-79.46646881103516</v>
+        <v>-53.08217620849609</v>
       </c>
       <c r="N24" t="n">
-        <v>-76.15562438964844</v>
+        <v>-56.71810913085938</v>
       </c>
       <c r="O24" t="n">
-        <v>-77.7506103515625</v>
+        <v>-56.64687347412109</v>
       </c>
       <c r="P24" t="n">
-        <v>-76.57834625244141</v>
+        <v>-55.54531860351562</v>
       </c>
       <c r="Q24" t="n">
-        <v>-80.03543853759766</v>
+        <v>-55.42816925048828</v>
       </c>
       <c r="R24" t="n">
-        <v>-72.43936157226562</v>
+        <v>-55.80179595947266</v>
       </c>
       <c r="S24" t="n">
-        <v>-80.81486511230469</v>
+        <v>-57.04141235351562</v>
       </c>
       <c r="T24" t="n">
-        <v>-80.46818542480469</v>
+        <v>-57.05416870117188</v>
       </c>
       <c r="U24" t="n">
-        <v>-72.40145111083984</v>
+        <v>-54.4736213684082</v>
       </c>
       <c r="V24" t="n">
-        <v>-81.62532043457031</v>
+        <v>-56.85734176635742</v>
       </c>
       <c r="W24" t="n">
-        <v>-82.2410888671875</v>
+        <v>-55.1370735168457</v>
       </c>
       <c r="X24" t="n">
-        <v>-74.94746398925781</v>
+        <v>-57.75749588012695</v>
       </c>
       <c r="Y24" t="n">
-        <v>-81.07450103759766</v>
+        <v>-69.50279998779297</v>
       </c>
       <c r="Z24" t="n">
-        <v>-76.77145385742188</v>
+        <v>-75.34295654296875</v>
       </c>
       <c r="AA24" t="n">
-        <v>-79.66426849365234</v>
+        <v>-73.65448760986328</v>
       </c>
       <c r="AB24" t="n">
-        <v>-78.9097900390625</v>
+        <v>-70.92965698242188</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>-76.6339111328125</v>
+        <v>-48.77504730224609</v>
       </c>
       <c r="B25" t="n">
-        <v>-76.89310455322266</v>
+        <v>-53.398681640625</v>
       </c>
       <c r="C25" t="n">
-        <v>-73.57195281982422</v>
+        <v>-54.9883918762207</v>
       </c>
       <c r="D25" t="n">
-        <v>-78.45179748535156</v>
+        <v>-55.47389984130859</v>
       </c>
       <c r="E25" t="n">
-        <v>-74.48390197753906</v>
+        <v>-50.65058135986328</v>
       </c>
       <c r="F25" t="n">
-        <v>-72.8756103515625</v>
+        <v>-50.44338226318359</v>
       </c>
       <c r="G25" t="n">
-        <v>-76.81378173828125</v>
+        <v>-53.81319046020508</v>
       </c>
       <c r="H25" t="n">
-        <v>-71.61107635498047</v>
+        <v>-57.38076019287109</v>
       </c>
       <c r="I25" t="n">
-        <v>-75.9609375</v>
+        <v>-53.24556350708008</v>
       </c>
       <c r="J25" t="n">
-        <v>-69.08363342285156</v>
+        <v>-53.29892730712891</v>
       </c>
       <c r="K25" t="n">
-        <v>-78.69931030273438</v>
+        <v>-56.98215866088867</v>
       </c>
       <c r="L25" t="n">
-        <v>-79.52665710449219</v>
+        <v>-55.66206741333008</v>
       </c>
       <c r="M25" t="n">
-        <v>-76.26544952392578</v>
+        <v>-54.9296875</v>
       </c>
       <c r="N25" t="n">
-        <v>-76.05919647216797</v>
+        <v>-56.30830764770508</v>
       </c>
       <c r="O25" t="n">
-        <v>-81.21054840087891</v>
+        <v>-57.09574127197266</v>
       </c>
       <c r="P25" t="n">
-        <v>-79.39593505859375</v>
+        <v>-54.82368850708008</v>
       </c>
       <c r="Q25" t="n">
-        <v>-82.25514221191406</v>
+        <v>-58.25018310546875</v>
       </c>
       <c r="R25" t="n">
-        <v>-72.0318603515625</v>
+        <v>-55.84614181518555</v>
       </c>
       <c r="S25" t="n">
-        <v>-81.05567932128906</v>
+        <v>-56.07160186767578</v>
       </c>
       <c r="T25" t="n">
-        <v>-81.41032409667969</v>
+        <v>-50.93399429321289</v>
       </c>
       <c r="U25" t="n">
-        <v>-77.55890655517578</v>
+        <v>-57.90365600585938</v>
       </c>
       <c r="V25" t="n">
-        <v>-79.62325286865234</v>
+        <v>-60.25502395629883</v>
       </c>
       <c r="W25" t="n">
-        <v>-79.58866119384766</v>
+        <v>-60.11211395263672</v>
       </c>
       <c r="X25" t="n">
-        <v>-77.59519195556641</v>
+        <v>-56.45001220703125</v>
       </c>
       <c r="Y25" t="n">
-        <v>-81.99845123291016</v>
+        <v>-58.03369140625</v>
       </c>
       <c r="Z25" t="n">
-        <v>-76.82286834716797</v>
+        <v>-70.56272888183594</v>
       </c>
       <c r="AA25" t="n">
-        <v>-79.83009338378906</v>
+        <v>-74.73351287841797</v>
       </c>
       <c r="AB25" t="n">
-        <v>-84.60743713378906</v>
+        <v>-72.53140258789062</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>-79.56044006347656</v>
+        <v>-52.14778900146484</v>
       </c>
       <c r="B26" t="n">
-        <v>-78.52989959716797</v>
+        <v>-50.83913421630859</v>
       </c>
       <c r="C26" t="n">
-        <v>-76.45951843261719</v>
+        <v>-54.84902191162109</v>
       </c>
       <c r="D26" t="n">
-        <v>-76.89188385009766</v>
+        <v>-56.95793533325195</v>
       </c>
       <c r="E26" t="n">
-        <v>-79.49822235107422</v>
+        <v>-51.96546173095703</v>
       </c>
       <c r="F26" t="n">
-        <v>-74.42856597900391</v>
+        <v>-53.24138641357422</v>
       </c>
       <c r="G26" t="n">
-        <v>-79.55971527099609</v>
+        <v>-54.2042121887207</v>
       </c>
       <c r="H26" t="n">
-        <v>-81.63719940185547</v>
+        <v>-55.77830123901367</v>
       </c>
       <c r="I26" t="n">
-        <v>-76.69266510009766</v>
+        <v>-55.86244583129883</v>
       </c>
       <c r="J26" t="n">
-        <v>-79.14131927490234</v>
+        <v>-54.20487213134766</v>
       </c>
       <c r="K26" t="n">
-        <v>-81.19374847412109</v>
+        <v>-55.08611297607422</v>
       </c>
       <c r="L26" t="n">
-        <v>-77.92402648925781</v>
+        <v>-58.04201126098633</v>
       </c>
       <c r="M26" t="n">
-        <v>-79.77883911132812</v>
+        <v>-56.90396118164062</v>
       </c>
       <c r="N26" t="n">
-        <v>-79.90240478515625</v>
+        <v>-53.19670486450195</v>
       </c>
       <c r="O26" t="n">
-        <v>-74.62898254394531</v>
+        <v>-57.4512939453125</v>
       </c>
       <c r="P26" t="n">
-        <v>-79.30819702148438</v>
+        <v>-57.9738883972168</v>
       </c>
       <c r="Q26" t="n">
-        <v>-82.02508544921875</v>
+        <v>-58.69335174560547</v>
       </c>
       <c r="R26" t="n">
-        <v>-82.02677917480469</v>
+        <v>-54.32785797119141</v>
       </c>
       <c r="S26" t="n">
-        <v>-75.99477386474609</v>
+        <v>-55.04790115356445</v>
       </c>
       <c r="T26" t="n">
-        <v>-78.98751068115234</v>
+        <v>-54.99552154541016</v>
       </c>
       <c r="U26" t="n">
-        <v>-73.92124938964844</v>
+        <v>-52.24306488037109</v>
       </c>
       <c r="V26" t="n">
-        <v>-78.29605865478516</v>
+        <v>-54.45438766479492</v>
       </c>
       <c r="W26" t="n">
-        <v>-78.02203369140625</v>
+        <v>-58.28511428833008</v>
       </c>
       <c r="X26" t="n">
-        <v>-78.61019134521484</v>
+        <v>-55.89629364013672</v>
       </c>
       <c r="Y26" t="n">
-        <v>-81.18259429931641</v>
+        <v>-56.69658660888672</v>
       </c>
       <c r="Z26" t="n">
-        <v>-78.49226379394531</v>
+        <v>-58.54105377197266</v>
       </c>
       <c r="AA26" t="n">
-        <v>-79.79507446289062</v>
+        <v>-74.29019927978516</v>
       </c>
       <c r="AB26" t="n">
-        <v>-81.22373962402344</v>
+        <v>-70.38643646240234</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-73.36844635009766</v>
+        <v>-57.5158576965332</v>
       </c>
       <c r="B27" t="n">
-        <v>-77.19682312011719</v>
+        <v>-55.49120330810547</v>
       </c>
       <c r="C27" t="n">
-        <v>-78.82787322998047</v>
+        <v>-53.33394622802734</v>
       </c>
       <c r="D27" t="n">
-        <v>-79.00032043457031</v>
+        <v>-52.5635871887207</v>
       </c>
       <c r="E27" t="n">
-        <v>-76.50749969482422</v>
+        <v>-56.56888961791992</v>
       </c>
       <c r="F27" t="n">
-        <v>-82.56536865234375</v>
+        <v>-54.5594596862793</v>
       </c>
       <c r="G27" t="n">
-        <v>-78.51487731933594</v>
+        <v>-56.66851806640625</v>
       </c>
       <c r="H27" t="n">
-        <v>-78.30803680419922</v>
+        <v>-56.2935791015625</v>
       </c>
       <c r="I27" t="n">
-        <v>-76.65489196777344</v>
+        <v>-56.19706344604492</v>
       </c>
       <c r="J27" t="n">
-        <v>-75.03974914550781</v>
+        <v>-57.14913940429688</v>
       </c>
       <c r="K27" t="n">
-        <v>-74.1781005859375</v>
+        <v>-56.83437347412109</v>
       </c>
       <c r="L27" t="n">
-        <v>-79.88047027587891</v>
+        <v>-53.30596923828125</v>
       </c>
       <c r="M27" t="n">
-        <v>-74.26854705810547</v>
+        <v>-53.83443450927734</v>
       </c>
       <c r="N27" t="n">
-        <v>-75.88855743408203</v>
+        <v>-55.21277618408203</v>
       </c>
       <c r="O27" t="n">
-        <v>-84.16246032714844</v>
+        <v>-56.5864372253418</v>
       </c>
       <c r="P27" t="n">
-        <v>-83.58545684814453</v>
+        <v>-56.5009765625</v>
       </c>
       <c r="Q27" t="n">
-        <v>-79.28048706054688</v>
+        <v>-57.05280303955078</v>
       </c>
       <c r="R27" t="n">
-        <v>-78.08992767333984</v>
+        <v>-56.52701568603516</v>
       </c>
       <c r="S27" t="n">
-        <v>-80.3148193359375</v>
+        <v>-60.17999267578125</v>
       </c>
       <c r="T27" t="n">
-        <v>-82.04225158691406</v>
+        <v>-55.94407272338867</v>
       </c>
       <c r="U27" t="n">
-        <v>-77.35020446777344</v>
+        <v>-56.00505828857422</v>
       </c>
       <c r="V27" t="n">
-        <v>-77.93212890625</v>
+        <v>-56.87162017822266</v>
       </c>
       <c r="W27" t="n">
-        <v>-82.75068664550781</v>
+        <v>-57.93756103515625</v>
       </c>
       <c r="X27" t="n">
-        <v>-80.12519836425781</v>
+        <v>-56.69522857666016</v>
       </c>
       <c r="Y27" t="n">
-        <v>-79.90282440185547</v>
+        <v>-58.19617462158203</v>
       </c>
       <c r="Z27" t="n">
-        <v>-80.65210723876953</v>
+        <v>-58.39019775390625</v>
       </c>
       <c r="AA27" t="n">
-        <v>-82.09708404541016</v>
+        <v>-57.28415679931641</v>
       </c>
       <c r="AB27" t="n">
-        <v>-82.69106292724609</v>
+        <v>-70.70953369140625</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-77.12129211425781</v>
+        <v>-57.16726684570312</v>
       </c>
       <c r="B28" t="n">
-        <v>-81.33280944824219</v>
+        <v>-54.3053092956543</v>
       </c>
       <c r="C28" t="n">
-        <v>-77.17927551269531</v>
+        <v>-55.60681915283203</v>
       </c>
       <c r="D28" t="n">
-        <v>-76.99478912353516</v>
+        <v>-55.0156135559082</v>
       </c>
       <c r="E28" t="n">
-        <v>-79.74996948242188</v>
+        <v>-55.93761444091797</v>
       </c>
       <c r="F28" t="n">
-        <v>-77.31790924072266</v>
+        <v>-57.15389251708984</v>
       </c>
       <c r="G28" t="n">
-        <v>-77.37118530273438</v>
+        <v>-53.85092926025391</v>
       </c>
       <c r="H28" t="n">
-        <v>-76.58278656005859</v>
+        <v>-57.5140380859375</v>
       </c>
       <c r="I28" t="n">
-        <v>-81.98173522949219</v>
+        <v>-55.10968017578125</v>
       </c>
       <c r="J28" t="n">
-        <v>-78.80445098876953</v>
+        <v>-56.17216873168945</v>
       </c>
       <c r="K28" t="n">
-        <v>-76.84877014160156</v>
+        <v>-51.51703643798828</v>
       </c>
       <c r="L28" t="n">
-        <v>-75.07277679443359</v>
+        <v>-53.84310150146484</v>
       </c>
       <c r="M28" t="n">
-        <v>-79.77114868164062</v>
+        <v>-57.86371994018555</v>
       </c>
       <c r="N28" t="n">
-        <v>-78.32823181152344</v>
+        <v>-56.8032341003418</v>
       </c>
       <c r="O28" t="n">
-        <v>-82.10035705566406</v>
+        <v>-55.06230545043945</v>
       </c>
       <c r="P28" t="n">
-        <v>-78.5245361328125</v>
+        <v>-57.23675537109375</v>
       </c>
       <c r="Q28" t="n">
-        <v>-76.74819946289062</v>
+        <v>-55.28859710693359</v>
       </c>
       <c r="R28" t="n">
-        <v>-81.63816833496094</v>
+        <v>-57.41031646728516</v>
       </c>
       <c r="S28" t="n">
-        <v>-78.95393371582031</v>
+        <v>-58.18102264404297</v>
       </c>
       <c r="T28" t="n">
-        <v>-77.98097229003906</v>
+        <v>-57.57196044921875</v>
       </c>
       <c r="U28" t="n">
-        <v>-78.92832946777344</v>
+        <v>-59.64554977416992</v>
       </c>
       <c r="V28" t="n">
-        <v>-87.82027435302734</v>
+        <v>-53.1104621887207</v>
       </c>
       <c r="W28" t="n">
-        <v>-79.27070617675781</v>
+        <v>-55.38903045654297</v>
       </c>
       <c r="X28" t="n">
-        <v>-79.71662902832031</v>
+        <v>-57.42118453979492</v>
       </c>
       <c r="Y28" t="n">
-        <v>-82.62809753417969</v>
+        <v>-54.16376876831055</v>
       </c>
       <c r="Z28" t="n">
-        <v>-75.72476959228516</v>
+        <v>-57.13166046142578</v>
       </c>
       <c r="AA28" t="n">
-        <v>-84.89713287353516</v>
+        <v>-58.08770751953125</v>
       </c>
       <c r="AB28" t="n">
-        <v>-83.12837219238281</v>
+        <v>-57.24158477783203</v>
       </c>
     </row>
   </sheetData>
